--- a/docs/downloads/indices/nifty200-quality-30.xlsx
+++ b/docs/downloads/indices/nifty200-quality-30.xlsx
@@ -547,7 +547,7 @@
     <col width="34" customWidth="1" min="1" max="1"/>
     <col width="34" customWidth="1" min="2" max="2"/>
     <col width="24" customWidth="1" min="3" max="3"/>
-    <col width="23" customWidth="1" min="4" max="4"/>
+    <col width="24" customWidth="1" min="4" max="4"/>
     <col width="29" customWidth="1" min="5" max="5"/>
     <col width="17" customWidth="1" min="6" max="6"/>
     <col width="19" customWidth="1" min="7" max="7"/>
@@ -567,7 +567,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>46283</v>
+        <v>46286</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -595,7 +595,7 @@
         </is>
       </c>
       <c r="B5" s="6" t="n">
-        <v>19561.45</v>
+        <v>19649.4</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -603,7 +603,7 @@
         </is>
       </c>
       <c r="E5" s="7" t="n">
-        <v>26.51</v>
+        <v>26.63</v>
       </c>
     </row>
     <row r="6">
@@ -613,7 +613,7 @@
         </is>
       </c>
       <c r="B6" s="8" t="n">
-        <v>0.1136363636363636</v>
+        <v>0.1287878787878788</v>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
@@ -621,7 +621,7 @@
         </is>
       </c>
       <c r="E6" s="9" t="n">
-        <v>737.8894756695587</v>
+        <v>737.8670672174241</v>
       </c>
     </row>
     <row r="7">
@@ -631,7 +631,7 @@
         </is>
       </c>
       <c r="B7" s="8" t="n">
-        <v>0.01347423789383195</v>
+        <v>0.01345026141026473</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -639,7 +639,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.03772161448509996</v>
+        <v>0.03755163349605708</v>
       </c>
     </row>
     <row r="8">
@@ -649,7 +649,7 @@
         </is>
       </c>
       <c r="B8" s="11" t="n">
-        <v>88.63636363636364</v>
+        <v>87.12121212121212</v>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
@@ -657,7 +657,7 @@
         </is>
       </c>
       <c r="E8" s="11" t="n">
-        <v>25.38969515753278</v>
+        <v>25.38010456410589</v>
       </c>
     </row>
     <row r="9">
@@ -667,7 +667,7 @@
         </is>
       </c>
       <c r="B9" s="11" t="n">
-        <v>69.66236309271439</v>
+        <v>68.59887985408025</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -717,13 +717,13 @@
         </is>
       </c>
       <c r="B13" s="14" t="n">
-        <v>26.51364218255135</v>
+        <v>26.56491203900006</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>19564.13752817311</v>
+        <v>19601.37373710582</v>
       </c>
       <c r="D13" s="16" t="n">
-        <v>0.0001373890060862859</v>
+        <v>-0.002444159256475231</v>
       </c>
     </row>
     <row r="14">
@@ -733,13 +733,13 @@
         </is>
       </c>
       <c r="B14" s="14" t="n">
-        <v>29.5592998650817</v>
+        <v>29.55927314842858</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>21811.49627860439</v>
+        <v>21810.81418710975</v>
       </c>
       <c r="D14" s="16" t="n">
-        <v>0.1150245139600792</v>
+        <v>0.1099989916796313</v>
       </c>
     </row>
     <row r="15"/>
@@ -3742,7 +3742,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I2"/>
+  <dimension ref="A1:I3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -3833,6 +3833,39 @@
       </c>
       <c r="I2">
         <f>IF(H2="","",IF(H2&gt;=70,"BUY",IF(H2&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="18" t="n">
+        <v>46286</v>
+      </c>
+      <c r="B3" s="6" t="n">
+        <v>19649.4</v>
+      </c>
+      <c r="C3" s="7" t="n">
+        <v>26.63</v>
+      </c>
+      <c r="D3" s="8" t="n">
+        <v>0.128787878788</v>
+      </c>
+      <c r="E3" s="8" t="n">
+        <v>0.0134502614103</v>
+      </c>
+      <c r="F3" s="22">
+        <f>IF(D3="","",100*(1-D3))</f>
+        <v/>
+      </c>
+      <c r="G3" s="22">
+        <f>IF(E3="","",IF(E3&lt;=0,20,IF(E3&lt;5%,20+400*E3,IF(E3&lt;10%,40+400*(E3-5%),IF(E3&lt;15%,60+400*(E3-10%),IF(E3&lt;25%,80+200*(E3-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H3" s="22">
+        <f>IF(OR(F3="",G3=""),"",70%*F3+30%*G3)</f>
+        <v/>
+      </c>
+      <c r="I3">
+        <f>IF(H3="","",IF(H3&gt;=70,"BUY",IF(H3&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>

--- a/docs/downloads/indices/nifty200-quality-30.xlsx
+++ b/docs/downloads/indices/nifty200-quality-30.xlsx
@@ -567,7 +567,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -595,7 +595,7 @@
         </is>
       </c>
       <c r="B5" s="6" t="n">
-        <v>19649.4</v>
+        <v>19550.75</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -603,7 +603,7 @@
         </is>
       </c>
       <c r="E5" s="7" t="n">
-        <v>26.63</v>
+        <v>26.5</v>
       </c>
     </row>
     <row r="6">
@@ -613,7 +613,7 @@
         </is>
       </c>
       <c r="B6" s="8" t="n">
-        <v>0.1287878787878788</v>
+        <v>0.1136363636363636</v>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
@@ -621,7 +621,7 @@
         </is>
       </c>
       <c r="E6" s="9" t="n">
-        <v>737.8670672174241</v>
+        <v>737.7641509433962</v>
       </c>
     </row>
     <row r="7">
@@ -631,7 +631,7 @@
         </is>
       </c>
       <c r="B7" s="8" t="n">
-        <v>0.01345026141026473</v>
+        <v>0.01340698395529483</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -639,7 +639,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.03755163349605708</v>
+        <v>0.03773584905660377</v>
       </c>
     </row>
     <row r="8">
@@ -649,7 +649,7 @@
         </is>
       </c>
       <c r="B8" s="11" t="n">
-        <v>87.12121212121212</v>
+        <v>88.63636363636364</v>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
@@ -657,7 +657,7 @@
         </is>
       </c>
       <c r="E8" s="11" t="n">
-        <v>25.38010456410589</v>
+        <v>25.36279358211793</v>
       </c>
     </row>
     <row r="9">
@@ -667,7 +667,7 @@
         </is>
       </c>
       <c r="B9" s="11" t="n">
-        <v>68.59887985408025</v>
+        <v>69.65429262008993</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -717,13 +717,13 @@
         </is>
       </c>
       <c r="B13" s="14" t="n">
-        <v>26.56491203900006</v>
+        <v>26.50392097844397</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>19601.37373710582</v>
+        <v>19553.64275733258</v>
       </c>
       <c r="D13" s="16" t="n">
-        <v>-0.002444159256475231</v>
+        <v>0.0001479614507158278</v>
       </c>
     </row>
     <row r="14">
@@ -733,13 +733,13 @@
         </is>
       </c>
       <c r="B14" s="14" t="n">
-        <v>29.55927314842858</v>
+        <v>29.55922492497876</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>21810.81418710975</v>
+        <v>21807.73647932183</v>
       </c>
       <c r="D14" s="16" t="n">
-        <v>0.1099989916796313</v>
+        <v>0.1154424499991982</v>
       </c>
     </row>
     <row r="15"/>
@@ -3742,7 +3742,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I3"/>
+  <dimension ref="A1:I4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -3866,6 +3866,39 @@
       </c>
       <c r="I3">
         <f>IF(H3="","",IF(H3&gt;=70,"BUY",IF(H3&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="18" t="n">
+        <v>46287</v>
+      </c>
+      <c r="B4" s="6" t="n">
+        <v>19550.75</v>
+      </c>
+      <c r="C4" s="7" t="n">
+        <v>26.5</v>
+      </c>
+      <c r="D4" s="8" t="n">
+        <v>0.113636363636</v>
+      </c>
+      <c r="E4" s="8" t="n">
+        <v>0.0134069839553</v>
+      </c>
+      <c r="F4" s="22">
+        <f>IF(D4="","",100*(1-D4))</f>
+        <v/>
+      </c>
+      <c r="G4" s="22">
+        <f>IF(E4="","",IF(E4&lt;=0,20,IF(E4&lt;5%,20+400*E4,IF(E4&lt;10%,40+400*(E4-5%),IF(E4&lt;15%,60+400*(E4-10%),IF(E4&lt;25%,80+200*(E4-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H4" s="22">
+        <f>IF(OR(F4="",G4=""),"",70%*F4+30%*G4)</f>
+        <v/>
+      </c>
+      <c r="I4">
+        <f>IF(H4="","",IF(H4&gt;=70,"BUY",IF(H4&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>

--- a/docs/downloads/indices/nifty200-quality-30.xlsx
+++ b/docs/downloads/indices/nifty200-quality-30.xlsx
@@ -12,6 +12,7 @@
     <sheet name="Quarterly Backtest" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Score History" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="Sources &amp; Methodology" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Composition" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -20,17 +21,16 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="8">
-    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
-    <numFmt numFmtId="165" formatCode="dd-mmm-yyyy"/>
-    <numFmt numFmtId="166" formatCode="#,##0.00;[Red](#,##0.00);-"/>
-    <numFmt numFmtId="167" formatCode="0.00x;[Red](0.00x);-"/>
-    <numFmt numFmtId="168" formatCode="0.0%"/>
-    <numFmt numFmtId="169" formatCode="#,##0.0;[Red](#,##0.0);-"/>
-    <numFmt numFmtId="170" formatCode="0.0"/>
-    <numFmt numFmtId="171" formatCode="0.00x"/>
+  <numFmts count="7">
+    <numFmt numFmtId="164" formatCode="dd-mmm-yyyy"/>
+    <numFmt numFmtId="165" formatCode="#,##0.00;[Red](#,##0.00);-"/>
+    <numFmt numFmtId="166" formatCode="0.00x;[Red](0.00x);-"/>
+    <numFmt numFmtId="167" formatCode="0.0%"/>
+    <numFmt numFmtId="168" formatCode="#,##0.0;[Red](#,##0.0);-"/>
+    <numFmt numFmtId="169" formatCode="0.0"/>
+    <numFmt numFmtId="170" formatCode="0.00x"/>
   </numFmts>
-  <fonts count="8">
+  <fonts count="9">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -67,6 +67,11 @@
       <color theme="10"/>
       <sz val="12"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="15"/>
     </font>
   </fonts>
   <fills count="5">
@@ -105,36 +110,49 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="168" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="10" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="169" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="170" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="10" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="167" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="168" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="169" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="10" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="170" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="171" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
+    <xf numFmtId="170" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="10" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="170" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -566,7 +584,7 @@
           <t>As of</t>
         </is>
       </c>
-      <c r="B2" s="3" t="n">
+      <c r="B2" s="23" t="n">
         <v>46287</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -580,7 +598,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
@@ -594,7 +611,7 @@
           <t>Index level</t>
         </is>
       </c>
-      <c r="B5" s="6" t="n">
+      <c r="B5" s="24" t="n">
         <v>19550.75</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -602,7 +619,7 @@
           <t>P/E</t>
         </is>
       </c>
-      <c r="E5" s="7" t="n">
+      <c r="E5" s="25" t="n">
         <v>26.5</v>
       </c>
     </row>
@@ -612,7 +629,7 @@
           <t>P/E percentile</t>
         </is>
       </c>
-      <c r="B6" s="8" t="n">
+      <c r="B6" s="26" t="n">
         <v>0.1136363636363636</v>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -620,7 +637,7 @@
           <t>Implied EPS</t>
         </is>
       </c>
-      <c r="E6" s="9" t="n">
+      <c r="E6" s="27" t="n">
         <v>737.7641509433962</v>
       </c>
     </row>
@@ -630,7 +647,7 @@
           <t>YoY implied EPS growth</t>
         </is>
       </c>
-      <c r="B7" s="8" t="n">
+      <c r="B7" s="26" t="n">
         <v>0.01340698395529483</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -648,7 +665,7 @@
           <t>Valuation score</t>
         </is>
       </c>
-      <c r="B8" s="11" t="n">
+      <c r="B8" s="28" t="n">
         <v>88.63636363636364</v>
       </c>
       <c r="D8" s="2" t="inlineStr">
@@ -656,7 +673,7 @@
           <t>Growth score</t>
         </is>
       </c>
-      <c r="E8" s="11" t="n">
+      <c r="E8" s="28" t="n">
         <v>25.36279358211793</v>
       </c>
     </row>
@@ -666,7 +683,7 @@
           <t>Composite score</t>
         </is>
       </c>
-      <c r="B9" s="11" t="n">
+      <c r="B9" s="28" t="n">
         <v>69.65429262008993</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -680,7 +697,6 @@
         </is>
       </c>
     </row>
-    <row r="10"/>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
@@ -716,13 +732,13 @@
           <t>BUY → HOLD</t>
         </is>
       </c>
-      <c r="B13" s="14" t="n">
+      <c r="B13" s="29" t="n">
         <v>26.50392097844397</v>
       </c>
       <c r="C13" s="15" t="n">
         <v>19553.64275733258</v>
       </c>
-      <c r="D13" s="16" t="n">
+      <c r="D13" s="30" t="n">
         <v>0.0001479614507158278</v>
       </c>
     </row>
@@ -732,17 +748,16 @@
           <t>HOLD → SELL</t>
         </is>
       </c>
-      <c r="B14" s="14" t="n">
+      <c r="B14" s="29" t="n">
         <v>29.55922492497876</v>
       </c>
       <c r="C14" s="15" t="n">
         <v>21807.73647932183</v>
       </c>
-      <c r="D14" s="16" t="n">
+      <c r="D14" s="30" t="n">
         <v>0.1154424499991982</v>
       </c>
     </row>
-    <row r="15"/>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
@@ -796,17 +811,17 @@
       <c r="B18" t="n">
         <v>6</v>
       </c>
-      <c r="C18" s="16" t="n">
+      <c r="C18" s="30" t="n">
         <v>0.3243788351336814</v>
       </c>
-      <c r="D18" s="16" t="n">
+      <c r="D18" s="30" t="n">
         <v>0.1350458114630114</v>
       </c>
-      <c r="E18" s="16" t="n">
+      <c r="E18" s="30" t="n">
         <v>0.1841677233393925</v>
       </c>
-      <c r="F18" s="16" t="n"/>
-      <c r="G18" s="16" t="n">
+      <c r="F18" s="30" t="n"/>
+      <c r="G18" s="30" t="n">
         <v>0</v>
       </c>
     </row>
@@ -819,17 +834,17 @@
       <c r="B19" t="n">
         <v>6</v>
       </c>
-      <c r="C19" s="16" t="n">
+      <c r="C19" s="30" t="n">
         <v>0.131826119588194</v>
       </c>
-      <c r="D19" s="16" t="n">
+      <c r="D19" s="30" t="n">
         <v>0.1375752715747722</v>
       </c>
-      <c r="E19" s="16" t="n">
+      <c r="E19" s="30" t="n">
         <v>0.1797087246808945</v>
       </c>
-      <c r="F19" s="16" t="n"/>
-      <c r="G19" s="16" t="n">
+      <c r="F19" s="30" t="n"/>
+      <c r="G19" s="30" t="n">
         <v>0</v>
       </c>
     </row>
@@ -842,17 +857,17 @@
       <c r="B20" t="n">
         <v>7</v>
       </c>
-      <c r="C20" s="16" t="n">
+      <c r="C20" s="30" t="n">
         <v>0.002608895744658335</v>
       </c>
-      <c r="D20" s="16" t="n">
+      <c r="D20" s="30" t="n">
         <v>0.1297583507672395</v>
       </c>
-      <c r="E20" s="16" t="n">
+      <c r="E20" s="30" t="n">
         <v>0.1524413062157007</v>
       </c>
-      <c r="F20" s="16" t="n"/>
-      <c r="G20" s="16" t="n">
+      <c r="F20" s="30" t="n"/>
+      <c r="G20" s="30" t="n">
         <v>0</v>
       </c>
     </row>
@@ -865,17 +880,17 @@
       <c r="B21" t="n">
         <v>6</v>
       </c>
-      <c r="C21" s="16" t="n">
+      <c r="C21" s="30" t="n">
         <v>-0.03771959588046353</v>
       </c>
-      <c r="D21" s="16" t="n">
+      <c r="D21" s="30" t="n">
         <v>0.1421152387233346</v>
       </c>
-      <c r="E21" s="16" t="n">
+      <c r="E21" s="30" t="n">
         <v>0.09409439304594247</v>
       </c>
-      <c r="F21" s="16" t="n"/>
-      <c r="G21" s="16" t="n">
+      <c r="F21" s="30" t="n"/>
+      <c r="G21" s="30" t="n">
         <v>0</v>
       </c>
     </row>
@@ -888,21 +903,20 @@
       <c r="B22" t="n">
         <v>8</v>
       </c>
-      <c r="C22" s="16" t="n">
+      <c r="C22" s="30" t="n">
         <v>0.03410216634441721</v>
       </c>
-      <c r="D22" s="16" t="n">
+      <c r="D22" s="30" t="n">
         <v>0.1694475511285383</v>
       </c>
-      <c r="E22" s="16" t="n">
+      <c r="E22" s="30" t="n">
         <v>0.1180829939767365</v>
       </c>
-      <c r="F22" s="16" t="n"/>
-      <c r="G22" s="16" t="n">
+      <c r="F22" s="30" t="n"/>
+      <c r="G22" s="30" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="23"/>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
@@ -1038,16 +1052,16 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="18" t="n">
+      <c r="A2" s="31" t="n">
         <v>44316</v>
       </c>
-      <c r="B2" s="6" t="n">
+      <c r="B2" s="24" t="n">
         <v>12108.8</v>
       </c>
-      <c r="C2" s="7" t="n">
+      <c r="C2" s="25" t="n">
         <v>31.15</v>
       </c>
-      <c r="D2" s="19">
+      <c r="D2" s="32">
         <f>IFERROR(B2/C2,"")</f>
         <v/>
       </c>
@@ -1057,16 +1071,16 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="18" t="n">
+      <c r="A3" s="31" t="n">
         <v>44347</v>
       </c>
-      <c r="B3" s="6" t="n">
+      <c r="B3" s="24" t="n">
         <v>13063.1</v>
       </c>
-      <c r="C3" s="7" t="n">
+      <c r="C3" s="25" t="n">
         <v>32.44</v>
       </c>
-      <c r="D3" s="19">
+      <c r="D3" s="32">
         <f>IFERROR(B3/C3,"")</f>
         <v/>
       </c>
@@ -1076,16 +1090,16 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="18" t="n">
+      <c r="A4" s="31" t="n">
         <v>44377</v>
       </c>
-      <c r="B4" s="6" t="n">
+      <c r="B4" s="24" t="n">
         <v>13433.05</v>
       </c>
-      <c r="C4" s="7" t="n">
+      <c r="C4" s="25" t="n">
         <v>31.16</v>
       </c>
-      <c r="D4" s="19">
+      <c r="D4" s="32">
         <f>IFERROR(B4/C4,"")</f>
         <v/>
       </c>
@@ -1095,16 +1109,16 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="18" t="n">
+      <c r="A5" s="31" t="n">
         <v>44408</v>
       </c>
-      <c r="B5" s="6" t="n">
+      <c r="B5" s="24" t="n">
         <v>13745.75</v>
       </c>
-      <c r="C5" s="7" t="n">
+      <c r="C5" s="25" t="n">
         <v>30.79</v>
       </c>
-      <c r="D5" s="19">
+      <c r="D5" s="32">
         <f>IFERROR(B5/C5,"")</f>
         <v/>
       </c>
@@ -1114,16 +1128,16 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="18" t="n">
+      <c r="A6" s="31" t="n">
         <v>44439</v>
       </c>
-      <c r="B6" s="6" t="n">
+      <c r="B6" s="24" t="n">
         <v>14606.2</v>
       </c>
-      <c r="C6" s="7" t="n">
+      <c r="C6" s="25" t="n">
         <v>31.29</v>
       </c>
-      <c r="D6" s="19">
+      <c r="D6" s="32">
         <f>IFERROR(B6/C6,"")</f>
         <v/>
       </c>
@@ -1133,16 +1147,16 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="18" t="n">
+      <c r="A7" s="31" t="n">
         <v>44469</v>
       </c>
-      <c r="B7" s="6" t="n">
+      <c r="B7" s="24" t="n">
         <v>15076.2</v>
       </c>
-      <c r="C7" s="7" t="n">
+      <c r="C7" s="25" t="n">
         <v>32.31</v>
       </c>
-      <c r="D7" s="19">
+      <c r="D7" s="32">
         <f>IFERROR(B7/C7,"")</f>
         <v/>
       </c>
@@ -1152,16 +1166,16 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="18" t="n">
+      <c r="A8" s="31" t="n">
         <v>44500</v>
       </c>
-      <c r="B8" s="6" t="n">
+      <c r="B8" s="24" t="n">
         <v>14665.8</v>
       </c>
-      <c r="C8" s="7" t="n">
+      <c r="C8" s="25" t="n">
         <v>30.72</v>
       </c>
-      <c r="D8" s="19">
+      <c r="D8" s="32">
         <f>IFERROR(B8/C8,"")</f>
         <v/>
       </c>
@@ -1171,16 +1185,16 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="18" t="n">
+      <c r="A9" s="31" t="n">
         <v>44530</v>
       </c>
-      <c r="B9" s="6" t="n">
+      <c r="B9" s="24" t="n">
         <v>14478.7</v>
       </c>
-      <c r="C9" s="7" t="n">
+      <c r="C9" s="25" t="n">
         <v>30.2</v>
       </c>
-      <c r="D9" s="19">
+      <c r="D9" s="32">
         <f>IFERROR(B9/C9,"")</f>
         <v/>
       </c>
@@ -1190,16 +1204,16 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="18" t="n">
+      <c r="A10" s="31" t="n">
         <v>44561</v>
       </c>
-      <c r="B10" s="6" t="n">
+      <c r="B10" s="24" t="n">
         <v>15166</v>
       </c>
-      <c r="C10" s="7" t="n">
+      <c r="C10" s="25" t="n">
         <v>31.73</v>
       </c>
-      <c r="D10" s="19">
+      <c r="D10" s="32">
         <f>IFERROR(B10/C10,"")</f>
         <v/>
       </c>
@@ -1209,16 +1223,16 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="18" t="n">
+      <c r="A11" s="31" t="n">
         <v>44592</v>
       </c>
-      <c r="B11" s="6" t="n">
+      <c r="B11" s="24" t="n">
         <v>14298.85</v>
       </c>
-      <c r="C11" s="7" t="n">
+      <c r="C11" s="25" t="n">
         <v>29.96</v>
       </c>
-      <c r="D11" s="19">
+      <c r="D11" s="32">
         <f>IFERROR(B11/C11,"")</f>
         <v/>
       </c>
@@ -1228,16 +1242,16 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="18" t="n">
+      <c r="A12" s="31" t="n">
         <v>44620</v>
       </c>
-      <c r="B12" s="6" t="n">
+      <c r="B12" s="24" t="n">
         <v>14042.5</v>
       </c>
-      <c r="C12" s="7" t="n">
+      <c r="C12" s="25" t="n">
         <v>29.04</v>
       </c>
-      <c r="D12" s="19">
+      <c r="D12" s="32">
         <f>IFERROR(B12/C12,"")</f>
         <v/>
       </c>
@@ -1247,16 +1261,16 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="18" t="n">
+      <c r="A13" s="31" t="n">
         <v>44651</v>
       </c>
-      <c r="B13" s="6" t="n">
+      <c r="B13" s="24" t="n">
         <v>14361.55</v>
       </c>
-      <c r="C13" s="7" t="n">
+      <c r="C13" s="25" t="n">
         <v>29.69</v>
       </c>
-      <c r="D13" s="19">
+      <c r="D13" s="32">
         <f>IFERROR(B13/C13,"")</f>
         <v/>
       </c>
@@ -1266,16 +1280,16 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="18" t="n">
+      <c r="A14" s="31" t="n">
         <v>44681</v>
       </c>
-      <c r="B14" s="6" t="n">
+      <c r="B14" s="24" t="n">
         <v>14235.6</v>
       </c>
-      <c r="C14" s="7" t="n">
+      <c r="C14" s="25" t="n">
         <v>28.96</v>
       </c>
-      <c r="D14" s="19">
+      <c r="D14" s="32">
         <f>IFERROR(B14/C14,"")</f>
         <v/>
       </c>
@@ -1285,16 +1299,16 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="18" t="n">
+      <c r="A15" s="31" t="n">
         <v>44712</v>
       </c>
-      <c r="B15" s="6" t="n">
+      <c r="B15" s="24" t="n">
         <v>13794.7</v>
       </c>
-      <c r="C15" s="7" t="n">
+      <c r="C15" s="25" t="n">
         <v>27.27</v>
       </c>
-      <c r="D15" s="19">
+      <c r="D15" s="32">
         <f>IFERROR(B15/C15,"")</f>
         <v/>
       </c>
@@ -1304,16 +1318,16 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="18" t="n">
+      <c r="A16" s="31" t="n">
         <v>44742</v>
       </c>
-      <c r="B16" s="6" t="n">
+      <c r="B16" s="24" t="n">
         <v>13077.95</v>
       </c>
-      <c r="C16" s="7" t="n">
+      <c r="C16" s="25" t="n">
         <v>27.04</v>
       </c>
-      <c r="D16" s="19">
+      <c r="D16" s="32">
         <f>IFERROR(B16/C16,"")</f>
         <v/>
       </c>
@@ -1323,16 +1337,16 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="18" t="n">
+      <c r="A17" s="31" t="n">
         <v>44773</v>
       </c>
-      <c r="B17" s="6" t="n">
+      <c r="B17" s="24" t="n">
         <v>14420.9</v>
       </c>
-      <c r="C17" s="7" t="n">
+      <c r="C17" s="25" t="n">
         <v>29.55</v>
       </c>
-      <c r="D17" s="19">
+      <c r="D17" s="32">
         <f>IFERROR(B17/C17,"")</f>
         <v/>
       </c>
@@ -1342,16 +1356,16 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="18" t="n">
+      <c r="A18" s="31" t="n">
         <v>44804</v>
       </c>
-      <c r="B18" s="6" t="n">
+      <c r="B18" s="24" t="n">
         <v>14792.25</v>
       </c>
-      <c r="C18" s="7" t="n">
+      <c r="C18" s="25" t="n">
         <v>28.25</v>
       </c>
-      <c r="D18" s="19">
+      <c r="D18" s="32">
         <f>IFERROR(B18/C18,"")</f>
         <v/>
       </c>
@@ -1361,16 +1375,16 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="18" t="n">
+      <c r="A19" s="31" t="n">
         <v>44834</v>
       </c>
-      <c r="B19" s="6" t="n">
+      <c r="B19" s="24" t="n">
         <v>14337.4</v>
       </c>
-      <c r="C19" s="7" t="n">
+      <c r="C19" s="25" t="n">
         <v>26.56</v>
       </c>
-      <c r="D19" s="19">
+      <c r="D19" s="32">
         <f>IFERROR(B19/C19,"")</f>
         <v/>
       </c>
@@ -1380,16 +1394,16 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="18" t="n">
+      <c r="A20" s="31" t="n">
         <v>44865</v>
       </c>
-      <c r="B20" s="6" t="n">
+      <c r="B20" s="24" t="n">
         <v>14532.9</v>
       </c>
-      <c r="C20" s="7" t="n">
+      <c r="C20" s="25" t="n">
         <v>26.8</v>
       </c>
-      <c r="D20" s="19">
+      <c r="D20" s="32">
         <f>IFERROR(B20/C20,"")</f>
         <v/>
       </c>
@@ -1399,16 +1413,16 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="18" t="n">
+      <c r="A21" s="31" t="n">
         <v>44895</v>
       </c>
-      <c r="B21" s="6" t="n">
+      <c r="B21" s="24" t="n">
         <v>14912.85</v>
       </c>
-      <c r="C21" s="7" t="n">
+      <c r="C21" s="25" t="n">
         <v>26.72</v>
       </c>
-      <c r="D21" s="19">
+      <c r="D21" s="32">
         <f>IFERROR(B21/C21,"")</f>
         <v/>
       </c>
@@ -1418,16 +1432,16 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="18" t="n">
+      <c r="A22" s="31" t="n">
         <v>44926</v>
       </c>
-      <c r="B22" s="6" t="n">
+      <c r="B22" s="24" t="n">
         <v>14208.25</v>
       </c>
-      <c r="C22" s="7" t="n">
+      <c r="C22" s="25" t="n">
         <v>25.73</v>
       </c>
-      <c r="D22" s="19">
+      <c r="D22" s="32">
         <f>IFERROR(B22/C22,"")</f>
         <v/>
       </c>
@@ -1437,16 +1451,16 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="18" t="n">
+      <c r="A23" s="31" t="n">
         <v>44957</v>
       </c>
-      <c r="B23" s="6" t="n">
+      <c r="B23" s="24" t="n">
         <v>14110.95</v>
       </c>
-      <c r="C23" s="7" t="n">
+      <c r="C23" s="25" t="n">
         <v>25.33</v>
       </c>
-      <c r="D23" s="19">
+      <c r="D23" s="32">
         <f>IFERROR(B23/C23,"")</f>
         <v/>
       </c>
@@ -1456,16 +1470,16 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="18" t="n">
+      <c r="A24" s="31" t="n">
         <v>44985</v>
       </c>
-      <c r="B24" s="6" t="n">
+      <c r="B24" s="24" t="n">
         <v>14025.55</v>
       </c>
-      <c r="C24" s="7" t="n">
+      <c r="C24" s="25" t="n">
         <v>24.35</v>
       </c>
-      <c r="D24" s="19">
+      <c r="D24" s="32">
         <f>IFERROR(B24/C24,"")</f>
         <v/>
       </c>
@@ -1475,16 +1489,16 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="18" t="n">
+      <c r="A25" s="31" t="n">
         <v>45016</v>
       </c>
-      <c r="B25" s="6" t="n">
+      <c r="B25" s="24" t="n">
         <v>14014.15</v>
       </c>
-      <c r="C25" s="7" t="n">
+      <c r="C25" s="25" t="n">
         <v>24.3</v>
       </c>
-      <c r="D25" s="19">
+      <c r="D25" s="32">
         <f>IFERROR(B25/C25,"")</f>
         <v/>
       </c>
@@ -1494,16 +1508,16 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="18" t="n">
+      <c r="A26" s="31" t="n">
         <v>45046</v>
       </c>
-      <c r="B26" s="6" t="n">
+      <c r="B26" s="24" t="n">
         <v>14596.3</v>
       </c>
-      <c r="C26" s="7" t="n">
+      <c r="C26" s="25" t="n">
         <v>25.14</v>
       </c>
-      <c r="D26" s="19">
+      <c r="D26" s="32">
         <f>IFERROR(B26/C26,"")</f>
         <v/>
       </c>
@@ -1513,16 +1527,16 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="18" t="n">
+      <c r="A27" s="31" t="n">
         <v>45077</v>
       </c>
-      <c r="B27" s="6" t="n">
+      <c r="B27" s="24" t="n">
         <v>15285.35</v>
       </c>
-      <c r="C27" s="7" t="n">
+      <c r="C27" s="25" t="n">
         <v>26.49</v>
       </c>
-      <c r="D27" s="19">
+      <c r="D27" s="32">
         <f>IFERROR(B27/C27,"")</f>
         <v/>
       </c>
@@ -1532,16 +1546,16 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="18" t="n">
+      <c r="A28" s="31" t="n">
         <v>45107</v>
       </c>
-      <c r="B28" s="6" t="n">
+      <c r="B28" s="24" t="n">
         <v>15648.8</v>
       </c>
-      <c r="C28" s="7" t="n">
+      <c r="C28" s="25" t="n">
         <v>26.69</v>
       </c>
-      <c r="D28" s="19">
+      <c r="D28" s="32">
         <f>IFERROR(B28/C28,"")</f>
         <v/>
       </c>
@@ -1551,16 +1565,16 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="18" t="n">
+      <c r="A29" s="31" t="n">
         <v>45138</v>
       </c>
-      <c r="B29" s="6" t="n">
+      <c r="B29" s="24" t="n">
         <v>15980.5</v>
       </c>
-      <c r="C29" s="7" t="n">
+      <c r="C29" s="25" t="n">
         <v>26.79</v>
       </c>
-      <c r="D29" s="19">
+      <c r="D29" s="32">
         <f>IFERROR(B29/C29,"")</f>
         <v/>
       </c>
@@ -1570,16 +1584,16 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="18" t="n">
+      <c r="A30" s="31" t="n">
         <v>45169</v>
       </c>
-      <c r="B30" s="6" t="n">
+      <c r="B30" s="24" t="n">
         <v>15929.5</v>
       </c>
-      <c r="C30" s="7" t="n">
+      <c r="C30" s="25" t="n">
         <v>26.76</v>
       </c>
-      <c r="D30" s="19">
+      <c r="D30" s="32">
         <f>IFERROR(B30/C30,"")</f>
         <v/>
       </c>
@@ -1589,16 +1603,16 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="18" t="n">
+      <c r="A31" s="31" t="n">
         <v>45199</v>
       </c>
-      <c r="B31" s="6" t="n">
+      <c r="B31" s="24" t="n">
         <v>16391.8</v>
       </c>
-      <c r="C31" s="7" t="n">
+      <c r="C31" s="25" t="n">
         <v>27.54</v>
       </c>
-      <c r="D31" s="19">
+      <c r="D31" s="32">
         <f>IFERROR(B31/C31,"")</f>
         <v/>
       </c>
@@ -1608,16 +1622,16 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="18" t="n">
+      <c r="A32" s="31" t="n">
         <v>45230</v>
       </c>
-      <c r="B32" s="6" t="n">
+      <c r="B32" s="24" t="n">
         <v>16114.9</v>
       </c>
-      <c r="C32" s="7" t="n">
+      <c r="C32" s="25" t="n">
         <v>26.86</v>
       </c>
-      <c r="D32" s="19">
+      <c r="D32" s="32">
         <f>IFERROR(B32/C32,"")</f>
         <v/>
       </c>
@@ -1627,16 +1641,16 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="18" t="n">
+      <c r="A33" s="31" t="n">
         <v>45260</v>
       </c>
-      <c r="B33" s="6" t="n">
+      <c r="B33" s="24" t="n">
         <v>17185.2</v>
       </c>
-      <c r="C33" s="7" t="n">
+      <c r="C33" s="25" t="n">
         <v>28.06</v>
       </c>
-      <c r="D33" s="19">
+      <c r="D33" s="32">
         <f>IFERROR(B33/C33,"")</f>
         <v/>
       </c>
@@ -1646,16 +1660,16 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="18" t="n">
+      <c r="A34" s="31" t="n">
         <v>45291</v>
       </c>
-      <c r="B34" s="6" t="n">
+      <c r="B34" s="24" t="n">
         <v>18453.1</v>
       </c>
-      <c r="C34" s="7" t="n">
+      <c r="C34" s="25" t="n">
         <v>32.97</v>
       </c>
-      <c r="D34" s="19">
+      <c r="D34" s="32">
         <f>IFERROR(B34/C34,"")</f>
         <v/>
       </c>
@@ -1665,16 +1679,16 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="18" t="n">
+      <c r="A35" s="31" t="n">
         <v>45322</v>
       </c>
-      <c r="B35" s="6" t="n">
+      <c r="B35" s="24" t="n">
         <v>18503.25</v>
       </c>
-      <c r="C35" s="7" t="n">
+      <c r="C35" s="25" t="n">
         <v>32.69</v>
       </c>
-      <c r="D35" s="19">
+      <c r="D35" s="32">
         <f>IFERROR(B35/C35,"")</f>
         <v/>
       </c>
@@ -1684,16 +1698,16 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="18" t="n">
+      <c r="A36" s="31" t="n">
         <v>45351</v>
       </c>
-      <c r="B36" s="6" t="n">
+      <c r="B36" s="24" t="n">
         <v>18668.55</v>
       </c>
-      <c r="C36" s="7" t="n">
+      <c r="C36" s="25" t="n">
         <v>32.68</v>
       </c>
-      <c r="D36" s="19">
+      <c r="D36" s="32">
         <f>IFERROR(B36/C36,"")</f>
         <v/>
       </c>
@@ -1703,16 +1717,16 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="18" t="n">
+      <c r="A37" s="31" t="n">
         <v>45382</v>
       </c>
-      <c r="B37" s="6" t="n">
+      <c r="B37" s="24" t="n">
         <v>18598.05</v>
       </c>
-      <c r="C37" s="7" t="n">
+      <c r="C37" s="25" t="n">
         <v>32.57</v>
       </c>
-      <c r="D37" s="19">
+      <c r="D37" s="32">
         <f>IFERROR(B37/C37,"")</f>
         <v/>
       </c>
@@ -1722,16 +1736,16 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="18" t="n">
+      <c r="A38" s="31" t="n">
         <v>45412</v>
       </c>
-      <c r="B38" s="6" t="n">
+      <c r="B38" s="24" t="n">
         <v>18755.95</v>
       </c>
-      <c r="C38" s="7" t="n">
+      <c r="C38" s="25" t="n">
         <v>32.63</v>
       </c>
-      <c r="D38" s="19">
+      <c r="D38" s="32">
         <f>IFERROR(B38/C38,"")</f>
         <v/>
       </c>
@@ -1741,16 +1755,16 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="18" t="n">
+      <c r="A39" s="31" t="n">
         <v>45443</v>
       </c>
-      <c r="B39" s="6" t="n">
+      <c r="B39" s="24" t="n">
         <v>19451</v>
       </c>
-      <c r="C39" s="7" t="n">
+      <c r="C39" s="25" t="n">
         <v>32.51</v>
       </c>
-      <c r="D39" s="19">
+      <c r="D39" s="32">
         <f>IFERROR(B39/C39,"")</f>
         <v/>
       </c>
@@ -1760,16 +1774,16 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="18" t="n">
+      <c r="A40" s="31" t="n">
         <v>45473</v>
       </c>
-      <c r="B40" s="6" t="n">
+      <c r="B40" s="24" t="n">
         <v>20682.5</v>
       </c>
-      <c r="C40" s="7" t="n">
+      <c r="C40" s="25" t="n">
         <v>35.08</v>
       </c>
-      <c r="D40" s="19">
+      <c r="D40" s="32">
         <f>IFERROR(B40/C40,"")</f>
         <v/>
       </c>
@@ -1779,16 +1793,16 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="18" t="n">
+      <c r="A41" s="31" t="n">
         <v>45504</v>
       </c>
-      <c r="B41" s="6" t="n">
+      <c r="B41" s="24" t="n">
         <v>22273</v>
       </c>
-      <c r="C41" s="7" t="n">
+      <c r="C41" s="25" t="n">
         <v>37.25</v>
       </c>
-      <c r="D41" s="19">
+      <c r="D41" s="32">
         <f>IFERROR(B41/C41,"")</f>
         <v/>
       </c>
@@ -1798,16 +1812,16 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="18" t="n">
+      <c r="A42" s="31" t="n">
         <v>45535</v>
       </c>
-      <c r="B42" s="6" t="n">
+      <c r="B42" s="24" t="n">
         <v>22807.2</v>
       </c>
-      <c r="C42" s="7" t="n">
+      <c r="C42" s="25" t="n">
         <v>37.18</v>
       </c>
-      <c r="D42" s="19">
+      <c r="D42" s="32">
         <f>IFERROR(B42/C42,"")</f>
         <v/>
       </c>
@@ -1817,16 +1831,16 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="18" t="n">
+      <c r="A43" s="31" t="n">
         <v>45565</v>
       </c>
-      <c r="B43" s="6" t="n">
+      <c r="B43" s="24" t="n">
         <v>23336.15</v>
       </c>
-      <c r="C43" s="7" t="n">
+      <c r="C43" s="25" t="n">
         <v>38.05</v>
       </c>
-      <c r="D43" s="19">
+      <c r="D43" s="32">
         <f>IFERROR(B43/C43,"")</f>
         <v/>
       </c>
@@ -1836,16 +1850,16 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="18" t="n">
+      <c r="A44" s="31" t="n">
         <v>45596</v>
       </c>
-      <c r="B44" s="6" t="n">
+      <c r="B44" s="24" t="n">
         <v>21303.7</v>
       </c>
-      <c r="C44" s="7" t="n">
+      <c r="C44" s="25" t="n">
         <v>34.41</v>
       </c>
-      <c r="D44" s="19">
+      <c r="D44" s="32">
         <f>IFERROR(B44/C44,"")</f>
         <v/>
       </c>
@@ -1855,16 +1869,16 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="18" t="n">
+      <c r="A45" s="31" t="n">
         <v>45626</v>
       </c>
-      <c r="B45" s="6" t="n">
+      <c r="B45" s="24" t="n">
         <v>21263.25</v>
       </c>
-      <c r="C45" s="7" t="n">
+      <c r="C45" s="25" t="n">
         <v>34.31</v>
       </c>
-      <c r="D45" s="19">
+      <c r="D45" s="32">
         <f>IFERROR(B45/C45,"")</f>
         <v/>
       </c>
@@ -1874,16 +1888,16 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="18" t="n">
+      <c r="A46" s="31" t="n">
         <v>45657</v>
       </c>
-      <c r="B46" s="6" t="n">
+      <c r="B46" s="24" t="n">
         <v>20799.2</v>
       </c>
-      <c r="C46" s="7" t="n">
+      <c r="C46" s="25" t="n">
         <v>30.56</v>
       </c>
-      <c r="D46" s="19">
+      <c r="D46" s="32">
         <f>IFERROR(B46/C46,"")</f>
         <v/>
       </c>
@@ -1893,16 +1907,16 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="18" t="n">
+      <c r="A47" s="31" t="n">
         <v>45688</v>
       </c>
-      <c r="B47" s="6" t="n">
+      <c r="B47" s="24" t="n">
         <v>20475.05</v>
       </c>
-      <c r="C47" s="7" t="n">
+      <c r="C47" s="25" t="n">
         <v>29.93</v>
       </c>
-      <c r="D47" s="19">
+      <c r="D47" s="32">
         <f>IFERROR(B47/C47,"")</f>
         <v/>
       </c>
@@ -1912,16 +1926,16 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="18" t="n">
+      <c r="A48" s="31" t="n">
         <v>45716</v>
       </c>
-      <c r="B48" s="6" t="n">
+      <c r="B48" s="24" t="n">
         <v>18158.8</v>
       </c>
-      <c r="C48" s="7" t="n">
+      <c r="C48" s="25" t="n">
         <v>26.45</v>
       </c>
-      <c r="D48" s="19">
+      <c r="D48" s="32">
         <f>IFERROR(B48/C48,"")</f>
         <v/>
       </c>
@@ -1931,16 +1945,16 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="18" t="n">
+      <c r="A49" s="31" t="n">
         <v>45747</v>
       </c>
-      <c r="B49" s="6" t="n">
+      <c r="B49" s="24" t="n">
         <v>19187.1</v>
       </c>
-      <c r="C49" s="7" t="n">
+      <c r="C49" s="25" t="n">
         <v>27.95</v>
       </c>
-      <c r="D49" s="19">
+      <c r="D49" s="32">
         <f>IFERROR(B49/C49,"")</f>
         <v/>
       </c>
@@ -1950,16 +1964,16 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="18" t="n">
+      <c r="A50" s="31" t="n">
         <v>45777</v>
       </c>
-      <c r="B50" s="6" t="n">
+      <c r="B50" s="24" t="n">
         <v>19791.95</v>
       </c>
-      <c r="C50" s="7" t="n">
+      <c r="C50" s="25" t="n">
         <v>28.74</v>
       </c>
-      <c r="D50" s="19">
+      <c r="D50" s="32">
         <f>IFERROR(B50/C50,"")</f>
         <v/>
       </c>
@@ -1969,16 +1983,16 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="18" t="n">
+      <c r="A51" s="31" t="n">
         <v>45808</v>
       </c>
-      <c r="B51" s="6" t="n">
+      <c r="B51" s="24" t="n">
         <v>20532.1</v>
       </c>
-      <c r="C51" s="7" t="n">
+      <c r="C51" s="25" t="n">
         <v>29.65</v>
       </c>
-      <c r="D51" s="19">
+      <c r="D51" s="32">
         <f>IFERROR(B51/C51,"")</f>
         <v/>
       </c>
@@ -1988,16 +2002,16 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="18" t="n">
+      <c r="A52" s="31" t="n">
         <v>45838</v>
       </c>
-      <c r="B52" s="6" t="n">
+      <c r="B52" s="24" t="n">
         <v>21025.4</v>
       </c>
-      <c r="C52" s="7" t="n">
+      <c r="C52" s="25" t="n">
         <v>29.56</v>
       </c>
-      <c r="D52" s="19">
+      <c r="D52" s="32">
         <f>IFERROR(B52/C52,"")</f>
         <v/>
       </c>
@@ -2007,16 +2021,16 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="18" t="n">
+      <c r="A53" s="31" t="n">
         <v>45869</v>
       </c>
-      <c r="B53" s="6" t="n">
+      <c r="B53" s="24" t="n">
         <v>20203.55</v>
       </c>
-      <c r="C53" s="7" t="n">
+      <c r="C53" s="25" t="n">
         <v>28.33</v>
       </c>
-      <c r="D53" s="19">
+      <c r="D53" s="32">
         <f>IFERROR(B53/C53,"")</f>
         <v/>
       </c>
@@ -2026,16 +2040,16 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="18" t="n">
+      <c r="A54" s="31" t="n">
         <v>45900</v>
       </c>
-      <c r="B54" s="6" t="n">
+      <c r="B54" s="24" t="n">
         <v>20377.05</v>
       </c>
-      <c r="C54" s="7" t="n">
+      <c r="C54" s="25" t="n">
         <v>27.99</v>
       </c>
-      <c r="D54" s="19">
+      <c r="D54" s="32">
         <f>IFERROR(B54/C54,"")</f>
         <v/>
       </c>
@@ -2045,16 +2059,16 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="18" t="n">
+      <c r="A55" s="31" t="n">
         <v>45930</v>
       </c>
-      <c r="B55" s="6" t="n">
+      <c r="B55" s="24" t="n">
         <v>20338.8</v>
       </c>
-      <c r="C55" s="7" t="n">
+      <c r="C55" s="25" t="n">
         <v>27.94</v>
       </c>
-      <c r="D55" s="19">
+      <c r="D55" s="32">
         <f>IFERROR(B55/C55,"")</f>
         <v/>
       </c>
@@ -2064,16 +2078,16 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="18" t="n">
+      <c r="A56" s="31" t="n">
         <v>45961</v>
       </c>
-      <c r="B56" s="6" t="n">
+      <c r="B56" s="24" t="n">
         <v>21091.25</v>
       </c>
-      <c r="C56" s="7" t="n">
+      <c r="C56" s="25" t="n">
         <v>29.16</v>
       </c>
-      <c r="D56" s="19">
+      <c r="D56" s="32">
         <f>IFERROR(B56/C56,"")</f>
         <v/>
       </c>
@@ -2083,16 +2097,16 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="18" t="n">
+      <c r="A57" s="31" t="n">
         <v>45991</v>
       </c>
-      <c r="B57" s="6" t="n">
+      <c r="B57" s="24" t="n">
         <v>21332.4</v>
       </c>
-      <c r="C57" s="7" t="n">
+      <c r="C57" s="25" t="n">
         <v>28.48</v>
       </c>
-      <c r="D57" s="19">
+      <c r="D57" s="32">
         <f>IFERROR(B57/C57,"")</f>
         <v/>
       </c>
@@ -2102,16 +2116,16 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="18" t="n">
+      <c r="A58" s="31" t="n">
         <v>46022</v>
       </c>
-      <c r="B58" s="6" t="n">
+      <c r="B58" s="24" t="n">
         <v>21410.85</v>
       </c>
-      <c r="C58" s="7" t="n">
+      <c r="C58" s="25" t="n">
         <v>33.02</v>
       </c>
-      <c r="D58" s="19">
+      <c r="D58" s="32">
         <f>IFERROR(B58/C58,"")</f>
         <v/>
       </c>
@@ -2121,16 +2135,16 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="18" t="n">
+      <c r="A59" s="31" t="n">
         <v>46053</v>
       </c>
-      <c r="B59" s="6" t="n">
+      <c r="B59" s="24" t="n">
         <v>21005.25</v>
       </c>
-      <c r="C59" s="7" t="n">
+      <c r="C59" s="25" t="n">
         <v>32.29</v>
       </c>
-      <c r="D59" s="19">
+      <c r="D59" s="32">
         <f>IFERROR(B59/C59,"")</f>
         <v/>
       </c>
@@ -2140,16 +2154,16 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="18" t="n">
+      <c r="A60" s="31" t="n">
         <v>46081</v>
       </c>
-      <c r="B60" s="6" t="n">
+      <c r="B60" s="24" t="n">
         <v>20146.8</v>
       </c>
-      <c r="C60" s="7" t="n">
+      <c r="C60" s="25" t="n">
         <v>30.9</v>
       </c>
-      <c r="D60" s="19">
+      <c r="D60" s="32">
         <f>IFERROR(B60/C60,"")</f>
         <v/>
       </c>
@@ -2159,16 +2173,16 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="18" t="n">
+      <c r="A61" s="31" t="n">
         <v>46112</v>
       </c>
-      <c r="B61" s="6" t="n">
+      <c r="B61" s="24" t="n">
         <v>18207</v>
       </c>
-      <c r="C61" s="7" t="n">
+      <c r="C61" s="25" t="n">
         <v>27.93</v>
       </c>
-      <c r="D61" s="19">
+      <c r="D61" s="32">
         <f>IFERROR(B61/C61,"")</f>
         <v/>
       </c>
@@ -2178,16 +2192,16 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="18" t="n">
+      <c r="A62" s="31" t="n">
         <v>46142</v>
       </c>
-      <c r="B62" s="6" t="n">
+      <c r="B62" s="24" t="n">
         <v>20153.9</v>
       </c>
-      <c r="C62" s="7" t="n">
+      <c r="C62" s="25" t="n">
         <v>30.06</v>
       </c>
-      <c r="D62" s="19">
+      <c r="D62" s="32">
         <f>IFERROR(B62/C62,"")</f>
         <v/>
       </c>
@@ -2197,16 +2211,16 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="18" t="n">
+      <c r="A63" s="31" t="n">
         <v>46173</v>
       </c>
-      <c r="B63" s="6" t="n">
+      <c r="B63" s="24" t="n">
         <v>20112</v>
       </c>
-      <c r="C63" s="7" t="n">
+      <c r="C63" s="25" t="n">
         <v>29.48</v>
       </c>
-      <c r="D63" s="19">
+      <c r="D63" s="32">
         <f>IFERROR(B63/C63,"")</f>
         <v/>
       </c>
@@ -2216,16 +2230,16 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="18" t="n">
+      <c r="A64" s="31" t="n">
         <v>46203</v>
       </c>
-      <c r="B64" s="6" t="n">
+      <c r="B64" s="24" t="n">
         <v>19561.4</v>
       </c>
-      <c r="C64" s="7" t="n">
+      <c r="C64" s="25" t="n">
         <v>27.55</v>
       </c>
-      <c r="D64" s="19">
+      <c r="D64" s="32">
         <f>IFERROR(B64/C64,"")</f>
         <v/>
       </c>
@@ -2235,16 +2249,16 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="18" t="n">
+      <c r="A65" s="31" t="n">
         <v>46234</v>
       </c>
-      <c r="B65" s="6" t="n">
+      <c r="B65" s="24" t="n">
         <v>20613.65</v>
       </c>
-      <c r="C65" s="7" t="n">
+      <c r="C65" s="25" t="n">
         <v>28.17</v>
       </c>
-      <c r="D65" s="19">
+      <c r="D65" s="32">
         <f>IFERROR(B65/C65,"")</f>
         <v/>
       </c>
@@ -2254,16 +2268,16 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="18" t="n">
+      <c r="A66" s="31" t="n">
         <v>46265</v>
       </c>
-      <c r="B66" s="6" t="n">
+      <c r="B66" s="24" t="n">
         <v>20579.35</v>
       </c>
-      <c r="C66" s="7" t="n">
+      <c r="C66" s="25" t="n">
         <v>27.89</v>
       </c>
-      <c r="D66" s="19">
+      <c r="D66" s="32">
         <f>IFERROR(B66/C66,"")</f>
         <v/>
       </c>
@@ -2365,13 +2379,13 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="18" t="n">
+      <c r="A2" s="31" t="n">
         <v>43281</v>
       </c>
-      <c r="B2" s="6" t="n">
+      <c r="B2" s="24" t="n">
         <v>9337.639999999999</v>
       </c>
-      <c r="C2" s="7" t="n">
+      <c r="C2" s="25" t="n">
         <v>29.27</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -2379,12 +2393,12 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E2" s="21">
+      <c r="E2" s="33">
         <f>IFERROR(B2/C2,"")</f>
         <v/>
       </c>
-      <c r="F2" s="16" t="n"/>
-      <c r="G2" s="16">
+      <c r="F2" s="30" t="n"/>
+      <c r="G2" s="30">
         <f>IF(C2="","",(COUNTIFS($D$2:$D$34,D2,$C$2:$C$34,"&gt;0",$C$2:$C$34,"&lt;"&amp;C2)+(COUNTIFS($D$2:$D$34,D2,$C$2:$C$34,C2)+1)/2)/COUNTIFS($D$2:$D$34,D2,$C$2:$C$34,"&gt;0"))</f>
         <v/>
       </c>
@@ -2392,28 +2406,28 @@
         <f>IF(G2="","",IF(G2&lt;=20%,"Q1 Cheapest",IF(G2&lt;=40%,"Q2",IF(G2&lt;=60%,"Q3",IF(G2&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I2" s="16">
+      <c r="I2" s="30">
         <f>IFERROR(B6/B2-1,"")</f>
         <v/>
       </c>
-      <c r="J2" s="16">
+      <c r="J2" s="30">
         <f>IFERROR((B14/B2)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K2" s="16">
+      <c r="K2" s="30">
         <f>IFERROR((B22/B2)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L2" s="16" t="n"/>
+      <c r="L2" s="30" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="18" t="n">
+      <c r="A3" s="31" t="n">
         <v>43373</v>
       </c>
-      <c r="B3" s="6" t="n">
+      <c r="B3" s="24" t="n">
         <v>9418.17</v>
       </c>
-      <c r="C3" s="7" t="n">
+      <c r="C3" s="25" t="n">
         <v>31.21</v>
       </c>
       <c r="D3" s="2" t="inlineStr">
@@ -2421,12 +2435,12 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E3" s="21">
+      <c r="E3" s="33">
         <f>IFERROR(B3/C3,"")</f>
         <v/>
       </c>
-      <c r="F3" s="16" t="n"/>
-      <c r="G3" s="16">
+      <c r="F3" s="30" t="n"/>
+      <c r="G3" s="30">
         <f>IF(C3="","",(COUNTIFS($D$2:$D$34,D3,$C$2:$C$34,"&gt;0",$C$2:$C$34,"&lt;"&amp;C3)+(COUNTIFS($D$2:$D$34,D3,$C$2:$C$34,C3)+1)/2)/COUNTIFS($D$2:$D$34,D3,$C$2:$C$34,"&gt;0"))</f>
         <v/>
       </c>
@@ -2434,28 +2448,28 @@
         <f>IF(G3="","",IF(G3&lt;=20%,"Q1 Cheapest",IF(G3&lt;=40%,"Q2",IF(G3&lt;=60%,"Q3",IF(G3&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I3" s="16">
+      <c r="I3" s="30">
         <f>IFERROR(B7/B3-1,"")</f>
         <v/>
       </c>
-      <c r="J3" s="16">
+      <c r="J3" s="30">
         <f>IFERROR((B15/B3)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K3" s="16">
+      <c r="K3" s="30">
         <f>IFERROR((B23/B3)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L3" s="16" t="n"/>
+      <c r="L3" s="30" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="18" t="n">
+      <c r="A4" s="31" t="n">
         <v>43465</v>
       </c>
-      <c r="B4" s="6" t="n">
+      <c r="B4" s="24" t="n">
         <v>9482.629999999999</v>
       </c>
-      <c r="C4" s="7" t="n">
+      <c r="C4" s="25" t="n">
         <v>30.8</v>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -2463,12 +2477,12 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E4" s="21">
+      <c r="E4" s="33">
         <f>IFERROR(B4/C4,"")</f>
         <v/>
       </c>
-      <c r="F4" s="16" t="n"/>
-      <c r="G4" s="16">
+      <c r="F4" s="30" t="n"/>
+      <c r="G4" s="30">
         <f>IF(C4="","",(COUNTIFS($D$2:$D$34,D4,$C$2:$C$34,"&gt;0",$C$2:$C$34,"&lt;"&amp;C4)+(COUNTIFS($D$2:$D$34,D4,$C$2:$C$34,C4)+1)/2)/COUNTIFS($D$2:$D$34,D4,$C$2:$C$34,"&gt;0"))</f>
         <v/>
       </c>
@@ -2476,28 +2490,28 @@
         <f>IF(G4="","",IF(G4&lt;=20%,"Q1 Cheapest",IF(G4&lt;=40%,"Q2",IF(G4&lt;=60%,"Q3",IF(G4&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I4" s="16">
+      <c r="I4" s="30">
         <f>IFERROR(B8/B4-1,"")</f>
         <v/>
       </c>
-      <c r="J4" s="16">
+      <c r="J4" s="30">
         <f>IFERROR((B16/B4)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K4" s="16">
+      <c r="K4" s="30">
         <f>IFERROR((B24/B4)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L4" s="16" t="n"/>
+      <c r="L4" s="30" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="18" t="n">
+      <c r="A5" s="31" t="n">
         <v>43555</v>
       </c>
-      <c r="B5" s="6" t="n">
+      <c r="B5" s="24" t="n">
         <v>9684.700000000001</v>
       </c>
-      <c r="C5" s="7" t="n">
+      <c r="C5" s="25" t="n">
         <v>29.38</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -2505,12 +2519,12 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E5" s="21">
+      <c r="E5" s="33">
         <f>IFERROR(B5/C5,"")</f>
         <v/>
       </c>
-      <c r="F5" s="16" t="n"/>
-      <c r="G5" s="16">
+      <c r="F5" s="30" t="n"/>
+      <c r="G5" s="30">
         <f>IF(C5="","",(COUNTIFS($D$2:$D$34,D5,$C$2:$C$34,"&gt;0",$C$2:$C$34,"&lt;"&amp;C5)+(COUNTIFS($D$2:$D$34,D5,$C$2:$C$34,C5)+1)/2)/COUNTIFS($D$2:$D$34,D5,$C$2:$C$34,"&gt;0"))</f>
         <v/>
       </c>
@@ -2518,28 +2532,28 @@
         <f>IF(G5="","",IF(G5&lt;=20%,"Q1 Cheapest",IF(G5&lt;=40%,"Q2",IF(G5&lt;=60%,"Q3",IF(G5&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I5" s="16">
+      <c r="I5" s="30">
         <f>IFERROR(B9/B5-1,"")</f>
         <v/>
       </c>
-      <c r="J5" s="16">
+      <c r="J5" s="30">
         <f>IFERROR((B17/B5)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K5" s="16">
+      <c r="K5" s="30">
         <f>IFERROR((B25/B5)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L5" s="16" t="n"/>
+      <c r="L5" s="30" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="18" t="n">
+      <c r="A6" s="31" t="n">
         <v>43646</v>
       </c>
-      <c r="B6" s="6" t="n">
+      <c r="B6" s="24" t="n">
         <v>9496.25</v>
       </c>
-      <c r="C6" s="7" t="n">
+      <c r="C6" s="25" t="n">
         <v>24.96</v>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -2547,15 +2561,15 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E6" s="21">
+      <c r="E6" s="33">
         <f>IFERROR(B6/C6,"")</f>
         <v/>
       </c>
-      <c r="F6" s="16">
+      <c r="F6" s="30">
         <f>IF(AND(D6=D2,E2&lt;&gt;""),E6/E2-1,"")</f>
         <v/>
       </c>
-      <c r="G6" s="16">
+      <c r="G6" s="30">
         <f>IF(C6="","",(COUNTIFS($D$2:$D$34,D6,$C$2:$C$34,"&gt;0",$C$2:$C$34,"&lt;"&amp;C6)+(COUNTIFS($D$2:$D$34,D6,$C$2:$C$34,C6)+1)/2)/COUNTIFS($D$2:$D$34,D6,$C$2:$C$34,"&gt;0"))</f>
         <v/>
       </c>
@@ -2563,28 +2577,28 @@
         <f>IF(G6="","",IF(G6&lt;=20%,"Q1 Cheapest",IF(G6&lt;=40%,"Q2",IF(G6&lt;=60%,"Q3",IF(G6&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I6" s="16">
+      <c r="I6" s="30">
         <f>IFERROR(B10/B6-1,"")</f>
         <v/>
       </c>
-      <c r="J6" s="16">
+      <c r="J6" s="30">
         <f>IFERROR((B18/B6)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K6" s="16">
+      <c r="K6" s="30">
         <f>IFERROR((B26/B6)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L6" s="16" t="n"/>
+      <c r="L6" s="30" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="18" t="n">
+      <c r="A7" s="31" t="n">
         <v>43738</v>
       </c>
-      <c r="B7" s="6" t="n">
+      <c r="B7" s="24" t="n">
         <v>9739.35</v>
       </c>
-      <c r="C7" s="7" t="n">
+      <c r="C7" s="25" t="n">
         <v>25.39</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -2592,15 +2606,15 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E7" s="21">
+      <c r="E7" s="33">
         <f>IFERROR(B7/C7,"")</f>
         <v/>
       </c>
-      <c r="F7" s="16">
+      <c r="F7" s="30">
         <f>IF(AND(D7=D3,E3&lt;&gt;""),E7/E3-1,"")</f>
         <v/>
       </c>
-      <c r="G7" s="16">
+      <c r="G7" s="30">
         <f>IF(C7="","",(COUNTIFS($D$2:$D$34,D7,$C$2:$C$34,"&gt;0",$C$2:$C$34,"&lt;"&amp;C7)+(COUNTIFS($D$2:$D$34,D7,$C$2:$C$34,C7)+1)/2)/COUNTIFS($D$2:$D$34,D7,$C$2:$C$34,"&gt;0"))</f>
         <v/>
       </c>
@@ -2608,28 +2622,28 @@
         <f>IF(G7="","",IF(G7&lt;=20%,"Q1 Cheapest",IF(G7&lt;=40%,"Q2",IF(G7&lt;=60%,"Q3",IF(G7&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I7" s="16">
+      <c r="I7" s="30">
         <f>IFERROR(B11/B7-1,"")</f>
         <v/>
       </c>
-      <c r="J7" s="16">
+      <c r="J7" s="30">
         <f>IFERROR((B19/B7)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K7" s="16">
+      <c r="K7" s="30">
         <f>IFERROR((B27/B7)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L7" s="16" t="n"/>
+      <c r="L7" s="30" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="18" t="n">
+      <c r="A8" s="31" t="n">
         <v>43830</v>
       </c>
-      <c r="B8" s="6" t="n">
+      <c r="B8" s="24" t="n">
         <v>9853.35</v>
       </c>
-      <c r="C8" s="7" t="n">
+      <c r="C8" s="25" t="n">
         <v>26.19</v>
       </c>
       <c r="D8" s="2" t="inlineStr">
@@ -2637,15 +2651,15 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E8" s="21">
+      <c r="E8" s="33">
         <f>IFERROR(B8/C8,"")</f>
         <v/>
       </c>
-      <c r="F8" s="16">
+      <c r="F8" s="30">
         <f>IF(AND(D8=D4,E4&lt;&gt;""),E8/E4-1,"")</f>
         <v/>
       </c>
-      <c r="G8" s="16">
+      <c r="G8" s="30">
         <f>IF(C8="","",(COUNTIFS($D$2:$D$34,D8,$C$2:$C$34,"&gt;0",$C$2:$C$34,"&lt;"&amp;C8)+(COUNTIFS($D$2:$D$34,D8,$C$2:$C$34,C8)+1)/2)/COUNTIFS($D$2:$D$34,D8,$C$2:$C$34,"&gt;0"))</f>
         <v/>
       </c>
@@ -2653,28 +2667,28 @@
         <f>IF(G8="","",IF(G8&lt;=20%,"Q1 Cheapest",IF(G8&lt;=40%,"Q2",IF(G8&lt;=60%,"Q3",IF(G8&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I8" s="16">
+      <c r="I8" s="30">
         <f>IFERROR(B12/B8-1,"")</f>
         <v/>
       </c>
-      <c r="J8" s="16">
+      <c r="J8" s="30">
         <f>IFERROR((B20/B8)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K8" s="16">
+      <c r="K8" s="30">
         <f>IFERROR((B28/B8)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L8" s="16" t="n"/>
+      <c r="L8" s="30" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="18" t="n">
+      <c r="A9" s="31" t="n">
         <v>43921</v>
       </c>
-      <c r="B9" s="6" t="n">
+      <c r="B9" s="24" t="n">
         <v>8042.1</v>
       </c>
-      <c r="C9" s="7" t="n">
+      <c r="C9" s="25" t="n">
         <v>22.62</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -2682,15 +2696,15 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E9" s="21">
+      <c r="E9" s="33">
         <f>IFERROR(B9/C9,"")</f>
         <v/>
       </c>
-      <c r="F9" s="16">
+      <c r="F9" s="30">
         <f>IF(AND(D9=D5,E5&lt;&gt;""),E9/E5-1,"")</f>
         <v/>
       </c>
-      <c r="G9" s="16">
+      <c r="G9" s="30">
         <f>IF(C9="","",(COUNTIFS($D$2:$D$34,D9,$C$2:$C$34,"&gt;0",$C$2:$C$34,"&lt;"&amp;C9)+(COUNTIFS($D$2:$D$34,D9,$C$2:$C$34,C9)+1)/2)/COUNTIFS($D$2:$D$34,D9,$C$2:$C$34,"&gt;0"))</f>
         <v/>
       </c>
@@ -2698,28 +2712,28 @@
         <f>IF(G9="","",IF(G9&lt;=20%,"Q1 Cheapest",IF(G9&lt;=40%,"Q2",IF(G9&lt;=60%,"Q3",IF(G9&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I9" s="16">
+      <c r="I9" s="30">
         <f>IFERROR(B13/B9-1,"")</f>
         <v/>
       </c>
-      <c r="J9" s="16">
+      <c r="J9" s="30">
         <f>IFERROR((B21/B9)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K9" s="16">
+      <c r="K9" s="30">
         <f>IFERROR((B29/B9)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L9" s="16" t="n"/>
+      <c r="L9" s="30" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="18" t="n">
+      <c r="A10" s="31" t="n">
         <v>44012</v>
       </c>
-      <c r="B10" s="6" t="n">
+      <c r="B10" s="24" t="n">
         <v>9253.450000000001</v>
       </c>
-      <c r="C10" s="7" t="n">
+      <c r="C10" s="25" t="n">
         <v>23.19</v>
       </c>
       <c r="D10" s="2" t="inlineStr">
@@ -2727,15 +2741,15 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E10" s="21">
+      <c r="E10" s="33">
         <f>IFERROR(B10/C10,"")</f>
         <v/>
       </c>
-      <c r="F10" s="16">
+      <c r="F10" s="30">
         <f>IF(AND(D10=D6,E6&lt;&gt;""),E10/E6-1,"")</f>
         <v/>
       </c>
-      <c r="G10" s="16">
+      <c r="G10" s="30">
         <f>IF(C10="","",(COUNTIFS($D$2:$D$34,D10,$C$2:$C$34,"&gt;0",$C$2:$C$34,"&lt;"&amp;C10)+(COUNTIFS($D$2:$D$34,D10,$C$2:$C$34,C10)+1)/2)/COUNTIFS($D$2:$D$34,D10,$C$2:$C$34,"&gt;0"))</f>
         <v/>
       </c>
@@ -2743,28 +2757,28 @@
         <f>IF(G10="","",IF(G10&lt;=20%,"Q1 Cheapest",IF(G10&lt;=40%,"Q2",IF(G10&lt;=60%,"Q3",IF(G10&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I10" s="16">
+      <c r="I10" s="30">
         <f>IFERROR(B14/B10-1,"")</f>
         <v/>
       </c>
-      <c r="J10" s="16">
+      <c r="J10" s="30">
         <f>IFERROR((B22/B10)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K10" s="16">
+      <c r="K10" s="30">
         <f>IFERROR((B30/B10)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L10" s="16" t="n"/>
+      <c r="L10" s="30" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="18" t="n">
+      <c r="A11" s="31" t="n">
         <v>44104</v>
       </c>
-      <c r="B11" s="6" t="n">
+      <c r="B11" s="24" t="n">
         <v>10392.6</v>
       </c>
-      <c r="C11" s="7" t="n">
+      <c r="C11" s="25" t="n">
         <v>28.79</v>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -2772,15 +2786,15 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E11" s="21">
+      <c r="E11" s="33">
         <f>IFERROR(B11/C11,"")</f>
         <v/>
       </c>
-      <c r="F11" s="16">
+      <c r="F11" s="30">
         <f>IF(AND(D11=D7,E7&lt;&gt;""),E11/E7-1,"")</f>
         <v/>
       </c>
-      <c r="G11" s="16">
+      <c r="G11" s="30">
         <f>IF(C11="","",(COUNTIFS($D$2:$D$34,D11,$C$2:$C$34,"&gt;0",$C$2:$C$34,"&lt;"&amp;C11)+(COUNTIFS($D$2:$D$34,D11,$C$2:$C$34,C11)+1)/2)/COUNTIFS($D$2:$D$34,D11,$C$2:$C$34,"&gt;0"))</f>
         <v/>
       </c>
@@ -2788,28 +2802,28 @@
         <f>IF(G11="","",IF(G11&lt;=20%,"Q1 Cheapest",IF(G11&lt;=40%,"Q2",IF(G11&lt;=60%,"Q3",IF(G11&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I11" s="16">
+      <c r="I11" s="30">
         <f>IFERROR(B15/B11-1,"")</f>
         <v/>
       </c>
-      <c r="J11" s="16">
+      <c r="J11" s="30">
         <f>IFERROR((B23/B11)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K11" s="16">
+      <c r="K11" s="30">
         <f>IFERROR((B31/B11)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L11" s="16" t="n"/>
+      <c r="L11" s="30" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="18" t="n">
+      <c r="A12" s="31" t="n">
         <v>44196</v>
       </c>
-      <c r="B12" s="6" t="n">
+      <c r="B12" s="24" t="n">
         <v>12253.6</v>
       </c>
-      <c r="C12" s="7" t="n">
+      <c r="C12" s="25" t="n">
         <v>34.61</v>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -2817,15 +2831,15 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E12" s="21">
+      <c r="E12" s="33">
         <f>IFERROR(B12/C12,"")</f>
         <v/>
       </c>
-      <c r="F12" s="16">
+      <c r="F12" s="30">
         <f>IF(AND(D12=D8,E8&lt;&gt;""),E12/E8-1,"")</f>
         <v/>
       </c>
-      <c r="G12" s="16">
+      <c r="G12" s="30">
         <f>IF(C12="","",(COUNTIFS($D$2:$D$34,D12,$C$2:$C$34,"&gt;0",$C$2:$C$34,"&lt;"&amp;C12)+(COUNTIFS($D$2:$D$34,D12,$C$2:$C$34,C12)+1)/2)/COUNTIFS($D$2:$D$34,D12,$C$2:$C$34,"&gt;0"))</f>
         <v/>
       </c>
@@ -2833,28 +2847,28 @@
         <f>IF(G12="","",IF(G12&lt;=20%,"Q1 Cheapest",IF(G12&lt;=40%,"Q2",IF(G12&lt;=60%,"Q3",IF(G12&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I12" s="16">
+      <c r="I12" s="30">
         <f>IFERROR(B16/B12-1,"")</f>
         <v/>
       </c>
-      <c r="J12" s="16">
+      <c r="J12" s="30">
         <f>IFERROR((B24/B12)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K12" s="16">
+      <c r="K12" s="30">
         <f>IFERROR((B32/B12)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L12" s="16" t="n"/>
+      <c r="L12" s="30" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="18" t="n">
+      <c r="A13" s="31" t="n">
         <v>44286</v>
       </c>
-      <c r="B13" s="6" t="n">
+      <c r="B13" s="24" t="n">
         <v>12425.85</v>
       </c>
-      <c r="C13" s="7" t="n">
+      <c r="C13" s="25" t="n">
         <v>31.88</v>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -2862,15 +2876,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E13" s="21">
+      <c r="E13" s="33">
         <f>IFERROR(B13/C13,"")</f>
         <v/>
       </c>
-      <c r="F13" s="16">
+      <c r="F13" s="30">
         <f>IF(AND(D13=D9,E9&lt;&gt;""),E13/E9-1,"")</f>
         <v/>
       </c>
-      <c r="G13" s="16">
+      <c r="G13" s="30">
         <f>IF(C13="","",(COUNTIFS($D$2:$D$34,D13,$C$2:$C$34,"&gt;0",$C$2:$C$34,"&lt;"&amp;C13)+(COUNTIFS($D$2:$D$34,D13,$C$2:$C$34,C13)+1)/2)/COUNTIFS($D$2:$D$34,D13,$C$2:$C$34,"&gt;0"))</f>
         <v/>
       </c>
@@ -2878,28 +2892,28 @@
         <f>IF(G13="","",IF(G13&lt;=20%,"Q1 Cheapest",IF(G13&lt;=40%,"Q2",IF(G13&lt;=60%,"Q3",IF(G13&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I13" s="16">
+      <c r="I13" s="30">
         <f>IFERROR(B17/B13-1,"")</f>
         <v/>
       </c>
-      <c r="J13" s="16">
+      <c r="J13" s="30">
         <f>IFERROR((B25/B13)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K13" s="16">
+      <c r="K13" s="30">
         <f>IFERROR((B33/B13)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L13" s="16" t="n"/>
+      <c r="L13" s="30" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="18" t="n">
+      <c r="A14" s="31" t="n">
         <v>44377</v>
       </c>
-      <c r="B14" s="6" t="n">
+      <c r="B14" s="24" t="n">
         <v>13433.05</v>
       </c>
-      <c r="C14" s="7" t="n">
+      <c r="C14" s="25" t="n">
         <v>31.16</v>
       </c>
       <c r="D14" s="2" t="inlineStr">
@@ -2907,15 +2921,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E14" s="21">
+      <c r="E14" s="33">
         <f>IFERROR(B14/C14,"")</f>
         <v/>
       </c>
-      <c r="F14" s="16">
+      <c r="F14" s="30">
         <f>IF(AND(D14=D10,E10&lt;&gt;""),E14/E10-1,"")</f>
         <v/>
       </c>
-      <c r="G14" s="16">
+      <c r="G14" s="30">
         <f>IF(C14="","",(COUNTIFS($D$2:$D$34,D14,$C$2:$C$34,"&gt;0",$C$2:$C$34,"&lt;"&amp;C14)+(COUNTIFS($D$2:$D$34,D14,$C$2:$C$34,C14)+1)/2)/COUNTIFS($D$2:$D$34,D14,$C$2:$C$34,"&gt;0"))</f>
         <v/>
       </c>
@@ -2923,28 +2937,28 @@
         <f>IF(G14="","",IF(G14&lt;=20%,"Q1 Cheapest",IF(G14&lt;=40%,"Q2",IF(G14&lt;=60%,"Q3",IF(G14&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I14" s="16">
+      <c r="I14" s="30">
         <f>IFERROR(B18/B14-1,"")</f>
         <v/>
       </c>
-      <c r="J14" s="16">
+      <c r="J14" s="30">
         <f>IFERROR((B26/B14)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K14" s="16">
+      <c r="K14" s="30">
         <f>IFERROR((B34/B14)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L14" s="16" t="n"/>
+      <c r="L14" s="30" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="18" t="n">
+      <c r="A15" s="31" t="n">
         <v>44469</v>
       </c>
-      <c r="B15" s="6" t="n">
+      <c r="B15" s="24" t="n">
         <v>15076.2</v>
       </c>
-      <c r="C15" s="7" t="n">
+      <c r="C15" s="25" t="n">
         <v>32.31</v>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -2952,15 +2966,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E15" s="21">
+      <c r="E15" s="33">
         <f>IFERROR(B15/C15,"")</f>
         <v/>
       </c>
-      <c r="F15" s="16">
+      <c r="F15" s="30">
         <f>IF(AND(D15=D11,E11&lt;&gt;""),E15/E11-1,"")</f>
         <v/>
       </c>
-      <c r="G15" s="16">
+      <c r="G15" s="30">
         <f>IF(C15="","",(COUNTIFS($D$2:$D$34,D15,$C$2:$C$34,"&gt;0",$C$2:$C$34,"&lt;"&amp;C15)+(COUNTIFS($D$2:$D$34,D15,$C$2:$C$34,C15)+1)/2)/COUNTIFS($D$2:$D$34,D15,$C$2:$C$34,"&gt;0"))</f>
         <v/>
       </c>
@@ -2968,25 +2982,25 @@
         <f>IF(G15="","",IF(G15&lt;=20%,"Q1 Cheapest",IF(G15&lt;=40%,"Q2",IF(G15&lt;=60%,"Q3",IF(G15&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I15" s="16">
+      <c r="I15" s="30">
         <f>IFERROR(B19/B15-1,"")</f>
         <v/>
       </c>
-      <c r="J15" s="16">
+      <c r="J15" s="30">
         <f>IFERROR((B27/B15)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K15" s="16" t="n"/>
-      <c r="L15" s="16" t="n"/>
+      <c r="K15" s="30" t="n"/>
+      <c r="L15" s="30" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="18" t="n">
+      <c r="A16" s="31" t="n">
         <v>44561</v>
       </c>
-      <c r="B16" s="6" t="n">
+      <c r="B16" s="24" t="n">
         <v>15166</v>
       </c>
-      <c r="C16" s="7" t="n">
+      <c r="C16" s="25" t="n">
         <v>31.73</v>
       </c>
       <c r="D16" s="2" t="inlineStr">
@@ -2994,15 +3008,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E16" s="21">
+      <c r="E16" s="33">
         <f>IFERROR(B16/C16,"")</f>
         <v/>
       </c>
-      <c r="F16" s="16">
+      <c r="F16" s="30">
         <f>IF(AND(D16=D12,E12&lt;&gt;""),E16/E12-1,"")</f>
         <v/>
       </c>
-      <c r="G16" s="16">
+      <c r="G16" s="30">
         <f>IF(C16="","",(COUNTIFS($D$2:$D$34,D16,$C$2:$C$34,"&gt;0",$C$2:$C$34,"&lt;"&amp;C16)+(COUNTIFS($D$2:$D$34,D16,$C$2:$C$34,C16)+1)/2)/COUNTIFS($D$2:$D$34,D16,$C$2:$C$34,"&gt;0"))</f>
         <v/>
       </c>
@@ -3010,25 +3024,25 @@
         <f>IF(G16="","",IF(G16&lt;=20%,"Q1 Cheapest",IF(G16&lt;=40%,"Q2",IF(G16&lt;=60%,"Q3",IF(G16&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I16" s="16">
+      <c r="I16" s="30">
         <f>IFERROR(B20/B16-1,"")</f>
         <v/>
       </c>
-      <c r="J16" s="16">
+      <c r="J16" s="30">
         <f>IFERROR((B28/B16)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K16" s="16" t="n"/>
-      <c r="L16" s="16" t="n"/>
+      <c r="K16" s="30" t="n"/>
+      <c r="L16" s="30" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="18" t="n">
+      <c r="A17" s="31" t="n">
         <v>44651</v>
       </c>
-      <c r="B17" s="6" t="n">
+      <c r="B17" s="24" t="n">
         <v>14361.55</v>
       </c>
-      <c r="C17" s="7" t="n">
+      <c r="C17" s="25" t="n">
         <v>29.69</v>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -3036,15 +3050,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E17" s="21">
+      <c r="E17" s="33">
         <f>IFERROR(B17/C17,"")</f>
         <v/>
       </c>
-      <c r="F17" s="16">
+      <c r="F17" s="30">
         <f>IF(AND(D17=D13,E13&lt;&gt;""),E17/E13-1,"")</f>
         <v/>
       </c>
-      <c r="G17" s="16">
+      <c r="G17" s="30">
         <f>IF(C17="","",(COUNTIFS($D$2:$D$34,D17,$C$2:$C$34,"&gt;0",$C$2:$C$34,"&lt;"&amp;C17)+(COUNTIFS($D$2:$D$34,D17,$C$2:$C$34,C17)+1)/2)/COUNTIFS($D$2:$D$34,D17,$C$2:$C$34,"&gt;0"))</f>
         <v/>
       </c>
@@ -3052,25 +3066,25 @@
         <f>IF(G17="","",IF(G17&lt;=20%,"Q1 Cheapest",IF(G17&lt;=40%,"Q2",IF(G17&lt;=60%,"Q3",IF(G17&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I17" s="16">
+      <c r="I17" s="30">
         <f>IFERROR(B21/B17-1,"")</f>
         <v/>
       </c>
-      <c r="J17" s="16">
+      <c r="J17" s="30">
         <f>IFERROR((B29/B17)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K17" s="16" t="n"/>
-      <c r="L17" s="16" t="n"/>
+      <c r="K17" s="30" t="n"/>
+      <c r="L17" s="30" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="18" t="n">
+      <c r="A18" s="31" t="n">
         <v>44742</v>
       </c>
-      <c r="B18" s="6" t="n">
+      <c r="B18" s="24" t="n">
         <v>13077.95</v>
       </c>
-      <c r="C18" s="7" t="n">
+      <c r="C18" s="25" t="n">
         <v>27.04</v>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -3078,15 +3092,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E18" s="21">
+      <c r="E18" s="33">
         <f>IFERROR(B18/C18,"")</f>
         <v/>
       </c>
-      <c r="F18" s="16">
+      <c r="F18" s="30">
         <f>IF(AND(D18=D14,E14&lt;&gt;""),E18/E14-1,"")</f>
         <v/>
       </c>
-      <c r="G18" s="16">
+      <c r="G18" s="30">
         <f>IF(C18="","",(COUNTIFS($D$2:$D$34,D18,$C$2:$C$34,"&gt;0",$C$2:$C$34,"&lt;"&amp;C18)+(COUNTIFS($D$2:$D$34,D18,$C$2:$C$34,C18)+1)/2)/COUNTIFS($D$2:$D$34,D18,$C$2:$C$34,"&gt;0"))</f>
         <v/>
       </c>
@@ -3094,25 +3108,25 @@
         <f>IF(G18="","",IF(G18&lt;=20%,"Q1 Cheapest",IF(G18&lt;=40%,"Q2",IF(G18&lt;=60%,"Q3",IF(G18&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I18" s="16">
+      <c r="I18" s="30">
         <f>IFERROR(B22/B18-1,"")</f>
         <v/>
       </c>
-      <c r="J18" s="16">
+      <c r="J18" s="30">
         <f>IFERROR((B30/B18)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K18" s="16" t="n"/>
-      <c r="L18" s="16" t="n"/>
+      <c r="K18" s="30" t="n"/>
+      <c r="L18" s="30" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="18" t="n">
+      <c r="A19" s="31" t="n">
         <v>44834</v>
       </c>
-      <c r="B19" s="6" t="n">
+      <c r="B19" s="24" t="n">
         <v>14337.4</v>
       </c>
-      <c r="C19" s="7" t="n">
+      <c r="C19" s="25" t="n">
         <v>26.56</v>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -3120,15 +3134,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E19" s="21">
+      <c r="E19" s="33">
         <f>IFERROR(B19/C19,"")</f>
         <v/>
       </c>
-      <c r="F19" s="16">
+      <c r="F19" s="30">
         <f>IF(AND(D19=D15,E15&lt;&gt;""),E19/E15-1,"")</f>
         <v/>
       </c>
-      <c r="G19" s="16">
+      <c r="G19" s="30">
         <f>IF(C19="","",(COUNTIFS($D$2:$D$34,D19,$C$2:$C$34,"&gt;0",$C$2:$C$34,"&lt;"&amp;C19)+(COUNTIFS($D$2:$D$34,D19,$C$2:$C$34,C19)+1)/2)/COUNTIFS($D$2:$D$34,D19,$C$2:$C$34,"&gt;0"))</f>
         <v/>
       </c>
@@ -3136,25 +3150,25 @@
         <f>IF(G19="","",IF(G19&lt;=20%,"Q1 Cheapest",IF(G19&lt;=40%,"Q2",IF(G19&lt;=60%,"Q3",IF(G19&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I19" s="16">
+      <c r="I19" s="30">
         <f>IFERROR(B23/B19-1,"")</f>
         <v/>
       </c>
-      <c r="J19" s="16">
+      <c r="J19" s="30">
         <f>IFERROR((B31/B19)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K19" s="16" t="n"/>
-      <c r="L19" s="16" t="n"/>
+      <c r="K19" s="30" t="n"/>
+      <c r="L19" s="30" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="18" t="n">
+      <c r="A20" s="31" t="n">
         <v>44926</v>
       </c>
-      <c r="B20" s="6" t="n">
+      <c r="B20" s="24" t="n">
         <v>14208.25</v>
       </c>
-      <c r="C20" s="7" t="n">
+      <c r="C20" s="25" t="n">
         <v>25.73</v>
       </c>
       <c r="D20" s="2" t="inlineStr">
@@ -3162,15 +3176,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E20" s="21">
+      <c r="E20" s="33">
         <f>IFERROR(B20/C20,"")</f>
         <v/>
       </c>
-      <c r="F20" s="16">
+      <c r="F20" s="30">
         <f>IF(AND(D20=D16,E16&lt;&gt;""),E20/E16-1,"")</f>
         <v/>
       </c>
-      <c r="G20" s="16">
+      <c r="G20" s="30">
         <f>IF(C20="","",(COUNTIFS($D$2:$D$34,D20,$C$2:$C$34,"&gt;0",$C$2:$C$34,"&lt;"&amp;C20)+(COUNTIFS($D$2:$D$34,D20,$C$2:$C$34,C20)+1)/2)/COUNTIFS($D$2:$D$34,D20,$C$2:$C$34,"&gt;0"))</f>
         <v/>
       </c>
@@ -3178,25 +3192,25 @@
         <f>IF(G20="","",IF(G20&lt;=20%,"Q1 Cheapest",IF(G20&lt;=40%,"Q2",IF(G20&lt;=60%,"Q3",IF(G20&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I20" s="16">
+      <c r="I20" s="30">
         <f>IFERROR(B24/B20-1,"")</f>
         <v/>
       </c>
-      <c r="J20" s="16">
+      <c r="J20" s="30">
         <f>IFERROR((B32/B20)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K20" s="16" t="n"/>
-      <c r="L20" s="16" t="n"/>
+      <c r="K20" s="30" t="n"/>
+      <c r="L20" s="30" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="18" t="n">
+      <c r="A21" s="31" t="n">
         <v>45016</v>
       </c>
-      <c r="B21" s="6" t="n">
+      <c r="B21" s="24" t="n">
         <v>14014.15</v>
       </c>
-      <c r="C21" s="7" t="n">
+      <c r="C21" s="25" t="n">
         <v>24.3</v>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -3204,15 +3218,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E21" s="21">
+      <c r="E21" s="33">
         <f>IFERROR(B21/C21,"")</f>
         <v/>
       </c>
-      <c r="F21" s="16">
+      <c r="F21" s="30">
         <f>IF(AND(D21=D17,E17&lt;&gt;""),E21/E17-1,"")</f>
         <v/>
       </c>
-      <c r="G21" s="16">
+      <c r="G21" s="30">
         <f>IF(C21="","",(COUNTIFS($D$2:$D$34,D21,$C$2:$C$34,"&gt;0",$C$2:$C$34,"&lt;"&amp;C21)+(COUNTIFS($D$2:$D$34,D21,$C$2:$C$34,C21)+1)/2)/COUNTIFS($D$2:$D$34,D21,$C$2:$C$34,"&gt;0"))</f>
         <v/>
       </c>
@@ -3220,25 +3234,25 @@
         <f>IF(G21="","",IF(G21&lt;=20%,"Q1 Cheapest",IF(G21&lt;=40%,"Q2",IF(G21&lt;=60%,"Q3",IF(G21&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I21" s="16">
+      <c r="I21" s="30">
         <f>IFERROR(B25/B21-1,"")</f>
         <v/>
       </c>
-      <c r="J21" s="16">
+      <c r="J21" s="30">
         <f>IFERROR((B33/B21)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K21" s="16" t="n"/>
-      <c r="L21" s="16" t="n"/>
+      <c r="K21" s="30" t="n"/>
+      <c r="L21" s="30" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="18" t="n">
+      <c r="A22" s="31" t="n">
         <v>45107</v>
       </c>
-      <c r="B22" s="6" t="n">
+      <c r="B22" s="24" t="n">
         <v>15648.8</v>
       </c>
-      <c r="C22" s="7" t="n">
+      <c r="C22" s="25" t="n">
         <v>26.69</v>
       </c>
       <c r="D22" s="2" t="inlineStr">
@@ -3246,15 +3260,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E22" s="21">
+      <c r="E22" s="33">
         <f>IFERROR(B22/C22,"")</f>
         <v/>
       </c>
-      <c r="F22" s="16">
+      <c r="F22" s="30">
         <f>IF(AND(D22=D18,E18&lt;&gt;""),E22/E18-1,"")</f>
         <v/>
       </c>
-      <c r="G22" s="16">
+      <c r="G22" s="30">
         <f>IF(C22="","",(COUNTIFS($D$2:$D$34,D22,$C$2:$C$34,"&gt;0",$C$2:$C$34,"&lt;"&amp;C22)+(COUNTIFS($D$2:$D$34,D22,$C$2:$C$34,C22)+1)/2)/COUNTIFS($D$2:$D$34,D22,$C$2:$C$34,"&gt;0"))</f>
         <v/>
       </c>
@@ -3262,25 +3276,25 @@
         <f>IF(G22="","",IF(G22&lt;=20%,"Q1 Cheapest",IF(G22&lt;=40%,"Q2",IF(G22&lt;=60%,"Q3",IF(G22&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I22" s="16">
+      <c r="I22" s="30">
         <f>IFERROR(B26/B22-1,"")</f>
         <v/>
       </c>
-      <c r="J22" s="16">
+      <c r="J22" s="30">
         <f>IFERROR((B34/B22)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K22" s="16" t="n"/>
-      <c r="L22" s="16" t="n"/>
+      <c r="K22" s="30" t="n"/>
+      <c r="L22" s="30" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="18" t="n">
+      <c r="A23" s="31" t="n">
         <v>45199</v>
       </c>
-      <c r="B23" s="6" t="n">
+      <c r="B23" s="24" t="n">
         <v>16391.8</v>
       </c>
-      <c r="C23" s="7" t="n">
+      <c r="C23" s="25" t="n">
         <v>27.54</v>
       </c>
       <c r="D23" s="2" t="inlineStr">
@@ -3288,15 +3302,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E23" s="21">
+      <c r="E23" s="33">
         <f>IFERROR(B23/C23,"")</f>
         <v/>
       </c>
-      <c r="F23" s="16">
+      <c r="F23" s="30">
         <f>IF(AND(D23=D19,E19&lt;&gt;""),E23/E19-1,"")</f>
         <v/>
       </c>
-      <c r="G23" s="16">
+      <c r="G23" s="30">
         <f>IF(C23="","",(COUNTIFS($D$2:$D$34,D23,$C$2:$C$34,"&gt;0",$C$2:$C$34,"&lt;"&amp;C23)+(COUNTIFS($D$2:$D$34,D23,$C$2:$C$34,C23)+1)/2)/COUNTIFS($D$2:$D$34,D23,$C$2:$C$34,"&gt;0"))</f>
         <v/>
       </c>
@@ -3304,22 +3318,22 @@
         <f>IF(G23="","",IF(G23&lt;=20%,"Q1 Cheapest",IF(G23&lt;=40%,"Q2",IF(G23&lt;=60%,"Q3",IF(G23&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I23" s="16">
+      <c r="I23" s="30">
         <f>IFERROR(B27/B23-1,"")</f>
         <v/>
       </c>
-      <c r="J23" s="16" t="n"/>
-      <c r="K23" s="16" t="n"/>
-      <c r="L23" s="16" t="n"/>
+      <c r="J23" s="30" t="n"/>
+      <c r="K23" s="30" t="n"/>
+      <c r="L23" s="30" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="18" t="n">
+      <c r="A24" s="31" t="n">
         <v>45291</v>
       </c>
-      <c r="B24" s="6" t="n">
+      <c r="B24" s="24" t="n">
         <v>18453.1</v>
       </c>
-      <c r="C24" s="7" t="n">
+      <c r="C24" s="25" t="n">
         <v>32.97</v>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -3327,15 +3341,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E24" s="21">
+      <c r="E24" s="33">
         <f>IFERROR(B24/C24,"")</f>
         <v/>
       </c>
-      <c r="F24" s="16">
+      <c r="F24" s="30">
         <f>IF(AND(D24=D20,E20&lt;&gt;""),E24/E20-1,"")</f>
         <v/>
       </c>
-      <c r="G24" s="16">
+      <c r="G24" s="30">
         <f>IF(C24="","",(COUNTIFS($D$2:$D$34,D24,$C$2:$C$34,"&gt;0",$C$2:$C$34,"&lt;"&amp;C24)+(COUNTIFS($D$2:$D$34,D24,$C$2:$C$34,C24)+1)/2)/COUNTIFS($D$2:$D$34,D24,$C$2:$C$34,"&gt;0"))</f>
         <v/>
       </c>
@@ -3343,22 +3357,22 @@
         <f>IF(G24="","",IF(G24&lt;=20%,"Q1 Cheapest",IF(G24&lt;=40%,"Q2",IF(G24&lt;=60%,"Q3",IF(G24&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I24" s="16">
+      <c r="I24" s="30">
         <f>IFERROR(B28/B24-1,"")</f>
         <v/>
       </c>
-      <c r="J24" s="16" t="n"/>
-      <c r="K24" s="16" t="n"/>
-      <c r="L24" s="16" t="n"/>
+      <c r="J24" s="30" t="n"/>
+      <c r="K24" s="30" t="n"/>
+      <c r="L24" s="30" t="n"/>
     </row>
     <row r="25">
-      <c r="A25" s="18" t="n">
+      <c r="A25" s="31" t="n">
         <v>45382</v>
       </c>
-      <c r="B25" s="6" t="n">
+      <c r="B25" s="24" t="n">
         <v>18598.05</v>
       </c>
-      <c r="C25" s="7" t="n">
+      <c r="C25" s="25" t="n">
         <v>32.57</v>
       </c>
       <c r="D25" s="2" t="inlineStr">
@@ -3366,15 +3380,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E25" s="21">
+      <c r="E25" s="33">
         <f>IFERROR(B25/C25,"")</f>
         <v/>
       </c>
-      <c r="F25" s="16">
+      <c r="F25" s="30">
         <f>IF(AND(D25=D21,E21&lt;&gt;""),E25/E21-1,"")</f>
         <v/>
       </c>
-      <c r="G25" s="16">
+      <c r="G25" s="30">
         <f>IF(C25="","",(COUNTIFS($D$2:$D$34,D25,$C$2:$C$34,"&gt;0",$C$2:$C$34,"&lt;"&amp;C25)+(COUNTIFS($D$2:$D$34,D25,$C$2:$C$34,C25)+1)/2)/COUNTIFS($D$2:$D$34,D25,$C$2:$C$34,"&gt;0"))</f>
         <v/>
       </c>
@@ -3382,22 +3396,22 @@
         <f>IF(G25="","",IF(G25&lt;=20%,"Q1 Cheapest",IF(G25&lt;=40%,"Q2",IF(G25&lt;=60%,"Q3",IF(G25&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I25" s="16">
+      <c r="I25" s="30">
         <f>IFERROR(B29/B25-1,"")</f>
         <v/>
       </c>
-      <c r="J25" s="16" t="n"/>
-      <c r="K25" s="16" t="n"/>
-      <c r="L25" s="16" t="n"/>
+      <c r="J25" s="30" t="n"/>
+      <c r="K25" s="30" t="n"/>
+      <c r="L25" s="30" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" s="18" t="n">
+      <c r="A26" s="31" t="n">
         <v>45473</v>
       </c>
-      <c r="B26" s="6" t="n">
+      <c r="B26" s="24" t="n">
         <v>20682.5</v>
       </c>
-      <c r="C26" s="7" t="n">
+      <c r="C26" s="25" t="n">
         <v>35.08</v>
       </c>
       <c r="D26" s="2" t="inlineStr">
@@ -3405,15 +3419,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E26" s="21">
+      <c r="E26" s="33">
         <f>IFERROR(B26/C26,"")</f>
         <v/>
       </c>
-      <c r="F26" s="16">
+      <c r="F26" s="30">
         <f>IF(AND(D26=D22,E22&lt;&gt;""),E26/E22-1,"")</f>
         <v/>
       </c>
-      <c r="G26" s="16">
+      <c r="G26" s="30">
         <f>IF(C26="","",(COUNTIFS($D$2:$D$34,D26,$C$2:$C$34,"&gt;0",$C$2:$C$34,"&lt;"&amp;C26)+(COUNTIFS($D$2:$D$34,D26,$C$2:$C$34,C26)+1)/2)/COUNTIFS($D$2:$D$34,D26,$C$2:$C$34,"&gt;0"))</f>
         <v/>
       </c>
@@ -3421,22 +3435,22 @@
         <f>IF(G26="","",IF(G26&lt;=20%,"Q1 Cheapest",IF(G26&lt;=40%,"Q2",IF(G26&lt;=60%,"Q3",IF(G26&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I26" s="16">
+      <c r="I26" s="30">
         <f>IFERROR(B30/B26-1,"")</f>
         <v/>
       </c>
-      <c r="J26" s="16" t="n"/>
-      <c r="K26" s="16" t="n"/>
-      <c r="L26" s="16" t="n"/>
+      <c r="J26" s="30" t="n"/>
+      <c r="K26" s="30" t="n"/>
+      <c r="L26" s="30" t="n"/>
     </row>
     <row r="27">
-      <c r="A27" s="18" t="n">
+      <c r="A27" s="31" t="n">
         <v>45565</v>
       </c>
-      <c r="B27" s="6" t="n">
+      <c r="B27" s="24" t="n">
         <v>23336.15</v>
       </c>
-      <c r="C27" s="7" t="n">
+      <c r="C27" s="25" t="n">
         <v>38.05</v>
       </c>
       <c r="D27" s="2" t="inlineStr">
@@ -3444,15 +3458,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E27" s="21">
+      <c r="E27" s="33">
         <f>IFERROR(B27/C27,"")</f>
         <v/>
       </c>
-      <c r="F27" s="16">
+      <c r="F27" s="30">
         <f>IF(AND(D27=D23,E23&lt;&gt;""),E27/E23-1,"")</f>
         <v/>
       </c>
-      <c r="G27" s="16">
+      <c r="G27" s="30">
         <f>IF(C27="","",(COUNTIFS($D$2:$D$34,D27,$C$2:$C$34,"&gt;0",$C$2:$C$34,"&lt;"&amp;C27)+(COUNTIFS($D$2:$D$34,D27,$C$2:$C$34,C27)+1)/2)/COUNTIFS($D$2:$D$34,D27,$C$2:$C$34,"&gt;0"))</f>
         <v/>
       </c>
@@ -3460,22 +3474,22 @@
         <f>IF(G27="","",IF(G27&lt;=20%,"Q1 Cheapest",IF(G27&lt;=40%,"Q2",IF(G27&lt;=60%,"Q3",IF(G27&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I27" s="16">
+      <c r="I27" s="30">
         <f>IFERROR(B31/B27-1,"")</f>
         <v/>
       </c>
-      <c r="J27" s="16" t="n"/>
-      <c r="K27" s="16" t="n"/>
-      <c r="L27" s="16" t="n"/>
+      <c r="J27" s="30" t="n"/>
+      <c r="K27" s="30" t="n"/>
+      <c r="L27" s="30" t="n"/>
     </row>
     <row r="28">
-      <c r="A28" s="18" t="n">
+      <c r="A28" s="31" t="n">
         <v>45657</v>
       </c>
-      <c r="B28" s="6" t="n">
+      <c r="B28" s="24" t="n">
         <v>20799.2</v>
       </c>
-      <c r="C28" s="7" t="n">
+      <c r="C28" s="25" t="n">
         <v>30.56</v>
       </c>
       <c r="D28" s="2" t="inlineStr">
@@ -3483,15 +3497,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E28" s="21">
+      <c r="E28" s="33">
         <f>IFERROR(B28/C28,"")</f>
         <v/>
       </c>
-      <c r="F28" s="16">
+      <c r="F28" s="30">
         <f>IF(AND(D28=D24,E24&lt;&gt;""),E28/E24-1,"")</f>
         <v/>
       </c>
-      <c r="G28" s="16">
+      <c r="G28" s="30">
         <f>IF(C28="","",(COUNTIFS($D$2:$D$34,D28,$C$2:$C$34,"&gt;0",$C$2:$C$34,"&lt;"&amp;C28)+(COUNTIFS($D$2:$D$34,D28,$C$2:$C$34,C28)+1)/2)/COUNTIFS($D$2:$D$34,D28,$C$2:$C$34,"&gt;0"))</f>
         <v/>
       </c>
@@ -3499,22 +3513,22 @@
         <f>IF(G28="","",IF(G28&lt;=20%,"Q1 Cheapest",IF(G28&lt;=40%,"Q2",IF(G28&lt;=60%,"Q3",IF(G28&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I28" s="16">
+      <c r="I28" s="30">
         <f>IFERROR(B32/B28-1,"")</f>
         <v/>
       </c>
-      <c r="J28" s="16" t="n"/>
-      <c r="K28" s="16" t="n"/>
-      <c r="L28" s="16" t="n"/>
+      <c r="J28" s="30" t="n"/>
+      <c r="K28" s="30" t="n"/>
+      <c r="L28" s="30" t="n"/>
     </row>
     <row r="29">
-      <c r="A29" s="18" t="n">
+      <c r="A29" s="31" t="n">
         <v>45747</v>
       </c>
-      <c r="B29" s="6" t="n">
+      <c r="B29" s="24" t="n">
         <v>19187.1</v>
       </c>
-      <c r="C29" s="7" t="n">
+      <c r="C29" s="25" t="n">
         <v>27.95</v>
       </c>
       <c r="D29" s="2" t="inlineStr">
@@ -3522,15 +3536,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E29" s="21">
+      <c r="E29" s="33">
         <f>IFERROR(B29/C29,"")</f>
         <v/>
       </c>
-      <c r="F29" s="16">
+      <c r="F29" s="30">
         <f>IF(AND(D29=D25,E25&lt;&gt;""),E29/E25-1,"")</f>
         <v/>
       </c>
-      <c r="G29" s="16">
+      <c r="G29" s="30">
         <f>IF(C29="","",(COUNTIFS($D$2:$D$34,D29,$C$2:$C$34,"&gt;0",$C$2:$C$34,"&lt;"&amp;C29)+(COUNTIFS($D$2:$D$34,D29,$C$2:$C$34,C29)+1)/2)/COUNTIFS($D$2:$D$34,D29,$C$2:$C$34,"&gt;0"))</f>
         <v/>
       </c>
@@ -3538,22 +3552,22 @@
         <f>IF(G29="","",IF(G29&lt;=20%,"Q1 Cheapest",IF(G29&lt;=40%,"Q2",IF(G29&lt;=60%,"Q3",IF(G29&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I29" s="16">
+      <c r="I29" s="30">
         <f>IFERROR(B33/B29-1,"")</f>
         <v/>
       </c>
-      <c r="J29" s="16" t="n"/>
-      <c r="K29" s="16" t="n"/>
-      <c r="L29" s="16" t="n"/>
+      <c r="J29" s="30" t="n"/>
+      <c r="K29" s="30" t="n"/>
+      <c r="L29" s="30" t="n"/>
     </row>
     <row r="30">
-      <c r="A30" s="18" t="n">
+      <c r="A30" s="31" t="n">
         <v>45838</v>
       </c>
-      <c r="B30" s="6" t="n">
+      <c r="B30" s="24" t="n">
         <v>21025.4</v>
       </c>
-      <c r="C30" s="7" t="n">
+      <c r="C30" s="25" t="n">
         <v>29.56</v>
       </c>
       <c r="D30" s="2" t="inlineStr">
@@ -3561,15 +3575,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E30" s="21">
+      <c r="E30" s="33">
         <f>IFERROR(B30/C30,"")</f>
         <v/>
       </c>
-      <c r="F30" s="16">
+      <c r="F30" s="30">
         <f>IF(AND(D30=D26,E26&lt;&gt;""),E30/E26-1,"")</f>
         <v/>
       </c>
-      <c r="G30" s="16">
+      <c r="G30" s="30">
         <f>IF(C30="","",(COUNTIFS($D$2:$D$34,D30,$C$2:$C$34,"&gt;0",$C$2:$C$34,"&lt;"&amp;C30)+(COUNTIFS($D$2:$D$34,D30,$C$2:$C$34,C30)+1)/2)/COUNTIFS($D$2:$D$34,D30,$C$2:$C$34,"&gt;0"))</f>
         <v/>
       </c>
@@ -3577,22 +3591,22 @@
         <f>IF(G30="","",IF(G30&lt;=20%,"Q1 Cheapest",IF(G30&lt;=40%,"Q2",IF(G30&lt;=60%,"Q3",IF(G30&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I30" s="16">
+      <c r="I30" s="30">
         <f>IFERROR(B34/B30-1,"")</f>
         <v/>
       </c>
-      <c r="J30" s="16" t="n"/>
-      <c r="K30" s="16" t="n"/>
-      <c r="L30" s="16" t="n"/>
+      <c r="J30" s="30" t="n"/>
+      <c r="K30" s="30" t="n"/>
+      <c r="L30" s="30" t="n"/>
     </row>
     <row r="31">
-      <c r="A31" s="18" t="n">
+      <c r="A31" s="31" t="n">
         <v>45930</v>
       </c>
-      <c r="B31" s="6" t="n">
+      <c r="B31" s="24" t="n">
         <v>20338.8</v>
       </c>
-      <c r="C31" s="7" t="n">
+      <c r="C31" s="25" t="n">
         <v>27.94</v>
       </c>
       <c r="D31" s="2" t="inlineStr">
@@ -3600,15 +3614,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E31" s="21">
+      <c r="E31" s="33">
         <f>IFERROR(B31/C31,"")</f>
         <v/>
       </c>
-      <c r="F31" s="16">
+      <c r="F31" s="30">
         <f>IF(AND(D31=D27,E27&lt;&gt;""),E31/E27-1,"")</f>
         <v/>
       </c>
-      <c r="G31" s="16">
+      <c r="G31" s="30">
         <f>IF(C31="","",(COUNTIFS($D$2:$D$34,D31,$C$2:$C$34,"&gt;0",$C$2:$C$34,"&lt;"&amp;C31)+(COUNTIFS($D$2:$D$34,D31,$C$2:$C$34,C31)+1)/2)/COUNTIFS($D$2:$D$34,D31,$C$2:$C$34,"&gt;0"))</f>
         <v/>
       </c>
@@ -3616,19 +3630,19 @@
         <f>IF(G31="","",IF(G31&lt;=20%,"Q1 Cheapest",IF(G31&lt;=40%,"Q2",IF(G31&lt;=60%,"Q3",IF(G31&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I31" s="16" t="n"/>
-      <c r="J31" s="16" t="n"/>
-      <c r="K31" s="16" t="n"/>
-      <c r="L31" s="16" t="n"/>
+      <c r="I31" s="30" t="n"/>
+      <c r="J31" s="30" t="n"/>
+      <c r="K31" s="30" t="n"/>
+      <c r="L31" s="30" t="n"/>
     </row>
     <row r="32">
-      <c r="A32" s="18" t="n">
+      <c r="A32" s="31" t="n">
         <v>46022</v>
       </c>
-      <c r="B32" s="6" t="n">
+      <c r="B32" s="24" t="n">
         <v>21410.85</v>
       </c>
-      <c r="C32" s="7" t="n">
+      <c r="C32" s="25" t="n">
         <v>33.02</v>
       </c>
       <c r="D32" s="2" t="inlineStr">
@@ -3636,15 +3650,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E32" s="21">
+      <c r="E32" s="33">
         <f>IFERROR(B32/C32,"")</f>
         <v/>
       </c>
-      <c r="F32" s="16">
+      <c r="F32" s="30">
         <f>IF(AND(D32=D28,E28&lt;&gt;""),E32/E28-1,"")</f>
         <v/>
       </c>
-      <c r="G32" s="16">
+      <c r="G32" s="30">
         <f>IF(C32="","",(COUNTIFS($D$2:$D$34,D32,$C$2:$C$34,"&gt;0",$C$2:$C$34,"&lt;"&amp;C32)+(COUNTIFS($D$2:$D$34,D32,$C$2:$C$34,C32)+1)/2)/COUNTIFS($D$2:$D$34,D32,$C$2:$C$34,"&gt;0"))</f>
         <v/>
       </c>
@@ -3652,19 +3666,19 @@
         <f>IF(G32="","",IF(G32&lt;=20%,"Q1 Cheapest",IF(G32&lt;=40%,"Q2",IF(G32&lt;=60%,"Q3",IF(G32&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I32" s="16" t="n"/>
-      <c r="J32" s="16" t="n"/>
-      <c r="K32" s="16" t="n"/>
-      <c r="L32" s="16" t="n"/>
+      <c r="I32" s="30" t="n"/>
+      <c r="J32" s="30" t="n"/>
+      <c r="K32" s="30" t="n"/>
+      <c r="L32" s="30" t="n"/>
     </row>
     <row r="33">
-      <c r="A33" s="18" t="n">
+      <c r="A33" s="31" t="n">
         <v>46112</v>
       </c>
-      <c r="B33" s="6" t="n">
+      <c r="B33" s="24" t="n">
         <v>18207</v>
       </c>
-      <c r="C33" s="7" t="n">
+      <c r="C33" s="25" t="n">
         <v>27.93</v>
       </c>
       <c r="D33" s="2" t="inlineStr">
@@ -3672,15 +3686,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E33" s="21">
+      <c r="E33" s="33">
         <f>IFERROR(B33/C33,"")</f>
         <v/>
       </c>
-      <c r="F33" s="16">
+      <c r="F33" s="30">
         <f>IF(AND(D33=D29,E29&lt;&gt;""),E33/E29-1,"")</f>
         <v/>
       </c>
-      <c r="G33" s="16">
+      <c r="G33" s="30">
         <f>IF(C33="","",(COUNTIFS($D$2:$D$34,D33,$C$2:$C$34,"&gt;0",$C$2:$C$34,"&lt;"&amp;C33)+(COUNTIFS($D$2:$D$34,D33,$C$2:$C$34,C33)+1)/2)/COUNTIFS($D$2:$D$34,D33,$C$2:$C$34,"&gt;0"))</f>
         <v/>
       </c>
@@ -3688,19 +3702,19 @@
         <f>IF(G33="","",IF(G33&lt;=20%,"Q1 Cheapest",IF(G33&lt;=40%,"Q2",IF(G33&lt;=60%,"Q3",IF(G33&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I33" s="16" t="n"/>
-      <c r="J33" s="16" t="n"/>
-      <c r="K33" s="16" t="n"/>
-      <c r="L33" s="16" t="n"/>
+      <c r="I33" s="30" t="n"/>
+      <c r="J33" s="30" t="n"/>
+      <c r="K33" s="30" t="n"/>
+      <c r="L33" s="30" t="n"/>
     </row>
     <row r="34">
-      <c r="A34" s="18" t="n">
+      <c r="A34" s="31" t="n">
         <v>46203</v>
       </c>
-      <c r="B34" s="6" t="n">
+      <c r="B34" s="24" t="n">
         <v>19561.4</v>
       </c>
-      <c r="C34" s="7" t="n">
+      <c r="C34" s="25" t="n">
         <v>27.55</v>
       </c>
       <c r="D34" s="2" t="inlineStr">
@@ -3708,15 +3722,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E34" s="21">
+      <c r="E34" s="33">
         <f>IFERROR(B34/C34,"")</f>
         <v/>
       </c>
-      <c r="F34" s="16">
+      <c r="F34" s="30">
         <f>IF(AND(D34=D30,E30&lt;&gt;""),E34/E30-1,"")</f>
         <v/>
       </c>
-      <c r="G34" s="16">
+      <c r="G34" s="30">
         <f>IF(C34="","",(COUNTIFS($D$2:$D$34,D34,$C$2:$C$34,"&gt;0",$C$2:$C$34,"&lt;"&amp;C34)+(COUNTIFS($D$2:$D$34,D34,$C$2:$C$34,C34)+1)/2)/COUNTIFS($D$2:$D$34,D34,$C$2:$C$34,"&gt;0"))</f>
         <v/>
       </c>
@@ -3724,10 +3738,10 @@
         <f>IF(G34="","",IF(G34&lt;=20%,"Q1 Cheapest",IF(G34&lt;=40%,"Q2",IF(G34&lt;=60%,"Q3",IF(G34&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I34" s="16" t="n"/>
-      <c r="J34" s="16" t="n"/>
-      <c r="K34" s="16" t="n"/>
-      <c r="L34" s="16" t="n"/>
+      <c r="I34" s="30" t="n"/>
+      <c r="J34" s="30" t="n"/>
+      <c r="K34" s="30" t="n"/>
+      <c r="L34" s="30" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.3" right="0.3" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>
@@ -3804,30 +3818,30 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="18" t="n">
+      <c r="A2" s="31" t="n">
         <v>46283</v>
       </c>
-      <c r="B2" s="6" t="n">
+      <c r="B2" s="24" t="n">
         <v>19561.45</v>
       </c>
-      <c r="C2" s="7" t="n">
+      <c r="C2" s="25" t="n">
         <v>26.51</v>
       </c>
-      <c r="D2" s="8" t="n">
+      <c r="D2" s="26" t="n">
         <v>0.113636363636</v>
       </c>
-      <c r="E2" s="8" t="n">
+      <c r="E2" s="26" t="n">
         <v>0.0134742378938</v>
       </c>
-      <c r="F2" s="22">
+      <c r="F2" s="34">
         <f>IF(D2="","",100*(1-D2))</f>
         <v/>
       </c>
-      <c r="G2" s="22">
+      <c r="G2" s="34">
         <f>IF(E2="","",IF(E2&lt;=0,20,IF(E2&lt;5%,20+400*E2,IF(E2&lt;10%,40+400*(E2-5%),IF(E2&lt;15%,60+400*(E2-10%),IF(E2&lt;25%,80+200*(E2-15%),100))))))</f>
         <v/>
       </c>
-      <c r="H2" s="22">
+      <c r="H2" s="34">
         <f>IF(OR(F2="",G2=""),"",70%*F2+30%*G2)</f>
         <v/>
       </c>
@@ -3837,30 +3851,30 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="18" t="n">
+      <c r="A3" s="31" t="n">
         <v>46286</v>
       </c>
-      <c r="B3" s="6" t="n">
+      <c r="B3" s="24" t="n">
         <v>19649.4</v>
       </c>
-      <c r="C3" s="7" t="n">
+      <c r="C3" s="25" t="n">
         <v>26.63</v>
       </c>
-      <c r="D3" s="8" t="n">
+      <c r="D3" s="26" t="n">
         <v>0.128787878788</v>
       </c>
-      <c r="E3" s="8" t="n">
+      <c r="E3" s="26" t="n">
         <v>0.0134502614103</v>
       </c>
-      <c r="F3" s="22">
+      <c r="F3" s="34">
         <f>IF(D3="","",100*(1-D3))</f>
         <v/>
       </c>
-      <c r="G3" s="22">
+      <c r="G3" s="34">
         <f>IF(E3="","",IF(E3&lt;=0,20,IF(E3&lt;5%,20+400*E3,IF(E3&lt;10%,40+400*(E3-5%),IF(E3&lt;15%,60+400*(E3-10%),IF(E3&lt;25%,80+200*(E3-15%),100))))))</f>
         <v/>
       </c>
-      <c r="H3" s="22">
+      <c r="H3" s="34">
         <f>IF(OR(F3="",G3=""),"",70%*F3+30%*G3)</f>
         <v/>
       </c>
@@ -3870,30 +3884,30 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="18" t="n">
+      <c r="A4" s="31" t="n">
         <v>46287</v>
       </c>
-      <c r="B4" s="6" t="n">
+      <c r="B4" s="24" t="n">
         <v>19550.75</v>
       </c>
-      <c r="C4" s="7" t="n">
+      <c r="C4" s="25" t="n">
         <v>26.5</v>
       </c>
-      <c r="D4" s="8" t="n">
+      <c r="D4" s="26" t="n">
         <v>0.113636363636</v>
       </c>
-      <c r="E4" s="8" t="n">
+      <c r="E4" s="26" t="n">
         <v>0.0134069839553</v>
       </c>
-      <c r="F4" s="22">
+      <c r="F4" s="34">
         <f>IF(D4="","",100*(1-D4))</f>
         <v/>
       </c>
-      <c r="G4" s="22">
+      <c r="G4" s="34">
         <f>IF(E4="","",IF(E4&lt;=0,20,IF(E4&lt;5%,20+400*E4,IF(E4&lt;10%,40+400*(E4-5%),IF(E4&lt;15%,60+400*(E4-10%),IF(E4&lt;25%,80+200*(E4-15%),100))))))</f>
         <v/>
       </c>
-      <c r="H4" s="22">
+      <c r="H4" s="34">
         <f>IF(OR(F4="",G4=""),"",70%*F4+30%*G4)</f>
         <v/>
       </c>
@@ -4013,4 +4027,43 @@
   <pageMargins left="0.3" right="0.3" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="0" fitToWidth="1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="42" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="35" t="inlineStr">
+        <is>
+          <t>Nifty200 Quality 30 Composition</t>
+        </is>
+      </c>
+    </row>
+    <row r="2"/>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Official composition data is not currently available for this index.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:E1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/docs/downloads/indices/nifty200-quality-30.xlsx
+++ b/docs/downloads/indices/nifty200-quality-30.xlsx
@@ -11,8 +11,8 @@
     <sheet name="Monthly PE History" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Quarterly Backtest" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Score History" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Sources &amp; Methodology" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Composition" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Composition" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Sources &amp; Methodology" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -110,7 +110,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="37">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -153,6 +153,9 @@
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="169" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -3926,6 +3929,712 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E35"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="33" customWidth="1" min="1" max="1"/>
+    <col width="41" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="32" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="35" t="inlineStr">
+        <is>
+          <t>Nifty200 Quality 30 Composition</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>As of</t>
+        </is>
+      </c>
+      <c r="B2" s="4" t="inlineStr">
+        <is>
+          <t>Retrieved 2026-09-23</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>Weight coverage</t>
+        </is>
+      </c>
+      <c r="E2" s="4" t="inlineStr">
+        <is>
+          <t>Not published</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="B3" s="17" t="inlineStr">
+        <is>
+          <t>NSE Indices — Index Constituent CSV</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>Top 10 weight</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>Not published</t>
+        </is>
+      </c>
+    </row>
+    <row r="4"/>
+    <row r="5">
+      <c r="A5" s="36" t="inlineStr">
+        <is>
+          <t>Rank</t>
+        </is>
+      </c>
+      <c r="B5" s="36" t="inlineStr">
+        <is>
+          <t>Company</t>
+        </is>
+      </c>
+      <c r="C5" s="36" t="inlineStr">
+        <is>
+          <t>Symbol</t>
+        </is>
+      </c>
+      <c r="D5" s="36" t="inlineStr">
+        <is>
+          <t>Sector / Industry</t>
+        </is>
+      </c>
+      <c r="E5" s="36" t="inlineStr">
+        <is>
+          <t>Weight</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>1</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Asian Paints Ltd.</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>ASIANPAINT</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Consumer Durables</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>2</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Bajaj Auto Ltd.</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>BAJAJ-AUTO</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Automobile and Auto Components</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>3</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Bharat Electronics Ltd.</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>BEL</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Capital Goods</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>4</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Britannia Industries Ltd.</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>BRITANNIA</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Fast Moving Consumer Goods</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>5</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Coal India Ltd.</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>COALINDIA</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Oil Gas &amp; Consumable Fuels</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>6</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Colgate Palmolive (India) Ltd.</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>COLPAL</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Fast Moving Consumer Goods</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>7</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Cummins India Ltd.</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>CUMMINSIND</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Capital Goods</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>8</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Dixon Technologies (India) Ltd.</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>DIXON</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Consumer Durables</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>9</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Havells India Ltd.</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>HAVELLS</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Consumer Durables</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>10</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>HCL Technologies Ltd.</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>HCLTECH</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Information Technology</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>11</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>HDFC Asset Management Company Ltd.</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>HDFCAMC</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>12</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Hero MotoCorp Ltd.</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>HEROMOTOCO</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Automobile and Auto Components</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>13</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Hindustan Aeronautics Ltd.</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>HAL</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Capital Goods</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>14</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Hindustan Unilever Ltd.</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>HINDUNILVR</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Fast Moving Consumer Goods</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>15</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Hindustan Zinc Ltd.</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>HINDZINC</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Metals &amp; Mining</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>16</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Infosys Ltd.</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>INFY</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Information Technology</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>17</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>ITC Ltd.</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>ITC</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Fast Moving Consumer Goods</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>18</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>KPIT Technologies Ltd.</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>KPITTECH</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Information Technology</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>19</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>LTM Ltd.</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>LTM</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Information Technology</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>20</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Marico Ltd.</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>MARICO</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Fast Moving Consumer Goods</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>21</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Mazagoan Dock Shipbuilders Ltd.</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>MAZDOCK</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Capital Goods</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>22</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Nestle India Ltd.</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>NESTLEIND</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Fast Moving Consumer Goods</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>23</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Oracle Financial Services Software Ltd.</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>OFSS</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Information Technology</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>24</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Page Industries Ltd.</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>PAGEIND</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Textiles</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>25</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Persistent Systems Ltd.</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>PERSISTENT</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Information Technology</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>26</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Pidilite Industries Ltd.</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>PIDILITIND</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Chemicals</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>27</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Polycab India Ltd.</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>POLYCAB</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Capital Goods</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>28</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Solar Industries India Ltd.</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>SOLARINDS</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Chemicals</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>29</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Tata Consultancy Services Ltd.</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>TCS</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Information Technology</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>30</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Tata Elxsi Ltd.</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>TATAELXSI</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Information Technology</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:E1"/>
+  </mergeCells>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B3" r:id="rId1"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:D11"/>
@@ -4027,43 +4736,4 @@
   <pageMargins left="0.3" right="0.3" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="0" fitToWidth="1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:E3"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="42" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="10" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="35" t="inlineStr">
-        <is>
-          <t>Nifty200 Quality 30 Composition</t>
-        </is>
-      </c>
-    </row>
-    <row r="2"/>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>Official composition data is not currently available for this index.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:E1"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>
--- a/docs/downloads/indices/nifty200-quality-30.xlsx
+++ b/docs/downloads/indices/nifty200-quality-30.xlsx
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>19550.75</v>
+        <v>19579.8</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>26.5</v>
+        <v>26.54</v>
       </c>
     </row>
     <row r="6">
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>737.7641509433962</v>
+        <v>737.7467972871137</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.01340698395529483</v>
+        <v>0.01318227501282165</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.03773584905660377</v>
+        <v>0.03767897513187642</v>
       </c>
     </row>
     <row r="8">
@@ -677,7 +677,7 @@
         </is>
       </c>
       <c r="E8" s="28" t="n">
-        <v>25.36279358211793</v>
+        <v>25.27291000512866</v>
       </c>
     </row>
     <row r="9">
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>69.65429262008993</v>
+        <v>69.62732754699314</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -736,13 +736,13 @@
         </is>
       </c>
       <c r="B13" s="29" t="n">
-        <v>26.50392097844397</v>
+        <v>26.54080621288572</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>19553.64275733258</v>
+        <v>19580.39478097437</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>0.0001479614507158278</v>
+        <v>3.037727527188672e-05</v>
       </c>
     </row>
     <row r="14">
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="B14" s="29" t="n">
-        <v>29.55922492497876</v>
+        <v>29.55897453501429</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>21807.73647932183</v>
+        <v>21807.03879429814</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>0.1154424499991982</v>
+        <v>0.1137518664285715</v>
       </c>
     </row>
     <row r="16">
@@ -3759,7 +3759,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I4"/>
+  <dimension ref="A1:I5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -3916,6 +3916,39 @@
       </c>
       <c r="I4">
         <f>IF(H4="","",IF(H4&gt;=70,"BUY",IF(H4&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="31" t="n">
+        <v>46288</v>
+      </c>
+      <c r="B5" s="24" t="n">
+        <v>19579.8</v>
+      </c>
+      <c r="C5" s="25" t="n">
+        <v>26.54</v>
+      </c>
+      <c r="D5" s="26" t="n">
+        <v>0.113636363636</v>
+      </c>
+      <c r="E5" s="26" t="n">
+        <v>0.0131822750128</v>
+      </c>
+      <c r="F5" s="34">
+        <f>IF(D5="","",100*(1-D5))</f>
+        <v/>
+      </c>
+      <c r="G5" s="34">
+        <f>IF(E5="","",IF(E5&lt;=0,20,IF(E5&lt;5%,20+400*E5,IF(E5&lt;10%,40+400*(E5-5%),IF(E5&lt;15%,60+400*(E5-10%),IF(E5&lt;25%,80+200*(E5-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H5" s="34">
+        <f>IF(OR(F5="",G5=""),"",70%*F5+30%*G5)</f>
+        <v/>
+      </c>
+      <c r="I5">
+        <f>IF(H5="","",IF(H5&gt;=70,"BUY",IF(H5&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>

--- a/docs/downloads/indices/nifty200-quality-30.xlsx
+++ b/docs/downloads/indices/nifty200-quality-30.xlsx
@@ -568,7 +568,7 @@
     <col width="34" customWidth="1" min="1" max="1"/>
     <col width="34" customWidth="1" min="2" max="2"/>
     <col width="24" customWidth="1" min="3" max="3"/>
-    <col width="24" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
     <col width="29" customWidth="1" min="5" max="5"/>
     <col width="17" customWidth="1" min="6" max="6"/>
     <col width="19" customWidth="1" min="7" max="7"/>
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>19579.8</v>
+        <v>19371.25</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>26.54</v>
+        <v>26.26</v>
       </c>
     </row>
     <row r="6">
@@ -633,7 +633,7 @@
         </is>
       </c>
       <c r="B6" s="26" t="n">
-        <v>0.1136363636363636</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>737.7467972871137</v>
+        <v>737.6713632901751</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.01318227501282165</v>
+        <v>0.0131075275984589</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.03767897513187642</v>
+        <v>0.03808073115003808</v>
       </c>
     </row>
     <row r="8">
@@ -669,7 +669,7 @@
         </is>
       </c>
       <c r="B8" s="28" t="n">
-        <v>88.63636363636364</v>
+        <v>91.66666666666666</v>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
@@ -677,7 +677,7 @@
         </is>
       </c>
       <c r="E8" s="28" t="n">
-        <v>25.27291000512866</v>
+        <v>25.24301103938356</v>
       </c>
     </row>
     <row r="9">
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>69.62732754699314</v>
+        <v>71.73956997848173</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -696,7 +696,7 @@
       </c>
       <c r="E9" s="12" t="inlineStr">
         <is>
-          <t>HOLD</t>
+          <t>BUY</t>
         </is>
       </c>
     </row>
@@ -736,13 +736,13 @@
         </is>
       </c>
       <c r="B13" s="29" t="n">
-        <v>26.54080621288572</v>
+        <v>26.49223871526798</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>19580.39478097437</v>
+        <v>19542.56584970049</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>3.037727527188672e-05</v>
+        <v>0.008843820078750175</v>
       </c>
     </row>
     <row r="14">
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="B14" s="29" t="n">
-        <v>29.55897453501429</v>
+        <v>29.55889124503828</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>21807.03879429814</v>
+        <v>21804.74760207341</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>0.1137518664285715</v>
+        <v>0.1256241905955171</v>
       </c>
     </row>
     <row r="16">
@@ -3759,13 +3759,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I5"/>
+  <dimension ref="A1:I6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
     <col width="13" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="17" customWidth="1" min="4" max="4"/>
     <col width="17" customWidth="1" min="5" max="5"/>
     <col width="26" customWidth="1" min="6" max="6"/>
     <col width="34" customWidth="1" min="7" max="7"/>
@@ -3949,6 +3949,39 @@
       </c>
       <c r="I5">
         <f>IF(H5="","",IF(H5&gt;=70,"BUY",IF(H5&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="31" t="n">
+        <v>46289</v>
+      </c>
+      <c r="B6" s="24" t="n">
+        <v>19371.25</v>
+      </c>
+      <c r="C6" s="25" t="n">
+        <v>26.26</v>
+      </c>
+      <c r="D6" s="26" t="n">
+        <v>0.08333333333329999</v>
+      </c>
+      <c r="E6" s="26" t="n">
+        <v>0.0131075275985</v>
+      </c>
+      <c r="F6" s="34">
+        <f>IF(D6="","",100*(1-D6))</f>
+        <v/>
+      </c>
+      <c r="G6" s="34">
+        <f>IF(E6="","",IF(E6&lt;=0,20,IF(E6&lt;5%,20+400*E6,IF(E6&lt;10%,40+400*(E6-5%),IF(E6&lt;15%,60+400*(E6-10%),IF(E6&lt;25%,80+200*(E6-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H6" s="34">
+        <f>IF(OR(F6="",G6=""),"",70%*F6+30%*G6)</f>
+        <v/>
+      </c>
+      <c r="I6">
+        <f>IF(H6="","",IF(H6&gt;=70,"BUY",IF(H6&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -3989,7 +4022,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-09-23</t>
+          <t>Retrieved 2026-09-24</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">

--- a/docs/downloads/indices/nifty200-quality-30.xlsx
+++ b/docs/downloads/indices/nifty200-quality-30.xlsx
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>19371.25</v>
+        <v>19453.95</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>26.26</v>
+        <v>26.37</v>
       </c>
     </row>
     <row r="6">
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>737.6713632901751</v>
+        <v>737.7303754266212</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.0131075275984589</v>
+        <v>0.01312847928925276</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.03808073115003808</v>
+        <v>0.0379218809252939</v>
       </c>
     </row>
     <row r="8">
@@ -677,7 +677,7 @@
         </is>
       </c>
       <c r="E8" s="28" t="n">
-        <v>25.24301103938356</v>
+        <v>25.2513917157011</v>
       </c>
     </row>
     <row r="9">
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>71.73956997848173</v>
+        <v>71.74208418137698</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -736,13 +736,13 @@
         </is>
       </c>
       <c r="B13" s="29" t="n">
-        <v>26.49223871526798</v>
+        <v>26.49240213845617</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>19542.56584970049</v>
+        <v>19544.24977555629</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>0.008843820078750175</v>
+        <v>0.004641719319536275</v>
       </c>
     </row>
     <row r="14">
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="B14" s="29" t="n">
-        <v>29.55889124503828</v>
+        <v>29.55891459120802</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>21804.74760207341</v>
+        <v>21806.50915857533</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>0.1256241905955171</v>
+        <v>0.1209296394087229</v>
       </c>
     </row>
     <row r="16">
@@ -3759,7 +3759,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I6"/>
+  <dimension ref="A1:I7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -3982,6 +3982,39 @@
       </c>
       <c r="I6">
         <f>IF(H6="","",IF(H6&gt;=70,"BUY",IF(H6&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="31" t="n">
+        <v>46290</v>
+      </c>
+      <c r="B7" s="24" t="n">
+        <v>19453.95</v>
+      </c>
+      <c r="C7" s="25" t="n">
+        <v>26.37</v>
+      </c>
+      <c r="D7" s="26" t="n">
+        <v>0.08333333333329999</v>
+      </c>
+      <c r="E7" s="26" t="n">
+        <v>0.0131284792893</v>
+      </c>
+      <c r="F7" s="34">
+        <f>IF(D7="","",100*(1-D7))</f>
+        <v/>
+      </c>
+      <c r="G7" s="34">
+        <f>IF(E7="","",IF(E7&lt;=0,20,IF(E7&lt;5%,20+400*E7,IF(E7&lt;10%,40+400*(E7-5%),IF(E7&lt;15%,60+400*(E7-10%),IF(E7&lt;25%,80+200*(E7-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H7" s="34">
+        <f>IF(OR(F7="",G7=""),"",70%*F7+30%*G7)</f>
+        <v/>
+      </c>
+      <c r="I7">
+        <f>IF(H7="","",IF(H7&gt;=70,"BUY",IF(H7&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -4022,7 +4055,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-09-24</t>
+          <t>Retrieved 2026-09-25</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">

--- a/docs/downloads/indices/nifty200-quality-30.xlsx
+++ b/docs/downloads/indices/nifty200-quality-30.xlsx
@@ -568,7 +568,7 @@
     <col width="34" customWidth="1" min="1" max="1"/>
     <col width="34" customWidth="1" min="2" max="2"/>
     <col width="24" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="21" customWidth="1" min="4" max="4"/>
     <col width="29" customWidth="1" min="5" max="5"/>
     <col width="17" customWidth="1" min="6" max="6"/>
     <col width="19" customWidth="1" min="7" max="7"/>
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46290</v>
+        <v>46293</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>19453.95</v>
+        <v>19245.55</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>26.37</v>
+        <v>26.09</v>
       </c>
     </row>
     <row r="6">
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>737.7303754266212</v>
+        <v>737.6600229973169</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.01312847928925276</v>
+        <v>0.01327723865888775</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.0379218809252939</v>
+        <v>0.0383288616328095</v>
       </c>
     </row>
     <row r="8">
@@ -677,7 +677,7 @@
         </is>
       </c>
       <c r="E8" s="28" t="n">
-        <v>25.2513917157011</v>
+        <v>25.3108954635551</v>
       </c>
     </row>
     <row r="9">
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>71.74208418137698</v>
+        <v>71.75993530573319</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -736,13 +736,13 @@
         </is>
       </c>
       <c r="B13" s="29" t="n">
-        <v>26.49240213845617</v>
+        <v>26.49356246153932</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>19544.24977555629</v>
+        <v>19543.24189465995</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>0.004641719319536275</v>
+        <v>0.01546808974853664</v>
       </c>
     </row>
     <row r="14">
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="B14" s="29" t="n">
-        <v>29.55891459120802</v>
+        <v>29.55908035164848</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>21806.50915857533</v>
+        <v>21804.55189197655</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>0.1209296394087229</v>
+        <v>0.1329659007914326</v>
       </c>
     </row>
     <row r="16">
@@ -3759,7 +3759,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I7"/>
+  <dimension ref="A1:I8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -4015,6 +4015,39 @@
       </c>
       <c r="I7">
         <f>IF(H7="","",IF(H7&gt;=70,"BUY",IF(H7&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="31" t="n">
+        <v>46293</v>
+      </c>
+      <c r="B8" s="24" t="n">
+        <v>19245.55</v>
+      </c>
+      <c r="C8" s="25" t="n">
+        <v>26.09</v>
+      </c>
+      <c r="D8" s="26" t="n">
+        <v>0.08333333333329999</v>
+      </c>
+      <c r="E8" s="26" t="n">
+        <v>0.0132772386589</v>
+      </c>
+      <c r="F8" s="34">
+        <f>IF(D8="","",100*(1-D8))</f>
+        <v/>
+      </c>
+      <c r="G8" s="34">
+        <f>IF(E8="","",IF(E8&lt;=0,20,IF(E8&lt;5%,20+400*E8,IF(E8&lt;10%,40+400*(E8-5%),IF(E8&lt;15%,60+400*(E8-10%),IF(E8&lt;25%,80+200*(E8-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H8" s="34">
+        <f>IF(OR(F8="",G8=""),"",70%*F8+30%*G8)</f>
+        <v/>
+      </c>
+      <c r="I8">
+        <f>IF(H8="","",IF(H8&gt;=70,"BUY",IF(H8&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -4055,7 +4088,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-09-25</t>
+          <t>Retrieved 2026-09-28</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">

--- a/docs/downloads/indices/nifty200-quality-30.xlsx
+++ b/docs/downloads/indices/nifty200-quality-30.xlsx
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>19245.55</v>
+        <v>18919.5</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>26.09</v>
+        <v>25.64</v>
       </c>
     </row>
     <row r="6">
@@ -633,7 +633,7 @@
         </is>
       </c>
       <c r="B6" s="26" t="n">
-        <v>0.08333333333333333</v>
+        <v>0.06818181818181818</v>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>737.6600229973169</v>
+        <v>737.890015600624</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.01327723865888775</v>
+        <v>0.01335858550754776</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.0383288616328095</v>
+        <v>0.0390015600624025</v>
       </c>
     </row>
     <row r="8">
@@ -669,7 +669,7 @@
         </is>
       </c>
       <c r="B8" s="28" t="n">
-        <v>91.66666666666666</v>
+        <v>93.18181818181819</v>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
@@ -677,7 +677,7 @@
         </is>
       </c>
       <c r="E8" s="28" t="n">
-        <v>25.3108954635551</v>
+        <v>25.3434342030191</v>
       </c>
     </row>
     <row r="9">
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>71.75993530573319</v>
+        <v>72.83030298817846</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -736,13 +736,13 @@
         </is>
       </c>
       <c r="B13" s="29" t="n">
-        <v>26.49356246153932</v>
+        <v>26.49419696695887</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>19543.24189465995</v>
+        <v>19549.80341327529</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>0.01546808974853664</v>
+        <v>0.03331501431196848</v>
       </c>
     </row>
     <row r="14">
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="B14" s="29" t="n">
-        <v>29.55908035164848</v>
+        <v>29.55917099527984</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>21804.55189197655</v>
+        <v>21811.41714684855</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>0.1329659007914326</v>
+        <v>0.1528537829672323</v>
       </c>
     </row>
     <row r="16">
@@ -3759,7 +3759,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I8"/>
+  <dimension ref="A1:I9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -4048,6 +4048,39 @@
       </c>
       <c r="I8">
         <f>IF(H8="","",IF(H8&gt;=70,"BUY",IF(H8&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="31" t="n">
+        <v>46294</v>
+      </c>
+      <c r="B9" s="24" t="n">
+        <v>18919.5</v>
+      </c>
+      <c r="C9" s="25" t="n">
+        <v>25.64</v>
+      </c>
+      <c r="D9" s="26" t="n">
+        <v>0.0681818181818</v>
+      </c>
+      <c r="E9" s="26" t="n">
+        <v>0.0133585855075</v>
+      </c>
+      <c r="F9" s="34">
+        <f>IF(D9="","",100*(1-D9))</f>
+        <v/>
+      </c>
+      <c r="G9" s="34">
+        <f>IF(E9="","",IF(E9&lt;=0,20,IF(E9&lt;5%,20+400*E9,IF(E9&lt;10%,40+400*(E9-5%),IF(E9&lt;15%,60+400*(E9-10%),IF(E9&lt;25%,80+200*(E9-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H9" s="34">
+        <f>IF(OR(F9="",G9=""),"",70%*F9+30%*G9)</f>
+        <v/>
+      </c>
+      <c r="I9">
+        <f>IF(H9="","",IF(H9&gt;=70,"BUY",IF(H9&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -4088,7 +4121,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-09-28</t>
+          <t>Retrieved 2026-09-29</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">

--- a/docs/downloads/indices/nifty200-quality-30.xlsx
+++ b/docs/downloads/indices/nifty200-quality-30.xlsx
@@ -568,7 +568,7 @@
     <col width="34" customWidth="1" min="1" max="1"/>
     <col width="34" customWidth="1" min="2" max="2"/>
     <col width="24" customWidth="1" min="3" max="3"/>
-    <col width="21" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
     <col width="29" customWidth="1" min="5" max="5"/>
     <col width="17" customWidth="1" min="6" max="6"/>
     <col width="19" customWidth="1" min="7" max="7"/>
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>18919.5</v>
+        <v>18943.05</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>25.64</v>
+        <v>25.66</v>
       </c>
     </row>
     <row r="6">
@@ -633,7 +633,7 @@
         </is>
       </c>
       <c r="B6" s="26" t="n">
-        <v>0.06818181818181818</v>
+        <v>0.07462686567164178</v>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>737.890015600624</v>
+        <v>738.2326578332033</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.01335858550754776</v>
+        <v>0.0141316331278003</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.0390015600624025</v>
+        <v>0.03897116134060795</v>
       </c>
     </row>
     <row r="8">
@@ -669,7 +669,7 @@
         </is>
       </c>
       <c r="B8" s="28" t="n">
-        <v>93.18181818181819</v>
+        <v>92.53731343283582</v>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
@@ -677,7 +677,7 @@
         </is>
       </c>
       <c r="E8" s="28" t="n">
-        <v>25.3434342030191</v>
+        <v>25.65265325112012</v>
       </c>
     </row>
     <row r="9">
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>72.83030298817846</v>
+        <v>72.47191537832111</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -736,13 +736,13 @@
         </is>
       </c>
       <c r="B13" s="29" t="n">
-        <v>26.49419696695887</v>
+        <v>26.46024144821267</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>19549.80341327529</v>
+        <v>19533.81437122233</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>0.03331501431196848</v>
+        <v>0.03118633858973752</v>
       </c>
     </row>
     <row r="14">
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="B14" s="29" t="n">
-        <v>29.55917099527984</v>
+        <v>29.55541750491031</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>21811.41714684855</v>
+        <v>21818.77441801992</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>0.1528537829672323</v>
+        <v>0.151808944072888</v>
       </c>
     </row>
     <row r="16">
@@ -815,10 +815,10 @@
         <v>6</v>
       </c>
       <c r="C18" s="30" t="n">
-        <v>0.3243788351336814</v>
+        <v>0.3270908331935936</v>
       </c>
       <c r="D18" s="30" t="n">
-        <v>0.1350458114630114</v>
+        <v>0.1464746057360189</v>
       </c>
       <c r="E18" s="30" t="n">
         <v>0.1841677233393925</v>
@@ -835,13 +835,13 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C19" s="30" t="n">
-        <v>0.131826119588194</v>
+        <v>0.1965789745334703</v>
       </c>
       <c r="D19" s="30" t="n">
-        <v>0.1375752715747722</v>
+        <v>0.1125746946104988</v>
       </c>
       <c r="E19" s="30" t="n">
         <v>0.1797087246808945</v>
@@ -858,10 +858,10 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C20" s="30" t="n">
-        <v>0.002608895744658335</v>
+        <v>-0.03763539237090535</v>
       </c>
       <c r="D20" s="30" t="n">
         <v>0.1297583507672395</v>
@@ -881,16 +881,16 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C21" s="30" t="n">
-        <v>-0.03771959588046353</v>
+        <v>-0.02643480073401039</v>
       </c>
       <c r="D21" s="30" t="n">
         <v>0.1421152387233346</v>
       </c>
       <c r="E21" s="30" t="n">
-        <v>0.09409439304594247</v>
+        <v>0.07940010781138862</v>
       </c>
       <c r="F21" s="30" t="n"/>
       <c r="G21" s="30" t="n">
@@ -934,7 +934,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="26">
@@ -944,7 +944,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="27">
@@ -967,7 +967,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-09-30</t>
         </is>
       </c>
     </row>
@@ -1017,7 +1017,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E66"/>
+  <dimension ref="A1:E67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -2286,6 +2286,25 @@
       </c>
       <c r="E66" s="20">
         <f>IFERROR(1/C66,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="31" t="n">
+        <v>46295</v>
+      </c>
+      <c r="B67" s="24" t="n">
+        <v>18943.05</v>
+      </c>
+      <c r="C67" s="25" t="n">
+        <v>25.66</v>
+      </c>
+      <c r="D67" s="32">
+        <f>IFERROR(B67/C67,"")</f>
+        <v/>
+      </c>
+      <c r="E67" s="20">
+        <f>IFERROR(1/C67,"")</f>
         <v/>
       </c>
     </row>
@@ -2302,7 +2321,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:L34"/>
+  <dimension ref="A1:L35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -2402,7 +2421,7 @@
       </c>
       <c r="F2" s="30" t="n"/>
       <c r="G2" s="30">
-        <f>IF(C2="","",(COUNTIFS($D$2:$D$34,D2,$C$2:$C$34,"&gt;0",$C$2:$C$34,"&lt;"&amp;C2)+(COUNTIFS($D$2:$D$34,D2,$C$2:$C$34,C2)+1)/2)/COUNTIFS($D$2:$D$34,D2,$C$2:$C$34,"&gt;0"))</f>
+        <f>IF(C2="","",(COUNTIFS($D$2:$D$35,D2,$C$2:$C$35,"&gt;0",$C$2:$C$35,"&lt;"&amp;C2)+(COUNTIFS($D$2:$D$35,D2,$C$2:$C$35,C2)+1)/2)/COUNTIFS($D$2:$D$35,D2,$C$2:$C$35,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H2">
@@ -2444,7 +2463,7 @@
       </c>
       <c r="F3" s="30" t="n"/>
       <c r="G3" s="30">
-        <f>IF(C3="","",(COUNTIFS($D$2:$D$34,D3,$C$2:$C$34,"&gt;0",$C$2:$C$34,"&lt;"&amp;C3)+(COUNTIFS($D$2:$D$34,D3,$C$2:$C$34,C3)+1)/2)/COUNTIFS($D$2:$D$34,D3,$C$2:$C$34,"&gt;0"))</f>
+        <f>IF(C3="","",(COUNTIFS($D$2:$D$35,D3,$C$2:$C$35,"&gt;0",$C$2:$C$35,"&lt;"&amp;C3)+(COUNTIFS($D$2:$D$35,D3,$C$2:$C$35,C3)+1)/2)/COUNTIFS($D$2:$D$35,D3,$C$2:$C$35,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H3">
@@ -2486,7 +2505,7 @@
       </c>
       <c r="F4" s="30" t="n"/>
       <c r="G4" s="30">
-        <f>IF(C4="","",(COUNTIFS($D$2:$D$34,D4,$C$2:$C$34,"&gt;0",$C$2:$C$34,"&lt;"&amp;C4)+(COUNTIFS($D$2:$D$34,D4,$C$2:$C$34,C4)+1)/2)/COUNTIFS($D$2:$D$34,D4,$C$2:$C$34,"&gt;0"))</f>
+        <f>IF(C4="","",(COUNTIFS($D$2:$D$35,D4,$C$2:$C$35,"&gt;0",$C$2:$C$35,"&lt;"&amp;C4)+(COUNTIFS($D$2:$D$35,D4,$C$2:$C$35,C4)+1)/2)/COUNTIFS($D$2:$D$35,D4,$C$2:$C$35,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H4">
@@ -2528,7 +2547,7 @@
       </c>
       <c r="F5" s="30" t="n"/>
       <c r="G5" s="30">
-        <f>IF(C5="","",(COUNTIFS($D$2:$D$34,D5,$C$2:$C$34,"&gt;0",$C$2:$C$34,"&lt;"&amp;C5)+(COUNTIFS($D$2:$D$34,D5,$C$2:$C$34,C5)+1)/2)/COUNTIFS($D$2:$D$34,D5,$C$2:$C$34,"&gt;0"))</f>
+        <f>IF(C5="","",(COUNTIFS($D$2:$D$35,D5,$C$2:$C$35,"&gt;0",$C$2:$C$35,"&lt;"&amp;C5)+(COUNTIFS($D$2:$D$35,D5,$C$2:$C$35,C5)+1)/2)/COUNTIFS($D$2:$D$35,D5,$C$2:$C$35,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H5">
@@ -2573,7 +2592,7 @@
         <v/>
       </c>
       <c r="G6" s="30">
-        <f>IF(C6="","",(COUNTIFS($D$2:$D$34,D6,$C$2:$C$34,"&gt;0",$C$2:$C$34,"&lt;"&amp;C6)+(COUNTIFS($D$2:$D$34,D6,$C$2:$C$34,C6)+1)/2)/COUNTIFS($D$2:$D$34,D6,$C$2:$C$34,"&gt;0"))</f>
+        <f>IF(C6="","",(COUNTIFS($D$2:$D$35,D6,$C$2:$C$35,"&gt;0",$C$2:$C$35,"&lt;"&amp;C6)+(COUNTIFS($D$2:$D$35,D6,$C$2:$C$35,C6)+1)/2)/COUNTIFS($D$2:$D$35,D6,$C$2:$C$35,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H6">
@@ -2618,7 +2637,7 @@
         <v/>
       </c>
       <c r="G7" s="30">
-        <f>IF(C7="","",(COUNTIFS($D$2:$D$34,D7,$C$2:$C$34,"&gt;0",$C$2:$C$34,"&lt;"&amp;C7)+(COUNTIFS($D$2:$D$34,D7,$C$2:$C$34,C7)+1)/2)/COUNTIFS($D$2:$D$34,D7,$C$2:$C$34,"&gt;0"))</f>
+        <f>IF(C7="","",(COUNTIFS($D$2:$D$35,D7,$C$2:$C$35,"&gt;0",$C$2:$C$35,"&lt;"&amp;C7)+(COUNTIFS($D$2:$D$35,D7,$C$2:$C$35,C7)+1)/2)/COUNTIFS($D$2:$D$35,D7,$C$2:$C$35,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H7">
@@ -2663,7 +2682,7 @@
         <v/>
       </c>
       <c r="G8" s="30">
-        <f>IF(C8="","",(COUNTIFS($D$2:$D$34,D8,$C$2:$C$34,"&gt;0",$C$2:$C$34,"&lt;"&amp;C8)+(COUNTIFS($D$2:$D$34,D8,$C$2:$C$34,C8)+1)/2)/COUNTIFS($D$2:$D$34,D8,$C$2:$C$34,"&gt;0"))</f>
+        <f>IF(C8="","",(COUNTIFS($D$2:$D$35,D8,$C$2:$C$35,"&gt;0",$C$2:$C$35,"&lt;"&amp;C8)+(COUNTIFS($D$2:$D$35,D8,$C$2:$C$35,C8)+1)/2)/COUNTIFS($D$2:$D$35,D8,$C$2:$C$35,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H8">
@@ -2708,7 +2727,7 @@
         <v/>
       </c>
       <c r="G9" s="30">
-        <f>IF(C9="","",(COUNTIFS($D$2:$D$34,D9,$C$2:$C$34,"&gt;0",$C$2:$C$34,"&lt;"&amp;C9)+(COUNTIFS($D$2:$D$34,D9,$C$2:$C$34,C9)+1)/2)/COUNTIFS($D$2:$D$34,D9,$C$2:$C$34,"&gt;0"))</f>
+        <f>IF(C9="","",(COUNTIFS($D$2:$D$35,D9,$C$2:$C$35,"&gt;0",$C$2:$C$35,"&lt;"&amp;C9)+(COUNTIFS($D$2:$D$35,D9,$C$2:$C$35,C9)+1)/2)/COUNTIFS($D$2:$D$35,D9,$C$2:$C$35,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H9">
@@ -2753,7 +2772,7 @@
         <v/>
       </c>
       <c r="G10" s="30">
-        <f>IF(C10="","",(COUNTIFS($D$2:$D$34,D10,$C$2:$C$34,"&gt;0",$C$2:$C$34,"&lt;"&amp;C10)+(COUNTIFS($D$2:$D$34,D10,$C$2:$C$34,C10)+1)/2)/COUNTIFS($D$2:$D$34,D10,$C$2:$C$34,"&gt;0"))</f>
+        <f>IF(C10="","",(COUNTIFS($D$2:$D$35,D10,$C$2:$C$35,"&gt;0",$C$2:$C$35,"&lt;"&amp;C10)+(COUNTIFS($D$2:$D$35,D10,$C$2:$C$35,C10)+1)/2)/COUNTIFS($D$2:$D$35,D10,$C$2:$C$35,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H10">
@@ -2798,7 +2817,7 @@
         <v/>
       </c>
       <c r="G11" s="30">
-        <f>IF(C11="","",(COUNTIFS($D$2:$D$34,D11,$C$2:$C$34,"&gt;0",$C$2:$C$34,"&lt;"&amp;C11)+(COUNTIFS($D$2:$D$34,D11,$C$2:$C$34,C11)+1)/2)/COUNTIFS($D$2:$D$34,D11,$C$2:$C$34,"&gt;0"))</f>
+        <f>IF(C11="","",(COUNTIFS($D$2:$D$35,D11,$C$2:$C$35,"&gt;0",$C$2:$C$35,"&lt;"&amp;C11)+(COUNTIFS($D$2:$D$35,D11,$C$2:$C$35,C11)+1)/2)/COUNTIFS($D$2:$D$35,D11,$C$2:$C$35,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H11">
@@ -2843,7 +2862,7 @@
         <v/>
       </c>
       <c r="G12" s="30">
-        <f>IF(C12="","",(COUNTIFS($D$2:$D$34,D12,$C$2:$C$34,"&gt;0",$C$2:$C$34,"&lt;"&amp;C12)+(COUNTIFS($D$2:$D$34,D12,$C$2:$C$34,C12)+1)/2)/COUNTIFS($D$2:$D$34,D12,$C$2:$C$34,"&gt;0"))</f>
+        <f>IF(C12="","",(COUNTIFS($D$2:$D$35,D12,$C$2:$C$35,"&gt;0",$C$2:$C$35,"&lt;"&amp;C12)+(COUNTIFS($D$2:$D$35,D12,$C$2:$C$35,C12)+1)/2)/COUNTIFS($D$2:$D$35,D12,$C$2:$C$35,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H12">
@@ -2888,7 +2907,7 @@
         <v/>
       </c>
       <c r="G13" s="30">
-        <f>IF(C13="","",(COUNTIFS($D$2:$D$34,D13,$C$2:$C$34,"&gt;0",$C$2:$C$34,"&lt;"&amp;C13)+(COUNTIFS($D$2:$D$34,D13,$C$2:$C$34,C13)+1)/2)/COUNTIFS($D$2:$D$34,D13,$C$2:$C$34,"&gt;0"))</f>
+        <f>IF(C13="","",(COUNTIFS($D$2:$D$35,D13,$C$2:$C$35,"&gt;0",$C$2:$C$35,"&lt;"&amp;C13)+(COUNTIFS($D$2:$D$35,D13,$C$2:$C$35,C13)+1)/2)/COUNTIFS($D$2:$D$35,D13,$C$2:$C$35,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H13">
@@ -2933,7 +2952,7 @@
         <v/>
       </c>
       <c r="G14" s="30">
-        <f>IF(C14="","",(COUNTIFS($D$2:$D$34,D14,$C$2:$C$34,"&gt;0",$C$2:$C$34,"&lt;"&amp;C14)+(COUNTIFS($D$2:$D$34,D14,$C$2:$C$34,C14)+1)/2)/COUNTIFS($D$2:$D$34,D14,$C$2:$C$34,"&gt;0"))</f>
+        <f>IF(C14="","",(COUNTIFS($D$2:$D$35,D14,$C$2:$C$35,"&gt;0",$C$2:$C$35,"&lt;"&amp;C14)+(COUNTIFS($D$2:$D$35,D14,$C$2:$C$35,C14)+1)/2)/COUNTIFS($D$2:$D$35,D14,$C$2:$C$35,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H14">
@@ -2978,7 +2997,7 @@
         <v/>
       </c>
       <c r="G15" s="30">
-        <f>IF(C15="","",(COUNTIFS($D$2:$D$34,D15,$C$2:$C$34,"&gt;0",$C$2:$C$34,"&lt;"&amp;C15)+(COUNTIFS($D$2:$D$34,D15,$C$2:$C$34,C15)+1)/2)/COUNTIFS($D$2:$D$34,D15,$C$2:$C$34,"&gt;0"))</f>
+        <f>IF(C15="","",(COUNTIFS($D$2:$D$35,D15,$C$2:$C$35,"&gt;0",$C$2:$C$35,"&lt;"&amp;C15)+(COUNTIFS($D$2:$D$35,D15,$C$2:$C$35,C15)+1)/2)/COUNTIFS($D$2:$D$35,D15,$C$2:$C$35,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H15">
@@ -2993,7 +3012,10 @@
         <f>IFERROR((B27/B15)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K15" s="30" t="n"/>
+      <c r="K15" s="30">
+        <f>IFERROR((B35/B15)^(1/5)-1,"")</f>
+        <v/>
+      </c>
       <c r="L15" s="30" t="n"/>
     </row>
     <row r="16">
@@ -3020,7 +3042,7 @@
         <v/>
       </c>
       <c r="G16" s="30">
-        <f>IF(C16="","",(COUNTIFS($D$2:$D$34,D16,$C$2:$C$34,"&gt;0",$C$2:$C$34,"&lt;"&amp;C16)+(COUNTIFS($D$2:$D$34,D16,$C$2:$C$34,C16)+1)/2)/COUNTIFS($D$2:$D$34,D16,$C$2:$C$34,"&gt;0"))</f>
+        <f>IF(C16="","",(COUNTIFS($D$2:$D$35,D16,$C$2:$C$35,"&gt;0",$C$2:$C$35,"&lt;"&amp;C16)+(COUNTIFS($D$2:$D$35,D16,$C$2:$C$35,C16)+1)/2)/COUNTIFS($D$2:$D$35,D16,$C$2:$C$35,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H16">
@@ -3062,7 +3084,7 @@
         <v/>
       </c>
       <c r="G17" s="30">
-        <f>IF(C17="","",(COUNTIFS($D$2:$D$34,D17,$C$2:$C$34,"&gt;0",$C$2:$C$34,"&lt;"&amp;C17)+(COUNTIFS($D$2:$D$34,D17,$C$2:$C$34,C17)+1)/2)/COUNTIFS($D$2:$D$34,D17,$C$2:$C$34,"&gt;0"))</f>
+        <f>IF(C17="","",(COUNTIFS($D$2:$D$35,D17,$C$2:$C$35,"&gt;0",$C$2:$C$35,"&lt;"&amp;C17)+(COUNTIFS($D$2:$D$35,D17,$C$2:$C$35,C17)+1)/2)/COUNTIFS($D$2:$D$35,D17,$C$2:$C$35,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H17">
@@ -3104,7 +3126,7 @@
         <v/>
       </c>
       <c r="G18" s="30">
-        <f>IF(C18="","",(COUNTIFS($D$2:$D$34,D18,$C$2:$C$34,"&gt;0",$C$2:$C$34,"&lt;"&amp;C18)+(COUNTIFS($D$2:$D$34,D18,$C$2:$C$34,C18)+1)/2)/COUNTIFS($D$2:$D$34,D18,$C$2:$C$34,"&gt;0"))</f>
+        <f>IF(C18="","",(COUNTIFS($D$2:$D$35,D18,$C$2:$C$35,"&gt;0",$C$2:$C$35,"&lt;"&amp;C18)+(COUNTIFS($D$2:$D$35,D18,$C$2:$C$35,C18)+1)/2)/COUNTIFS($D$2:$D$35,D18,$C$2:$C$35,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H18">
@@ -3146,7 +3168,7 @@
         <v/>
       </c>
       <c r="G19" s="30">
-        <f>IF(C19="","",(COUNTIFS($D$2:$D$34,D19,$C$2:$C$34,"&gt;0",$C$2:$C$34,"&lt;"&amp;C19)+(COUNTIFS($D$2:$D$34,D19,$C$2:$C$34,C19)+1)/2)/COUNTIFS($D$2:$D$34,D19,$C$2:$C$34,"&gt;0"))</f>
+        <f>IF(C19="","",(COUNTIFS($D$2:$D$35,D19,$C$2:$C$35,"&gt;0",$C$2:$C$35,"&lt;"&amp;C19)+(COUNTIFS($D$2:$D$35,D19,$C$2:$C$35,C19)+1)/2)/COUNTIFS($D$2:$D$35,D19,$C$2:$C$35,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H19">
@@ -3188,7 +3210,7 @@
         <v/>
       </c>
       <c r="G20" s="30">
-        <f>IF(C20="","",(COUNTIFS($D$2:$D$34,D20,$C$2:$C$34,"&gt;0",$C$2:$C$34,"&lt;"&amp;C20)+(COUNTIFS($D$2:$D$34,D20,$C$2:$C$34,C20)+1)/2)/COUNTIFS($D$2:$D$34,D20,$C$2:$C$34,"&gt;0"))</f>
+        <f>IF(C20="","",(COUNTIFS($D$2:$D$35,D20,$C$2:$C$35,"&gt;0",$C$2:$C$35,"&lt;"&amp;C20)+(COUNTIFS($D$2:$D$35,D20,$C$2:$C$35,C20)+1)/2)/COUNTIFS($D$2:$D$35,D20,$C$2:$C$35,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H20">
@@ -3230,7 +3252,7 @@
         <v/>
       </c>
       <c r="G21" s="30">
-        <f>IF(C21="","",(COUNTIFS($D$2:$D$34,D21,$C$2:$C$34,"&gt;0",$C$2:$C$34,"&lt;"&amp;C21)+(COUNTIFS($D$2:$D$34,D21,$C$2:$C$34,C21)+1)/2)/COUNTIFS($D$2:$D$34,D21,$C$2:$C$34,"&gt;0"))</f>
+        <f>IF(C21="","",(COUNTIFS($D$2:$D$35,D21,$C$2:$C$35,"&gt;0",$C$2:$C$35,"&lt;"&amp;C21)+(COUNTIFS($D$2:$D$35,D21,$C$2:$C$35,C21)+1)/2)/COUNTIFS($D$2:$D$35,D21,$C$2:$C$35,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H21">
@@ -3272,7 +3294,7 @@
         <v/>
       </c>
       <c r="G22" s="30">
-        <f>IF(C22="","",(COUNTIFS($D$2:$D$34,D22,$C$2:$C$34,"&gt;0",$C$2:$C$34,"&lt;"&amp;C22)+(COUNTIFS($D$2:$D$34,D22,$C$2:$C$34,C22)+1)/2)/COUNTIFS($D$2:$D$34,D22,$C$2:$C$34,"&gt;0"))</f>
+        <f>IF(C22="","",(COUNTIFS($D$2:$D$35,D22,$C$2:$C$35,"&gt;0",$C$2:$C$35,"&lt;"&amp;C22)+(COUNTIFS($D$2:$D$35,D22,$C$2:$C$35,C22)+1)/2)/COUNTIFS($D$2:$D$35,D22,$C$2:$C$35,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H22">
@@ -3314,7 +3336,7 @@
         <v/>
       </c>
       <c r="G23" s="30">
-        <f>IF(C23="","",(COUNTIFS($D$2:$D$34,D23,$C$2:$C$34,"&gt;0",$C$2:$C$34,"&lt;"&amp;C23)+(COUNTIFS($D$2:$D$34,D23,$C$2:$C$34,C23)+1)/2)/COUNTIFS($D$2:$D$34,D23,$C$2:$C$34,"&gt;0"))</f>
+        <f>IF(C23="","",(COUNTIFS($D$2:$D$35,D23,$C$2:$C$35,"&gt;0",$C$2:$C$35,"&lt;"&amp;C23)+(COUNTIFS($D$2:$D$35,D23,$C$2:$C$35,C23)+1)/2)/COUNTIFS($D$2:$D$35,D23,$C$2:$C$35,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H23">
@@ -3325,7 +3347,10 @@
         <f>IFERROR(B27/B23-1,"")</f>
         <v/>
       </c>
-      <c r="J23" s="30" t="n"/>
+      <c r="J23" s="30">
+        <f>IFERROR((B35/B23)^(1/3)-1,"")</f>
+        <v/>
+      </c>
       <c r="K23" s="30" t="n"/>
       <c r="L23" s="30" t="n"/>
     </row>
@@ -3353,7 +3378,7 @@
         <v/>
       </c>
       <c r="G24" s="30">
-        <f>IF(C24="","",(COUNTIFS($D$2:$D$34,D24,$C$2:$C$34,"&gt;0",$C$2:$C$34,"&lt;"&amp;C24)+(COUNTIFS($D$2:$D$34,D24,$C$2:$C$34,C24)+1)/2)/COUNTIFS($D$2:$D$34,D24,$C$2:$C$34,"&gt;0"))</f>
+        <f>IF(C24="","",(COUNTIFS($D$2:$D$35,D24,$C$2:$C$35,"&gt;0",$C$2:$C$35,"&lt;"&amp;C24)+(COUNTIFS($D$2:$D$35,D24,$C$2:$C$35,C24)+1)/2)/COUNTIFS($D$2:$D$35,D24,$C$2:$C$35,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H24">
@@ -3392,7 +3417,7 @@
         <v/>
       </c>
       <c r="G25" s="30">
-        <f>IF(C25="","",(COUNTIFS($D$2:$D$34,D25,$C$2:$C$34,"&gt;0",$C$2:$C$34,"&lt;"&amp;C25)+(COUNTIFS($D$2:$D$34,D25,$C$2:$C$34,C25)+1)/2)/COUNTIFS($D$2:$D$34,D25,$C$2:$C$34,"&gt;0"))</f>
+        <f>IF(C25="","",(COUNTIFS($D$2:$D$35,D25,$C$2:$C$35,"&gt;0",$C$2:$C$35,"&lt;"&amp;C25)+(COUNTIFS($D$2:$D$35,D25,$C$2:$C$35,C25)+1)/2)/COUNTIFS($D$2:$D$35,D25,$C$2:$C$35,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H25">
@@ -3431,7 +3456,7 @@
         <v/>
       </c>
       <c r="G26" s="30">
-        <f>IF(C26="","",(COUNTIFS($D$2:$D$34,D26,$C$2:$C$34,"&gt;0",$C$2:$C$34,"&lt;"&amp;C26)+(COUNTIFS($D$2:$D$34,D26,$C$2:$C$34,C26)+1)/2)/COUNTIFS($D$2:$D$34,D26,$C$2:$C$34,"&gt;0"))</f>
+        <f>IF(C26="","",(COUNTIFS($D$2:$D$35,D26,$C$2:$C$35,"&gt;0",$C$2:$C$35,"&lt;"&amp;C26)+(COUNTIFS($D$2:$D$35,D26,$C$2:$C$35,C26)+1)/2)/COUNTIFS($D$2:$D$35,D26,$C$2:$C$35,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H26">
@@ -3470,7 +3495,7 @@
         <v/>
       </c>
       <c r="G27" s="30">
-        <f>IF(C27="","",(COUNTIFS($D$2:$D$34,D27,$C$2:$C$34,"&gt;0",$C$2:$C$34,"&lt;"&amp;C27)+(COUNTIFS($D$2:$D$34,D27,$C$2:$C$34,C27)+1)/2)/COUNTIFS($D$2:$D$34,D27,$C$2:$C$34,"&gt;0"))</f>
+        <f>IF(C27="","",(COUNTIFS($D$2:$D$35,D27,$C$2:$C$35,"&gt;0",$C$2:$C$35,"&lt;"&amp;C27)+(COUNTIFS($D$2:$D$35,D27,$C$2:$C$35,C27)+1)/2)/COUNTIFS($D$2:$D$35,D27,$C$2:$C$35,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H27">
@@ -3509,7 +3534,7 @@
         <v/>
       </c>
       <c r="G28" s="30">
-        <f>IF(C28="","",(COUNTIFS($D$2:$D$34,D28,$C$2:$C$34,"&gt;0",$C$2:$C$34,"&lt;"&amp;C28)+(COUNTIFS($D$2:$D$34,D28,$C$2:$C$34,C28)+1)/2)/COUNTIFS($D$2:$D$34,D28,$C$2:$C$34,"&gt;0"))</f>
+        <f>IF(C28="","",(COUNTIFS($D$2:$D$35,D28,$C$2:$C$35,"&gt;0",$C$2:$C$35,"&lt;"&amp;C28)+(COUNTIFS($D$2:$D$35,D28,$C$2:$C$35,C28)+1)/2)/COUNTIFS($D$2:$D$35,D28,$C$2:$C$35,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H28">
@@ -3548,7 +3573,7 @@
         <v/>
       </c>
       <c r="G29" s="30">
-        <f>IF(C29="","",(COUNTIFS($D$2:$D$34,D29,$C$2:$C$34,"&gt;0",$C$2:$C$34,"&lt;"&amp;C29)+(COUNTIFS($D$2:$D$34,D29,$C$2:$C$34,C29)+1)/2)/COUNTIFS($D$2:$D$34,D29,$C$2:$C$34,"&gt;0"))</f>
+        <f>IF(C29="","",(COUNTIFS($D$2:$D$35,D29,$C$2:$C$35,"&gt;0",$C$2:$C$35,"&lt;"&amp;C29)+(COUNTIFS($D$2:$D$35,D29,$C$2:$C$35,C29)+1)/2)/COUNTIFS($D$2:$D$35,D29,$C$2:$C$35,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H29">
@@ -3587,7 +3612,7 @@
         <v/>
       </c>
       <c r="G30" s="30">
-        <f>IF(C30="","",(COUNTIFS($D$2:$D$34,D30,$C$2:$C$34,"&gt;0",$C$2:$C$34,"&lt;"&amp;C30)+(COUNTIFS($D$2:$D$34,D30,$C$2:$C$34,C30)+1)/2)/COUNTIFS($D$2:$D$34,D30,$C$2:$C$34,"&gt;0"))</f>
+        <f>IF(C30="","",(COUNTIFS($D$2:$D$35,D30,$C$2:$C$35,"&gt;0",$C$2:$C$35,"&lt;"&amp;C30)+(COUNTIFS($D$2:$D$35,D30,$C$2:$C$35,C30)+1)/2)/COUNTIFS($D$2:$D$35,D30,$C$2:$C$35,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H30">
@@ -3626,14 +3651,17 @@
         <v/>
       </c>
       <c r="G31" s="30">
-        <f>IF(C31="","",(COUNTIFS($D$2:$D$34,D31,$C$2:$C$34,"&gt;0",$C$2:$C$34,"&lt;"&amp;C31)+(COUNTIFS($D$2:$D$34,D31,$C$2:$C$34,C31)+1)/2)/COUNTIFS($D$2:$D$34,D31,$C$2:$C$34,"&gt;0"))</f>
+        <f>IF(C31="","",(COUNTIFS($D$2:$D$35,D31,$C$2:$C$35,"&gt;0",$C$2:$C$35,"&lt;"&amp;C31)+(COUNTIFS($D$2:$D$35,D31,$C$2:$C$35,C31)+1)/2)/COUNTIFS($D$2:$D$35,D31,$C$2:$C$35,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H31">
         <f>IF(G31="","",IF(G31&lt;=20%,"Q1 Cheapest",IF(G31&lt;=40%,"Q2",IF(G31&lt;=60%,"Q3",IF(G31&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I31" s="30" t="n"/>
+      <c r="I31" s="30">
+        <f>IFERROR(B35/B31-1,"")</f>
+        <v/>
+      </c>
       <c r="J31" s="30" t="n"/>
       <c r="K31" s="30" t="n"/>
       <c r="L31" s="30" t="n"/>
@@ -3662,7 +3690,7 @@
         <v/>
       </c>
       <c r="G32" s="30">
-        <f>IF(C32="","",(COUNTIFS($D$2:$D$34,D32,$C$2:$C$34,"&gt;0",$C$2:$C$34,"&lt;"&amp;C32)+(COUNTIFS($D$2:$D$34,D32,$C$2:$C$34,C32)+1)/2)/COUNTIFS($D$2:$D$34,D32,$C$2:$C$34,"&gt;0"))</f>
+        <f>IF(C32="","",(COUNTIFS($D$2:$D$35,D32,$C$2:$C$35,"&gt;0",$C$2:$C$35,"&lt;"&amp;C32)+(COUNTIFS($D$2:$D$35,D32,$C$2:$C$35,C32)+1)/2)/COUNTIFS($D$2:$D$35,D32,$C$2:$C$35,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H32">
@@ -3698,7 +3726,7 @@
         <v/>
       </c>
       <c r="G33" s="30">
-        <f>IF(C33="","",(COUNTIFS($D$2:$D$34,D33,$C$2:$C$34,"&gt;0",$C$2:$C$34,"&lt;"&amp;C33)+(COUNTIFS($D$2:$D$34,D33,$C$2:$C$34,C33)+1)/2)/COUNTIFS($D$2:$D$34,D33,$C$2:$C$34,"&gt;0"))</f>
+        <f>IF(C33="","",(COUNTIFS($D$2:$D$35,D33,$C$2:$C$35,"&gt;0",$C$2:$C$35,"&lt;"&amp;C33)+(COUNTIFS($D$2:$D$35,D33,$C$2:$C$35,C33)+1)/2)/COUNTIFS($D$2:$D$35,D33,$C$2:$C$35,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H33">
@@ -3734,7 +3762,7 @@
         <v/>
       </c>
       <c r="G34" s="30">
-        <f>IF(C34="","",(COUNTIFS($D$2:$D$34,D34,$C$2:$C$34,"&gt;0",$C$2:$C$34,"&lt;"&amp;C34)+(COUNTIFS($D$2:$D$34,D34,$C$2:$C$34,C34)+1)/2)/COUNTIFS($D$2:$D$34,D34,$C$2:$C$34,"&gt;0"))</f>
+        <f>IF(C34="","",(COUNTIFS($D$2:$D$35,D34,$C$2:$C$35,"&gt;0",$C$2:$C$35,"&lt;"&amp;C34)+(COUNTIFS($D$2:$D$35,D34,$C$2:$C$35,C34)+1)/2)/COUNTIFS($D$2:$D$35,D34,$C$2:$C$35,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H34">
@@ -3745,6 +3773,42 @@
       <c r="J34" s="30" t="n"/>
       <c r="K34" s="30" t="n"/>
       <c r="L34" s="30" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="31" t="n">
+        <v>46295</v>
+      </c>
+      <c r="B35" s="24" t="n">
+        <v>18943.05</v>
+      </c>
+      <c r="C35" s="25" t="n">
+        <v>25.66</v>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>Consolidated</t>
+        </is>
+      </c>
+      <c r="E35" s="33">
+        <f>IFERROR(B35/C35,"")</f>
+        <v/>
+      </c>
+      <c r="F35" s="30">
+        <f>IF(AND(D35=D31,E31&lt;&gt;""),E35/E31-1,"")</f>
+        <v/>
+      </c>
+      <c r="G35" s="30">
+        <f>IF(C35="","",(COUNTIFS($D$2:$D$35,D35,$C$2:$C$35,"&gt;0",$C$2:$C$35,"&lt;"&amp;C35)+(COUNTIFS($D$2:$D$35,D35,$C$2:$C$35,C35)+1)/2)/COUNTIFS($D$2:$D$35,D35,$C$2:$C$35,"&gt;0"))</f>
+        <v/>
+      </c>
+      <c r="H35">
+        <f>IF(G35="","",IF(G35&lt;=20%,"Q1 Cheapest",IF(G35&lt;=40%,"Q2",IF(G35&lt;=60%,"Q3",IF(G35&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
+        <v/>
+      </c>
+      <c r="I35" s="30" t="n"/>
+      <c r="J35" s="30" t="n"/>
+      <c r="K35" s="30" t="n"/>
+      <c r="L35" s="30" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.3" right="0.3" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>
@@ -3759,7 +3823,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I9"/>
+  <dimension ref="A1:I10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -3767,7 +3831,7 @@
     <col width="10" customWidth="1" min="3" max="3"/>
     <col width="17" customWidth="1" min="4" max="4"/>
     <col width="17" customWidth="1" min="5" max="5"/>
-    <col width="26" customWidth="1" min="6" max="6"/>
+    <col width="28" customWidth="1" min="6" max="6"/>
     <col width="34" customWidth="1" min="7" max="7"/>
     <col width="34" customWidth="1" min="8" max="8"/>
     <col width="34" customWidth="1" min="9" max="9"/>
@@ -4081,6 +4145,39 @@
       </c>
       <c r="I9">
         <f>IF(H9="","",IF(H9&gt;=70,"BUY",IF(H9&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="31" t="n">
+        <v>46295</v>
+      </c>
+      <c r="B10" s="24" t="n">
+        <v>18943.05</v>
+      </c>
+      <c r="C10" s="25" t="n">
+        <v>25.66</v>
+      </c>
+      <c r="D10" s="26" t="n">
+        <v>0.0746268656716</v>
+      </c>
+      <c r="E10" s="26" t="n">
+        <v>0.0141316331278</v>
+      </c>
+      <c r="F10" s="34">
+        <f>IF(D10="","",100*(1-D10))</f>
+        <v/>
+      </c>
+      <c r="G10" s="34">
+        <f>IF(E10="","",IF(E10&lt;=0,20,IF(E10&lt;5%,20+400*E10,IF(E10&lt;10%,40+400*(E10-5%),IF(E10&lt;15%,60+400*(E10-10%),IF(E10&lt;25%,80+200*(E10-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H10" s="34">
+        <f>IF(OR(F10="",G10=""),"",70%*F10+30%*G10)</f>
+        <v/>
+      </c>
+      <c r="I10">
+        <f>IF(H10="","",IF(H10&gt;=70,"BUY",IF(H10&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -4121,7 +4218,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-09-29</t>
+          <t>Retrieved 2026-09-30</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">

--- a/docs/downloads/indices/nifty200-quality-30.xlsx
+++ b/docs/downloads/indices/nifty200-quality-30.xlsx
@@ -568,7 +568,7 @@
     <col width="34" customWidth="1" min="1" max="1"/>
     <col width="34" customWidth="1" min="2" max="2"/>
     <col width="24" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="21" customWidth="1" min="4" max="4"/>
     <col width="29" customWidth="1" min="5" max="5"/>
     <col width="17" customWidth="1" min="6" max="6"/>
     <col width="19" customWidth="1" min="7" max="7"/>
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>18943.05</v>
+        <v>18803.9</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>25.66</v>
+        <v>25.47</v>
       </c>
     </row>
     <row r="6">
@@ -633,7 +633,7 @@
         </is>
       </c>
       <c r="B6" s="26" t="n">
-        <v>0.07462686567164178</v>
+        <v>0.06716417910447761</v>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>738.2326578332033</v>
+        <v>738.2764036120927</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.0141316331278003</v>
+        <v>0.0142256254978621</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.03897116134060795</v>
+        <v>0.03926187671770711</v>
       </c>
     </row>
     <row r="8">
@@ -669,7 +669,7 @@
         </is>
       </c>
       <c r="B8" s="28" t="n">
-        <v>92.53731343283582</v>
+        <v>93.28358208955224</v>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
@@ -677,7 +677,7 @@
         </is>
       </c>
       <c r="E8" s="28" t="n">
-        <v>25.65265325112012</v>
+        <v>25.69025019914484</v>
       </c>
     </row>
     <row r="9">
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>72.47191537832111</v>
+        <v>73.00558252243002</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -736,13 +736,13 @@
         </is>
       </c>
       <c r="B13" s="29" t="n">
-        <v>26.46024144821267</v>
+        <v>26.46066683082461</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>19533.81437122233</v>
+        <v>19535.28594503898</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>0.03118633858973752</v>
+        <v>0.03889543898015746</v>
       </c>
     </row>
     <row r="14">
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="B14" s="29" t="n">
-        <v>29.55541750491031</v>
+        <v>29.5555238505633</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>21818.77441801992</v>
+        <v>21820.1458552653</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>0.151808944072888</v>
+        <v>0.1604053337480682</v>
       </c>
     </row>
     <row r="16">
@@ -3823,7 +3823,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I10"/>
+  <dimension ref="A1:I11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -4178,6 +4178,39 @@
       </c>
       <c r="I10">
         <f>IF(H10="","",IF(H10&gt;=70,"BUY",IF(H10&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="31" t="n">
+        <v>46296</v>
+      </c>
+      <c r="B11" s="24" t="n">
+        <v>18803.9</v>
+      </c>
+      <c r="C11" s="25" t="n">
+        <v>25.47</v>
+      </c>
+      <c r="D11" s="26" t="n">
+        <v>0.0671641791045</v>
+      </c>
+      <c r="E11" s="26" t="n">
+        <v>0.0142256254979</v>
+      </c>
+      <c r="F11" s="34">
+        <f>IF(D11="","",100*(1-D11))</f>
+        <v/>
+      </c>
+      <c r="G11" s="34">
+        <f>IF(E11="","",IF(E11&lt;=0,20,IF(E11&lt;5%,20+400*E11,IF(E11&lt;10%,40+400*(E11-5%),IF(E11&lt;15%,60+400*(E11-10%),IF(E11&lt;25%,80+200*(E11-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H11" s="34">
+        <f>IF(OR(F11="",G11=""),"",70%*F11+30%*G11)</f>
+        <v/>
+      </c>
+      <c r="I11">
+        <f>IF(H11="","",IF(H11&gt;=70,"BUY",IF(H11&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -4218,7 +4251,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-09-30</t>
+          <t>Retrieved 2026-10-01</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">

--- a/docs/downloads/indices/nifty200-quality-30.xlsx
+++ b/docs/downloads/indices/nifty200-quality-30.xlsx
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46296</v>
+        <v>46300</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>18803.9</v>
+        <v>18905.4</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>25.47</v>
+        <v>25.61</v>
       </c>
     </row>
     <row r="6">
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>738.2764036120927</v>
+        <v>738.2038266302227</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.0142256254978621</v>
+        <v>0.01402857188791029</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.03926187671770711</v>
+        <v>0.03904724716907458</v>
       </c>
     </row>
     <row r="8">
@@ -677,7 +677,7 @@
         </is>
       </c>
       <c r="E8" s="28" t="n">
-        <v>25.69025019914484</v>
+        <v>25.61142875516412</v>
       </c>
     </row>
     <row r="9">
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>73.00558252243002</v>
+        <v>72.98193608923579</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -736,13 +736,13 @@
         </is>
       </c>
       <c r="B13" s="29" t="n">
-        <v>26.46066683082461</v>
+        <v>26.459775022487</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>19535.28594503898</v>
+        <v>19532.70717337469</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>0.03889543898015746</v>
+        <v>0.03318137534115584</v>
       </c>
     </row>
     <row r="14">
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="B14" s="29" t="n">
-        <v>29.5555238505633</v>
+        <v>29.55530089847889</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>21820.1458552653</v>
+        <v>21817.83622046477</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>0.1604053337480682</v>
+        <v>0.1540531393392772</v>
       </c>
     </row>
     <row r="16">
@@ -3823,7 +3823,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I11"/>
+  <dimension ref="A1:I12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -4211,6 +4211,39 @@
       </c>
       <c r="I11">
         <f>IF(H11="","",IF(H11&gt;=70,"BUY",IF(H11&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="31" t="n">
+        <v>46300</v>
+      </c>
+      <c r="B12" s="24" t="n">
+        <v>18905.4</v>
+      </c>
+      <c r="C12" s="25" t="n">
+        <v>25.61</v>
+      </c>
+      <c r="D12" s="26" t="n">
+        <v>0.0671641791045</v>
+      </c>
+      <c r="E12" s="26" t="n">
+        <v>0.0140285718879</v>
+      </c>
+      <c r="F12" s="34">
+        <f>IF(D12="","",100*(1-D12))</f>
+        <v/>
+      </c>
+      <c r="G12" s="34">
+        <f>IF(E12="","",IF(E12&lt;=0,20,IF(E12&lt;5%,20+400*E12,IF(E12&lt;10%,40+400*(E12-5%),IF(E12&lt;15%,60+400*(E12-10%),IF(E12&lt;25%,80+200*(E12-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H12" s="34">
+        <f>IF(OR(F12="",G12=""),"",70%*F12+30%*G12)</f>
+        <v/>
+      </c>
+      <c r="I12">
+        <f>IF(H12="","",IF(H12&gt;=70,"BUY",IF(H12&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -4251,7 +4284,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-10-01</t>
+          <t>Retrieved 2026-10-05</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">

--- a/docs/downloads/indices/nifty200-quality-30.xlsx
+++ b/docs/downloads/indices/nifty200-quality-30.xlsx
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>18905.4</v>
+        <v>19057</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>25.61</v>
+        <v>25.82</v>
       </c>
     </row>
     <row r="6">
@@ -633,7 +633,7 @@
         </is>
       </c>
       <c r="B6" s="26" t="n">
-        <v>0.06716417910447761</v>
+        <v>0.09701492537313433</v>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>738.2038266302227</v>
+        <v>738.0712625871417</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.01402857188791029</v>
+        <v>0.01379595886898954</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.03904724716907458</v>
+        <v>0.03872966692486444</v>
       </c>
     </row>
     <row r="8">
@@ -669,7 +669,7 @@
         </is>
       </c>
       <c r="B8" s="28" t="n">
-        <v>93.28358208955224</v>
+        <v>90.29850746268657</v>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
@@ -677,7 +677,7 @@
         </is>
       </c>
       <c r="E8" s="28" t="n">
-        <v>25.61142875516412</v>
+        <v>25.51838354759582</v>
       </c>
     </row>
     <row r="9">
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>72.98193608923579</v>
+        <v>70.86447028815934</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -736,13 +736,13 @@
         </is>
       </c>
       <c r="B13" s="29" t="n">
-        <v>26.459775022487</v>
+        <v>26.45872228242423</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>19532.70717337469</v>
+        <v>19528.42256143139</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>0.03318137534115584</v>
+        <v>0.02473750125577956</v>
       </c>
     </row>
     <row r="14">
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="B14" s="29" t="n">
-        <v>29.55530089847889</v>
+        <v>29.5550377134632</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>21817.83622046477</v>
+        <v>21813.72400098637</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>0.1540531393392772</v>
+        <v>0.1446567665942371</v>
       </c>
     </row>
     <row r="16">
@@ -3823,7 +3823,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I12"/>
+  <dimension ref="A1:I13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -4244,6 +4244,39 @@
       </c>
       <c r="I12">
         <f>IF(H12="","",IF(H12&gt;=70,"BUY",IF(H12&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="31" t="n">
+        <v>46301</v>
+      </c>
+      <c r="B13" s="24" t="n">
+        <v>19057</v>
+      </c>
+      <c r="C13" s="25" t="n">
+        <v>25.82</v>
+      </c>
+      <c r="D13" s="26" t="n">
+        <v>0.0970149253731</v>
+      </c>
+      <c r="E13" s="26" t="n">
+        <v>0.013795958869</v>
+      </c>
+      <c r="F13" s="34">
+        <f>IF(D13="","",100*(1-D13))</f>
+        <v/>
+      </c>
+      <c r="G13" s="34">
+        <f>IF(E13="","",IF(E13&lt;=0,20,IF(E13&lt;5%,20+400*E13,IF(E13&lt;10%,40+400*(E13-5%),IF(E13&lt;15%,60+400*(E13-10%),IF(E13&lt;25%,80+200*(E13-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H13" s="34">
+        <f>IF(OR(F13="",G13=""),"",70%*F13+30%*G13)</f>
+        <v/>
+      </c>
+      <c r="I13">
+        <f>IF(H13="","",IF(H13&gt;=70,"BUY",IF(H13&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -4284,7 +4317,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-10-05</t>
+          <t>Retrieved 2026-10-06</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">

--- a/docs/downloads/indices/nifty200-quality-30.xlsx
+++ b/docs/downloads/indices/nifty200-quality-30.xlsx
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>19057</v>
+        <v>18843.6</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>25.82</v>
+        <v>25.53</v>
       </c>
     </row>
     <row r="6">
@@ -633,7 +633,7 @@
         </is>
       </c>
       <c r="B6" s="26" t="n">
-        <v>0.09701492537313433</v>
+        <v>0.06716417910447761</v>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>738.0712625871417</v>
+        <v>738.096357226792</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.01379595886898954</v>
+        <v>0.0137319215072782</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.03872966692486444</v>
+        <v>0.03916960438699569</v>
       </c>
     </row>
     <row r="8">
@@ -669,7 +669,7 @@
         </is>
       </c>
       <c r="B8" s="28" t="n">
-        <v>90.29850746268657</v>
+        <v>93.28358208955224</v>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
@@ -677,7 +677,7 @@
         </is>
       </c>
       <c r="E8" s="28" t="n">
-        <v>25.51838354759582</v>
+        <v>25.49276860291128</v>
       </c>
     </row>
     <row r="9">
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>70.86447028815934</v>
+        <v>72.94633804355995</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -736,13 +736,13 @@
         </is>
       </c>
       <c r="B13" s="29" t="n">
-        <v>26.45872228242423</v>
+        <v>26.45843246762151</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>19528.42256143139</v>
+        <v>19528.87262228252</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>0.02473750125577956</v>
+        <v>0.03636633245677667</v>
       </c>
     </row>
     <row r="14">
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="B14" s="29" t="n">
-        <v>29.5550377134632</v>
+        <v>29.55496525976252</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>21813.72400098637</v>
+        <v>21814.4121961951</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>0.1446567665942371</v>
+        <v>0.1576562968962991</v>
       </c>
     </row>
     <row r="16">
@@ -3823,7 +3823,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I13"/>
+  <dimension ref="A1:I14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -4277,6 +4277,39 @@
       </c>
       <c r="I13">
         <f>IF(H13="","",IF(H13&gt;=70,"BUY",IF(H13&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="31" t="n">
+        <v>46302</v>
+      </c>
+      <c r="B14" s="24" t="n">
+        <v>18843.6</v>
+      </c>
+      <c r="C14" s="25" t="n">
+        <v>25.53</v>
+      </c>
+      <c r="D14" s="26" t="n">
+        <v>0.0671641791045</v>
+      </c>
+      <c r="E14" s="26" t="n">
+        <v>0.0137319215073</v>
+      </c>
+      <c r="F14" s="34">
+        <f>IF(D14="","",100*(1-D14))</f>
+        <v/>
+      </c>
+      <c r="G14" s="34">
+        <f>IF(E14="","",IF(E14&lt;=0,20,IF(E14&lt;5%,20+400*E14,IF(E14&lt;10%,40+400*(E14-5%),IF(E14&lt;15%,60+400*(E14-10%),IF(E14&lt;25%,80+200*(E14-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H14" s="34">
+        <f>IF(OR(F14="",G14=""),"",70%*F14+30%*G14)</f>
+        <v/>
+      </c>
+      <c r="I14">
+        <f>IF(H14="","",IF(H14&gt;=70,"BUY",IF(H14&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -4317,7 +4350,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-10-06</t>
+          <t>Retrieved 2026-10-07</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">

--- a/docs/downloads/indices/nifty200-quality-30.xlsx
+++ b/docs/downloads/indices/nifty200-quality-30.xlsx
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>18843.6</v>
+        <v>18507.1</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>25.53</v>
+        <v>25.07</v>
       </c>
     </row>
     <row r="6">
@@ -633,7 +633,7 @@
         </is>
       </c>
       <c r="B6" s="26" t="n">
-        <v>0.06716417910447761</v>
+        <v>0.03731343283582089</v>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>738.096357226792</v>
+        <v>738.2169924212205</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.0137319215072782</v>
+        <v>0.01411439418661264</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.03916960438699569</v>
+        <v>0.03988831272437176</v>
       </c>
     </row>
     <row r="8">
@@ -669,7 +669,7 @@
         </is>
       </c>
       <c r="B8" s="28" t="n">
-        <v>93.28358208955224</v>
+        <v>96.26865671641791</v>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
@@ -677,7 +677,7 @@
         </is>
       </c>
       <c r="E8" s="28" t="n">
-        <v>25.49276860291128</v>
+        <v>25.64575767464506</v>
       </c>
     </row>
     <row r="9">
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>72.94633804355995</v>
+        <v>75.08178700388605</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -736,13 +736,13 @@
         </is>
       </c>
       <c r="B13" s="29" t="n">
-        <v>26.45843246762151</v>
+        <v>26.46016342969027</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>19528.87262228252</v>
+        <v>19533.34226603992</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>0.03636633245677667</v>
+        <v>0.05545127362147073</v>
       </c>
     </row>
     <row r="14">
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="B14" s="29" t="n">
-        <v>29.55496525976252</v>
+        <v>29.55539800027971</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>21814.4121961951</v>
+        <v>21818.29702157864</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>0.1576562968962991</v>
+        <v>0.1789149581284286</v>
       </c>
     </row>
     <row r="16">
@@ -3823,7 +3823,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I14"/>
+  <dimension ref="A1:I15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -4310,6 +4310,39 @@
       </c>
       <c r="I14">
         <f>IF(H14="","",IF(H14&gt;=70,"BUY",IF(H14&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="31" t="n">
+        <v>46303</v>
+      </c>
+      <c r="B15" s="24" t="n">
+        <v>18507.1</v>
+      </c>
+      <c r="C15" s="25" t="n">
+        <v>25.07</v>
+      </c>
+      <c r="D15" s="26" t="n">
+        <v>0.0373134328358</v>
+      </c>
+      <c r="E15" s="26" t="n">
+        <v>0.0141143941866</v>
+      </c>
+      <c r="F15" s="34">
+        <f>IF(D15="","",100*(1-D15))</f>
+        <v/>
+      </c>
+      <c r="G15" s="34">
+        <f>IF(E15="","",IF(E15&lt;=0,20,IF(E15&lt;5%,20+400*E15,IF(E15&lt;10%,40+400*(E15-5%),IF(E15&lt;15%,60+400*(E15-10%),IF(E15&lt;25%,80+200*(E15-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H15" s="34">
+        <f>IF(OR(F15="",G15=""),"",70%*F15+30%*G15)</f>
+        <v/>
+      </c>
+      <c r="I15">
+        <f>IF(H15="","",IF(H15&gt;=70,"BUY",IF(H15&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -4350,7 +4383,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-10-07</t>
+          <t>Retrieved 2026-10-08</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">

--- a/docs/downloads/indices/nifty200-quality-30.xlsx
+++ b/docs/downloads/indices/nifty200-quality-30.xlsx
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>18507.1</v>
+        <v>18863.35</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>25.07</v>
+        <v>25.55</v>
       </c>
     </row>
     <row r="6">
@@ -633,7 +633,7 @@
         </is>
       </c>
       <c r="B6" s="26" t="n">
-        <v>0.03731343283582089</v>
+        <v>0.06716417910447761</v>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>738.2169924212205</v>
+        <v>738.2915851272015</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.01411439418661264</v>
+        <v>0.01423379852363893</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.03988831272437176</v>
+        <v>0.03913894324853229</v>
       </c>
     </row>
     <row r="8">
@@ -669,7 +669,7 @@
         </is>
       </c>
       <c r="B8" s="28" t="n">
-        <v>96.26865671641791</v>
+        <v>93.28358208955224</v>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
@@ -677,7 +677,7 @@
         </is>
       </c>
       <c r="E8" s="28" t="n">
-        <v>25.64575767464506</v>
+        <v>25.69351940945557</v>
       </c>
     </row>
     <row r="9">
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>75.08178700388605</v>
+        <v>73.00656328552323</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -736,13 +736,13 @@
         </is>
       </c>
       <c r="B13" s="29" t="n">
-        <v>26.46016342969027</v>
+        <v>26.46070381960412</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>19533.34226603992</v>
+        <v>19535.71496655692</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>0.05545127362147073</v>
+        <v>0.03564398511170741</v>
       </c>
     </row>
     <row r="14">
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="B14" s="29" t="n">
-        <v>29.55539800027971</v>
+        <v>29.55553309775817</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>21818.29702157864</v>
+        <v>21820.60138002335</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>0.1789149581284286</v>
+        <v>0.1567723325932748</v>
       </c>
     </row>
     <row r="16">
@@ -3823,7 +3823,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I15"/>
+  <dimension ref="A1:I16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -4343,6 +4343,39 @@
       </c>
       <c r="I15">
         <f>IF(H15="","",IF(H15&gt;=70,"BUY",IF(H15&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="31" t="n">
+        <v>46304</v>
+      </c>
+      <c r="B16" s="24" t="n">
+        <v>18863.35</v>
+      </c>
+      <c r="C16" s="25" t="n">
+        <v>25.55</v>
+      </c>
+      <c r="D16" s="26" t="n">
+        <v>0.0671641791045</v>
+      </c>
+      <c r="E16" s="26" t="n">
+        <v>0.0142337985236</v>
+      </c>
+      <c r="F16" s="34">
+        <f>IF(D16="","",100*(1-D16))</f>
+        <v/>
+      </c>
+      <c r="G16" s="34">
+        <f>IF(E16="","",IF(E16&lt;=0,20,IF(E16&lt;5%,20+400*E16,IF(E16&lt;10%,40+400*(E16-5%),IF(E16&lt;15%,60+400*(E16-10%),IF(E16&lt;25%,80+200*(E16-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H16" s="34">
+        <f>IF(OR(F16="",G16=""),"",70%*F16+30%*G16)</f>
+        <v/>
+      </c>
+      <c r="I16">
+        <f>IF(H16="","",IF(H16&gt;=70,"BUY",IF(H16&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -4383,7 +4416,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-10-08</t>
+          <t>Retrieved 2026-10-09</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">

--- a/docs/downloads/indices/nifty200-quality-30.xlsx
+++ b/docs/downloads/indices/nifty200-quality-30.xlsx
@@ -568,7 +568,7 @@
     <col width="34" customWidth="1" min="1" max="1"/>
     <col width="34" customWidth="1" min="2" max="2"/>
     <col width="24" customWidth="1" min="3" max="3"/>
-    <col width="21" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
     <col width="29" customWidth="1" min="5" max="5"/>
     <col width="17" customWidth="1" min="6" max="6"/>
     <col width="19" customWidth="1" min="7" max="7"/>
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46304</v>
+        <v>46307</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>18863.35</v>
+        <v>18836.9</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>25.55</v>
+        <v>25.44</v>
       </c>
     </row>
     <row r="6">
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>738.2915851272015</v>
+        <v>740.4441823899372</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.01423379852363893</v>
+        <v>0.01681441014966567</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.03913894324853229</v>
+        <v>0.03930817610062893</v>
       </c>
     </row>
     <row r="8">
@@ -677,7 +677,7 @@
         </is>
       </c>
       <c r="E8" s="28" t="n">
-        <v>25.69351940945557</v>
+        <v>26.72576405986627</v>
       </c>
     </row>
     <row r="9">
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>73.00656328552323</v>
+        <v>73.31623668064644</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -736,13 +736,13 @@
         </is>
       </c>
       <c r="B13" s="29" t="n">
-        <v>26.46070381960412</v>
+        <v>26.47238293050592</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>19535.71496655692</v>
+        <v>19601.32193489178</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>0.03564398511170741</v>
+        <v>0.04058109003560983</v>
       </c>
     </row>
     <row r="14">
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="B14" s="29" t="n">
-        <v>29.55553309775817</v>
+        <v>29.55845287548362</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>21820.60138002335</v>
+        <v>21886.38447209896</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>0.1567723325932748</v>
+        <v>0.1618888708916519</v>
       </c>
     </row>
     <row r="16">
@@ -3823,7 +3823,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I16"/>
+  <dimension ref="A1:I17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -4376,6 +4376,39 @@
       </c>
       <c r="I16">
         <f>IF(H16="","",IF(H16&gt;=70,"BUY",IF(H16&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="31" t="n">
+        <v>46307</v>
+      </c>
+      <c r="B17" s="24" t="n">
+        <v>18836.9</v>
+      </c>
+      <c r="C17" s="25" t="n">
+        <v>25.44</v>
+      </c>
+      <c r="D17" s="26" t="n">
+        <v>0.0671641791045</v>
+      </c>
+      <c r="E17" s="26" t="n">
+        <v>0.0168144101497</v>
+      </c>
+      <c r="F17" s="34">
+        <f>IF(D17="","",100*(1-D17))</f>
+        <v/>
+      </c>
+      <c r="G17" s="34">
+        <f>IF(E17="","",IF(E17&lt;=0,20,IF(E17&lt;5%,20+400*E17,IF(E17&lt;10%,40+400*(E17-5%),IF(E17&lt;15%,60+400*(E17-10%),IF(E17&lt;25%,80+200*(E17-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H17" s="34">
+        <f>IF(OR(F17="",G17=""),"",70%*F17+30%*G17)</f>
+        <v/>
+      </c>
+      <c r="I17">
+        <f>IF(H17="","",IF(H17&gt;=70,"BUY",IF(H17&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -4416,7 +4449,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-10-09</t>
+          <t>Retrieved 2026-10-12</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">

--- a/docs/downloads/indices/nifty200-quality-30.xlsx
+++ b/docs/downloads/indices/nifty200-quality-30.xlsx
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>18836.9</v>
+        <v>19269.75</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>25.44</v>
+        <v>25.94</v>
       </c>
     </row>
     <row r="6">
@@ -633,7 +633,7 @@
         </is>
       </c>
       <c r="B6" s="26" t="n">
-        <v>0.06716417910447761</v>
+        <v>0.09701492537313433</v>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>740.4441823899372</v>
+        <v>742.8585196607555</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.01681441014966567</v>
+        <v>0.02126384716183782</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.03930817610062893</v>
+        <v>0.03855050115651503</v>
       </c>
     </row>
     <row r="8">
@@ -669,7 +669,7 @@
         </is>
       </c>
       <c r="B8" s="28" t="n">
-        <v>93.28358208955224</v>
+        <v>90.29850746268657</v>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
@@ -677,7 +677,7 @@
         </is>
       </c>
       <c r="E8" s="28" t="n">
-        <v>26.72576405986627</v>
+        <v>28.50553886473513</v>
       </c>
     </row>
     <row r="9">
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>73.31623668064644</v>
+        <v>71.76061688330114</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -736,13 +736,13 @@
         </is>
       </c>
       <c r="B13" s="29" t="n">
-        <v>26.47238293050592</v>
+        <v>26.49440966952175</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>19601.32193489178</v>
+        <v>19681.59794638654</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>0.04058109003560983</v>
+        <v>0.02137277060608134</v>
       </c>
     </row>
     <row r="14">
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="B14" s="29" t="n">
-        <v>29.55845287548362</v>
+        <v>29.59138386081369</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>21886.38447209896</v>
+        <v>21982.21160955723</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>0.1618888708916519</v>
+        <v>0.1407626777491782</v>
       </c>
     </row>
     <row r="16">
@@ -3823,7 +3823,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I17"/>
+  <dimension ref="A1:I18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -4409,6 +4409,39 @@
       </c>
       <c r="I17">
         <f>IF(H17="","",IF(H17&gt;=70,"BUY",IF(H17&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="31" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B18" s="24" t="n">
+        <v>19269.75</v>
+      </c>
+      <c r="C18" s="25" t="n">
+        <v>25.94</v>
+      </c>
+      <c r="D18" s="26" t="n">
+        <v>0.0970149253731</v>
+      </c>
+      <c r="E18" s="26" t="n">
+        <v>0.0212638471618</v>
+      </c>
+      <c r="F18" s="34">
+        <f>IF(D18="","",100*(1-D18))</f>
+        <v/>
+      </c>
+      <c r="G18" s="34">
+        <f>IF(E18="","",IF(E18&lt;=0,20,IF(E18&lt;5%,20+400*E18,IF(E18&lt;10%,40+400*(E18-5%),IF(E18&lt;15%,60+400*(E18-10%),IF(E18&lt;25%,80+200*(E18-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H18" s="34">
+        <f>IF(OR(F18="",G18=""),"",70%*F18+30%*G18)</f>
+        <v/>
+      </c>
+      <c r="I18">
+        <f>IF(H18="","",IF(H18&gt;=70,"BUY",IF(H18&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -4449,7 +4482,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-10-12</t>
+          <t>Retrieved 2026-10-13</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">

--- a/docs/downloads/indices/nifty200-quality-30.xlsx
+++ b/docs/downloads/indices/nifty200-quality-30.xlsx
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>19269.75</v>
+        <v>19407.55</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>25.94</v>
+        <v>26.12</v>
       </c>
     </row>
     <row r="6">
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>742.8585196607555</v>
+        <v>743.0149310872894</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.02126384716183782</v>
+        <v>0.02166940523553329</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.03855050115651503</v>
+        <v>0.03828483920367534</v>
       </c>
     </row>
     <row r="8">
@@ -677,7 +677,7 @@
         </is>
       </c>
       <c r="E8" s="28" t="n">
-        <v>28.50553886473513</v>
+        <v>28.66776209421332</v>
       </c>
     </row>
     <row r="9">
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>71.76061688330114</v>
+        <v>71.80928385214459</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -736,13 +736,13 @@
         </is>
       </c>
       <c r="B13" s="29" t="n">
-        <v>26.49440966952175</v>
+        <v>26.49762168946542</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>19681.59794638654</v>
+        <v>19688.12855357521</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>0.02137277060608134</v>
+        <v>0.01445718566100362</v>
       </c>
     </row>
     <row r="14">
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="B14" s="29" t="n">
-        <v>29.59138386081369</v>
+        <v>29.59551360074126</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>21982.21160955723</v>
+        <v>21989.9084985477</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>0.1407626777491782</v>
+        <v>0.1330594793545656</v>
       </c>
     </row>
     <row r="16">
@@ -3823,7 +3823,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I18"/>
+  <dimension ref="A1:I19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -4442,6 +4442,39 @@
       </c>
       <c r="I18">
         <f>IF(H18="","",IF(H18&gt;=70,"BUY",IF(H18&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="31" t="n">
+        <v>46309</v>
+      </c>
+      <c r="B19" s="24" t="n">
+        <v>19407.55</v>
+      </c>
+      <c r="C19" s="25" t="n">
+        <v>26.12</v>
+      </c>
+      <c r="D19" s="26" t="n">
+        <v>0.0970149253731</v>
+      </c>
+      <c r="E19" s="26" t="n">
+        <v>0.0216694052355</v>
+      </c>
+      <c r="F19" s="34">
+        <f>IF(D19="","",100*(1-D19))</f>
+        <v/>
+      </c>
+      <c r="G19" s="34">
+        <f>IF(E19="","",IF(E19&lt;=0,20,IF(E19&lt;5%,20+400*E19,IF(E19&lt;10%,40+400*(E19-5%),IF(E19&lt;15%,60+400*(E19-10%),IF(E19&lt;25%,80+200*(E19-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H19" s="34">
+        <f>IF(OR(F19="",G19=""),"",70%*F19+30%*G19)</f>
+        <v/>
+      </c>
+      <c r="I19">
+        <f>IF(H19="","",IF(H19&gt;=70,"BUY",IF(H19&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -4482,7 +4515,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-10-13</t>
+          <t>Retrieved 2026-10-14</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">

--- a/docs/downloads/indices/nifty200-quality-30.xlsx
+++ b/docs/downloads/indices/nifty200-quality-30.xlsx
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>19407.55</v>
+        <v>19368.7</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>26.12</v>
+        <v>26.07</v>
       </c>
     </row>
     <row r="6">
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>743.0149310872894</v>
+        <v>742.9497506712697</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.02166940523553329</v>
+        <v>0.02002506738512966</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.03828483920367534</v>
+        <v>0.03835826620636747</v>
       </c>
     </row>
     <row r="8">
@@ -677,7 +677,7 @@
         </is>
       </c>
       <c r="E8" s="28" t="n">
-        <v>28.66776209421332</v>
+        <v>28.01002695405186</v>
       </c>
     </row>
     <row r="9">
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>71.80928385214459</v>
+        <v>71.61196331009616</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -736,13 +736,13 @@
         </is>
       </c>
       <c r="B13" s="29" t="n">
-        <v>26.49762168946542</v>
+        <v>26.48691344782299</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>19688.12855357521</v>
+        <v>19678.44574211159</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>0.01445718566100362</v>
+        <v>0.01599207701660865</v>
       </c>
     </row>
     <row r="14">
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="B14" s="29" t="n">
-        <v>29.59551360074126</v>
+        <v>29.57876954331601</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>21989.9084985477</v>
+        <v>21975.53945736957</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>0.1330594793545656</v>
+        <v>0.1345903161993098</v>
       </c>
     </row>
     <row r="16">
@@ -3823,7 +3823,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I19"/>
+  <dimension ref="A1:I20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -4475,6 +4475,39 @@
       </c>
       <c r="I19">
         <f>IF(H19="","",IF(H19&gt;=70,"BUY",IF(H19&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="31" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B20" s="24" t="n">
+        <v>19368.7</v>
+      </c>
+      <c r="C20" s="25" t="n">
+        <v>26.07</v>
+      </c>
+      <c r="D20" s="26" t="n">
+        <v>0.0970149253731</v>
+      </c>
+      <c r="E20" s="26" t="n">
+        <v>0.0200250673851</v>
+      </c>
+      <c r="F20" s="34">
+        <f>IF(D20="","",100*(1-D20))</f>
+        <v/>
+      </c>
+      <c r="G20" s="34">
+        <f>IF(E20="","",IF(E20&lt;=0,20,IF(E20&lt;5%,20+400*E20,IF(E20&lt;10%,40+400*(E20-5%),IF(E20&lt;15%,60+400*(E20-10%),IF(E20&lt;25%,80+200*(E20-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H20" s="34">
+        <f>IF(OR(F20="",G20=""),"",70%*F20+30%*G20)</f>
+        <v/>
+      </c>
+      <c r="I20">
+        <f>IF(H20="","",IF(H20&gt;=70,"BUY",IF(H20&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -4515,7 +4548,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-10-14</t>
+          <t>Retrieved 2026-10-15</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">

--- a/docs/downloads/indices/nifty200-quality-30.xlsx
+++ b/docs/downloads/indices/nifty200-quality-30.xlsx
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>19368.7</v>
+        <v>19470.45</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>26.07</v>
+        <v>26.15</v>
       </c>
     </row>
     <row r="6">
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>742.9497506712697</v>
+        <v>744.5678776290632</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.02002506738512966</v>
+        <v>0.02112529626350312</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.03835826620636747</v>
+        <v>0.03824091778202677</v>
       </c>
     </row>
     <row r="8">
@@ -677,7 +677,7 @@
         </is>
       </c>
       <c r="E8" s="28" t="n">
-        <v>28.01002695405186</v>
+        <v>28.45011850540125</v>
       </c>
     </row>
     <row r="9">
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>71.61196331009616</v>
+        <v>71.74399077550098</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -736,13 +736,13 @@
         </is>
       </c>
       <c r="B13" s="29" t="n">
-        <v>26.48691344782299</v>
+        <v>26.49331234640695</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>19678.44574211159</v>
+        <v>19726.06934512807</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>0.01599207701660865</v>
+        <v>0.01312857921250266</v>
       </c>
     </row>
     <row r="14">
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="B14" s="29" t="n">
-        <v>29.57876954331601</v>
+        <v>29.58997301680893</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>21975.53945736957</v>
+        <v>22031.74340822667</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>0.1345903161993098</v>
+        <v>0.1315477253081807</v>
       </c>
     </row>
     <row r="16">
@@ -3823,7 +3823,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I20"/>
+  <dimension ref="A1:I21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -4508,6 +4508,39 @@
       </c>
       <c r="I20">
         <f>IF(H20="","",IF(H20&gt;=70,"BUY",IF(H20&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="31" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B21" s="24" t="n">
+        <v>19470.45</v>
+      </c>
+      <c r="C21" s="25" t="n">
+        <v>26.15</v>
+      </c>
+      <c r="D21" s="26" t="n">
+        <v>0.0970149253731</v>
+      </c>
+      <c r="E21" s="26" t="n">
+        <v>0.0211252962635</v>
+      </c>
+      <c r="F21" s="34">
+        <f>IF(D21="","",100*(1-D21))</f>
+        <v/>
+      </c>
+      <c r="G21" s="34">
+        <f>IF(E21="","",IF(E21&lt;=0,20,IF(E21&lt;5%,20+400*E21,IF(E21&lt;10%,40+400*(E21-5%),IF(E21&lt;15%,60+400*(E21-10%),IF(E21&lt;25%,80+200*(E21-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H21" s="34">
+        <f>IF(OR(F21="",G21=""),"",70%*F21+30%*G21)</f>
+        <v/>
+      </c>
+      <c r="I21">
+        <f>IF(H21="","",IF(H21&gt;=70,"BUY",IF(H21&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -4548,7 +4581,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-10-15</t>
+          <t>Retrieved 2026-10-16</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">

--- a/docs/downloads/indices/nifty200-quality-30.xlsx
+++ b/docs/downloads/indices/nifty200-quality-30.xlsx
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46311</v>
+        <v>46314</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>19470.45</v>
+        <v>19244.1</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>26.15</v>
+        <v>25.85</v>
       </c>
     </row>
     <row r="6">
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>744.5678776290632</v>
+        <v>744.4526112185686</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.02112529626350312</v>
+        <v>0.01971595708939722</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.03824091778202677</v>
+        <v>0.03868471953578336</v>
       </c>
     </row>
     <row r="8">
@@ -677,7 +677,7 @@
         </is>
       </c>
       <c r="E8" s="28" t="n">
-        <v>28.45011850540125</v>
+        <v>27.88638283575889</v>
       </c>
     </row>
     <row r="9">
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>71.74399077550098</v>
+        <v>71.57487007460826</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -736,13 +736,13 @@
         </is>
       </c>
       <c r="B13" s="29" t="n">
-        <v>26.49331234640695</v>
+        <v>26.48551450294173</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>19726.06934512807</v>
+        <v>19717.21043118224</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>0.01312857921250266</v>
+        <v>0.02458470030722348</v>
       </c>
     </row>
     <row r="14">
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="B14" s="29" t="n">
-        <v>29.58997301680893</v>
+        <v>29.57562191733318</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>22031.74340822667</v>
+        <v>22017.64896477181</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>0.1315477253081807</v>
+        <v>0.1441246389684014</v>
       </c>
     </row>
     <row r="16">
@@ -3823,7 +3823,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I21"/>
+  <dimension ref="A1:I22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -4541,6 +4541,39 @@
       </c>
       <c r="I21">
         <f>IF(H21="","",IF(H21&gt;=70,"BUY",IF(H21&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="31" t="n">
+        <v>46314</v>
+      </c>
+      <c r="B22" s="24" t="n">
+        <v>19244.1</v>
+      </c>
+      <c r="C22" s="25" t="n">
+        <v>25.85</v>
+      </c>
+      <c r="D22" s="26" t="n">
+        <v>0.0970149253731</v>
+      </c>
+      <c r="E22" s="26" t="n">
+        <v>0.0197159570894</v>
+      </c>
+      <c r="F22" s="34">
+        <f>IF(D22="","",100*(1-D22))</f>
+        <v/>
+      </c>
+      <c r="G22" s="34">
+        <f>IF(E22="","",IF(E22&lt;=0,20,IF(E22&lt;5%,20+400*E22,IF(E22&lt;10%,40+400*(E22-5%),IF(E22&lt;15%,60+400*(E22-10%),IF(E22&lt;25%,80+200*(E22-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H22" s="34">
+        <f>IF(OR(F22="",G22=""),"",70%*F22+30%*G22)</f>
+        <v/>
+      </c>
+      <c r="I22">
+        <f>IF(H22="","",IF(H22&gt;=70,"BUY",IF(H22&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -4581,7 +4614,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-10-16</t>
+          <t>Retrieved 2026-10-19</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">

--- a/docs/downloads/indices/nifty200-quality-30.xlsx
+++ b/docs/downloads/indices/nifty200-quality-30.xlsx
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46314</v>
+        <v>46316</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>19244.1</v>
+        <v>19156.1</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>25.85</v>
+        <v>25.73</v>
       </c>
     </row>
     <row r="6">
@@ -633,7 +633,7 @@
         </is>
       </c>
       <c r="B6" s="26" t="n">
-        <v>0.09701492537313433</v>
+        <v>0.08955223880597014</v>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>744.4526112185686</v>
+        <v>744.5044694908667</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.01971595708939722</v>
+        <v>0.01707634981675876</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.03868471953578336</v>
+        <v>0.0388651379712398</v>
       </c>
     </row>
     <row r="8">
@@ -669,7 +669,7 @@
         </is>
       </c>
       <c r="B8" s="28" t="n">
-        <v>90.29850746268657</v>
+        <v>91.04477611940298</v>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
@@ -677,7 +677,7 @@
         </is>
       </c>
       <c r="E8" s="28" t="n">
-        <v>27.88638283575889</v>
+        <v>26.8305399267035</v>
       </c>
     </row>
     <row r="9">
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>71.57487007460826</v>
+        <v>71.78050526159313</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -736,13 +736,13 @@
         </is>
       </c>
       <c r="B13" s="29" t="n">
-        <v>26.48551450294173</v>
+        <v>26.47356839459927</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>19717.21043118224</v>
+        <v>19709.68999315131</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>0.02458470030722348</v>
+        <v>0.02889888824715414</v>
       </c>
     </row>
     <row r="14">
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="B14" s="29" t="n">
-        <v>29.57562191733318</v>
+        <v>29.55874924150696</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>22017.64896477181</v>
+        <v>22006.6209228617</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>0.1441246389684014</v>
+        <v>0.1488048675284479</v>
       </c>
     </row>
     <row r="16">
@@ -3823,7 +3823,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I22"/>
+  <dimension ref="A1:I23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -4574,6 +4574,39 @@
       </c>
       <c r="I22">
         <f>IF(H22="","",IF(H22&gt;=70,"BUY",IF(H22&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="31" t="n">
+        <v>46316</v>
+      </c>
+      <c r="B23" s="24" t="n">
+        <v>19156.1</v>
+      </c>
+      <c r="C23" s="25" t="n">
+        <v>25.73</v>
+      </c>
+      <c r="D23" s="26" t="n">
+        <v>0.089552238806</v>
+      </c>
+      <c r="E23" s="26" t="n">
+        <v>0.0170763498168</v>
+      </c>
+      <c r="F23" s="34">
+        <f>IF(D23="","",100*(1-D23))</f>
+        <v/>
+      </c>
+      <c r="G23" s="34">
+        <f>IF(E23="","",IF(E23&lt;=0,20,IF(E23&lt;5%,20+400*E23,IF(E23&lt;10%,40+400*(E23-5%),IF(E23&lt;15%,60+400*(E23-10%),IF(E23&lt;25%,80+200*(E23-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H23" s="34">
+        <f>IF(OR(F23="",G23=""),"",70%*F23+30%*G23)</f>
+        <v/>
+      </c>
+      <c r="I23">
+        <f>IF(H23="","",IF(H23&gt;=70,"BUY",IF(H23&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -4614,7 +4647,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-10-19</t>
+          <t>Retrieved 2026-10-21</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">

--- a/docs/downloads/indices/nifty200-quality-30.xlsx
+++ b/docs/downloads/indices/nifty200-quality-30.xlsx
@@ -568,7 +568,7 @@
     <col width="34" customWidth="1" min="1" max="1"/>
     <col width="34" customWidth="1" min="2" max="2"/>
     <col width="24" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="21" customWidth="1" min="4" max="4"/>
     <col width="29" customWidth="1" min="5" max="5"/>
     <col width="17" customWidth="1" min="6" max="6"/>
     <col width="19" customWidth="1" min="7" max="7"/>
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>19156.1</v>
+        <v>18949.55</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>25.73</v>
+        <v>25.13</v>
       </c>
     </row>
     <row r="6">
@@ -633,7 +633,7 @@
         </is>
       </c>
       <c r="B6" s="26" t="n">
-        <v>0.08955223880597014</v>
+        <v>0.03731343283582089</v>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>744.5044694908667</v>
+        <v>754.0608834062873</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.01707634981675876</v>
+        <v>0.03013147974644337</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.0388651379712398</v>
+        <v>0.03979307600477517</v>
       </c>
     </row>
     <row r="8">
@@ -669,7 +669,7 @@
         </is>
       </c>
       <c r="B8" s="28" t="n">
-        <v>91.04477611940298</v>
+        <v>96.26865671641791</v>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
@@ -677,7 +677,7 @@
         </is>
       </c>
       <c r="E8" s="28" t="n">
-        <v>26.8305399267035</v>
+        <v>32.05259189857735</v>
       </c>
     </row>
     <row r="9">
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>71.78050526159313</v>
+        <v>77.00383727106575</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -736,13 +736,13 @@
         </is>
       </c>
       <c r="B13" s="29" t="n">
-        <v>26.47356839459927</v>
+        <v>26.56861959352769</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>19709.68999315131</v>
+        <v>20034.35676158108</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>0.02889888824715414</v>
+        <v>0.0572470988272058</v>
       </c>
     </row>
     <row r="14">
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="B14" s="29" t="n">
-        <v>29.55874924150696</v>
+        <v>29.66408075405248</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>22006.6209228617</v>
+        <v>22368.52293883626</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>0.1488048675284479</v>
+        <v>0.1804250200577986</v>
       </c>
     </row>
     <row r="16">
@@ -3823,7 +3823,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I23"/>
+  <dimension ref="A1:I24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -4607,6 +4607,39 @@
       </c>
       <c r="I23">
         <f>IF(H23="","",IF(H23&gt;=70,"BUY",IF(H23&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="31" t="n">
+        <v>46317</v>
+      </c>
+      <c r="B24" s="24" t="n">
+        <v>18949.55</v>
+      </c>
+      <c r="C24" s="25" t="n">
+        <v>25.13</v>
+      </c>
+      <c r="D24" s="26" t="n">
+        <v>0.0373134328358</v>
+      </c>
+      <c r="E24" s="26" t="n">
+        <v>0.0301314797464</v>
+      </c>
+      <c r="F24" s="34">
+        <f>IF(D24="","",100*(1-D24))</f>
+        <v/>
+      </c>
+      <c r="G24" s="34">
+        <f>IF(E24="","",IF(E24&lt;=0,20,IF(E24&lt;5%,20+400*E24,IF(E24&lt;10%,40+400*(E24-5%),IF(E24&lt;15%,60+400*(E24-10%),IF(E24&lt;25%,80+200*(E24-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H24" s="34">
+        <f>IF(OR(F24="",G24=""),"",70%*F24+30%*G24)</f>
+        <v/>
+      </c>
+      <c r="I24">
+        <f>IF(H24="","",IF(H24&gt;=70,"BUY",IF(H24&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -4647,7 +4680,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-10-21</t>
+          <t>Retrieved 2026-10-22</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">

--- a/docs/downloads/indices/nifty200-quality-30.xlsx
+++ b/docs/downloads/indices/nifty200-quality-30.xlsx
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>18949.55</v>
+        <v>18680</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>25.13</v>
+        <v>24.78</v>
       </c>
     </row>
     <row r="6">
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>754.0608834062873</v>
+        <v>753.8337368845843</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.03013147974644337</v>
+        <v>0.02975318782455671</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.03979307600477517</v>
+        <v>0.04035512510088781</v>
       </c>
     </row>
     <row r="8">
@@ -677,7 +677,7 @@
         </is>
       </c>
       <c r="E8" s="28" t="n">
-        <v>32.05259189857735</v>
+        <v>31.90127512982269</v>
       </c>
     </row>
     <row r="9">
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>77.00383727106575</v>
+        <v>76.95844224043934</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -736,13 +736,13 @@
         </is>
       </c>
       <c r="B13" s="29" t="n">
-        <v>26.56861959352769</v>
+        <v>26.56305545977376</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>20034.35676158108</v>
+        <v>20024.12736031372</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>0.0572470988272058</v>
+        <v>0.07195542614099115</v>
       </c>
     </row>
     <row r="14">
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="B14" s="29" t="n">
-        <v>29.66408075405248</v>
+        <v>29.66236871289742</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>22368.52293883626</v>
+        <v>22360.49425169184</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>0.1804250200577986</v>
+        <v>0.1970286001976358</v>
       </c>
     </row>
     <row r="16">
@@ -3823,7 +3823,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I24"/>
+  <dimension ref="A1:I25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -4640,6 +4640,39 @@
       </c>
       <c r="I24">
         <f>IF(H24="","",IF(H24&gt;=70,"BUY",IF(H24&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="31" t="n">
+        <v>46318</v>
+      </c>
+      <c r="B25" s="24" t="n">
+        <v>18680</v>
+      </c>
+      <c r="C25" s="25" t="n">
+        <v>24.78</v>
+      </c>
+      <c r="D25" s="26" t="n">
+        <v>0.0373134328358</v>
+      </c>
+      <c r="E25" s="26" t="n">
+        <v>0.0297531878246</v>
+      </c>
+      <c r="F25" s="34">
+        <f>IF(D25="","",100*(1-D25))</f>
+        <v/>
+      </c>
+      <c r="G25" s="34">
+        <f>IF(E25="","",IF(E25&lt;=0,20,IF(E25&lt;5%,20+400*E25,IF(E25&lt;10%,40+400*(E25-5%),IF(E25&lt;15%,60+400*(E25-10%),IF(E25&lt;25%,80+200*(E25-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H25" s="34">
+        <f>IF(OR(F25="",G25=""),"",70%*F25+30%*G25)</f>
+        <v/>
+      </c>
+      <c r="I25">
+        <f>IF(H25="","",IF(H25&gt;=70,"BUY",IF(H25&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -4680,7 +4713,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-10-22</t>
+          <t>Retrieved 2026-10-23</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">

--- a/docs/downloads/indices/nifty200-quality-30.xlsx
+++ b/docs/downloads/indices/nifty200-quality-30.xlsx
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46318</v>
+        <v>46321</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>18680</v>
+        <v>18808.5</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>24.78</v>
+        <v>24.93</v>
       </c>
     </row>
     <row r="6">
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>753.8337368845843</v>
+        <v>754.4524669073405</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.02975318782455671</v>
+        <v>0.03166952007814983</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.04035512510088781</v>
+        <v>0.04011231448054553</v>
       </c>
     </row>
     <row r="8">
@@ -677,7 +677,7 @@
         </is>
       </c>
       <c r="E8" s="28" t="n">
-        <v>31.90127512982269</v>
+        <v>32.66780803125993</v>
       </c>
     </row>
     <row r="9">
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>76.95844224043934</v>
+        <v>77.18840211087051</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -736,13 +736,13 @@
         </is>
       </c>
       <c r="B13" s="29" t="n">
-        <v>26.56305545977376</v>
+        <v>26.59124196960661</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>20024.12736031372</v>
+        <v>20061.82810209972</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>0.07195542614099115</v>
+        <v>0.06663626031314118</v>
       </c>
     </row>
     <row r="14">
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="B14" s="29" t="n">
-        <v>29.66236871289742</v>
+        <v>29.67104148515368</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>22360.49425169184</v>
+        <v>22385.39044418424</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>0.1970286001976358</v>
+        <v>0.1901741470177971</v>
       </c>
     </row>
     <row r="16">
@@ -3823,7 +3823,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I25"/>
+  <dimension ref="A1:I26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -4673,6 +4673,39 @@
       </c>
       <c r="I25">
         <f>IF(H25="","",IF(H25&gt;=70,"BUY",IF(H25&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="31" t="n">
+        <v>46321</v>
+      </c>
+      <c r="B26" s="24" t="n">
+        <v>18808.5</v>
+      </c>
+      <c r="C26" s="25" t="n">
+        <v>24.93</v>
+      </c>
+      <c r="D26" s="26" t="n">
+        <v>0.0373134328358</v>
+      </c>
+      <c r="E26" s="26" t="n">
+        <v>0.0316695200781</v>
+      </c>
+      <c r="F26" s="34">
+        <f>IF(D26="","",100*(1-D26))</f>
+        <v/>
+      </c>
+      <c r="G26" s="34">
+        <f>IF(E26="","",IF(E26&lt;=0,20,IF(E26&lt;5%,20+400*E26,IF(E26&lt;10%,40+400*(E26-5%),IF(E26&lt;15%,60+400*(E26-10%),IF(E26&lt;25%,80+200*(E26-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H26" s="34">
+        <f>IF(OR(F26="",G26=""),"",70%*F26+30%*G26)</f>
+        <v/>
+      </c>
+      <c r="I26">
+        <f>IF(H26="","",IF(H26&gt;=70,"BUY",IF(H26&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -4713,7 +4746,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-10-23</t>
+          <t>Retrieved 2026-10-26</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">

--- a/docs/downloads/indices/nifty200-quality-30.xlsx
+++ b/docs/downloads/indices/nifty200-quality-30.xlsx
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>18808.5</v>
+        <v>18824.35</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>24.93</v>
+        <v>24.9</v>
       </c>
     </row>
     <row r="6">
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>754.4524669073405</v>
+        <v>755.9979919678715</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.03166952007814983</v>
+        <v>0.03359622193153333</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.04011231448054553</v>
+        <v>0.04016064257028112</v>
       </c>
     </row>
     <row r="8">
@@ -677,7 +677,7 @@
         </is>
       </c>
       <c r="E8" s="28" t="n">
-        <v>32.66780803125993</v>
+        <v>33.43848877261333</v>
       </c>
     </row>
     <row r="9">
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>77.18840211087051</v>
+        <v>77.41960633327653</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -736,13 +736,13 @@
         </is>
       </c>
       <c r="B13" s="29" t="n">
-        <v>26.59124196960661</v>
+        <v>26.61958100143867</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>20061.82810209972</v>
+        <v>20124.34978411374</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>0.06663626031314118</v>
+        <v>0.06905947796942447</v>
       </c>
     </row>
     <row r="14">
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="B14" s="29" t="n">
-        <v>29.67104148515368</v>
+        <v>29.67976118725586</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>22385.39044418424</v>
+        <v>22437.8398596514</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>0.1901741470177971</v>
+        <v>0.1919582806126852</v>
       </c>
     </row>
     <row r="16">
@@ -3823,7 +3823,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I26"/>
+  <dimension ref="A1:I27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -4706,6 +4706,39 @@
       </c>
       <c r="I26">
         <f>IF(H26="","",IF(H26&gt;=70,"BUY",IF(H26&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="31" t="n">
+        <v>46322</v>
+      </c>
+      <c r="B27" s="24" t="n">
+        <v>18824.35</v>
+      </c>
+      <c r="C27" s="25" t="n">
+        <v>24.9</v>
+      </c>
+      <c r="D27" s="26" t="n">
+        <v>0.0373134328358</v>
+      </c>
+      <c r="E27" s="26" t="n">
+        <v>0.0335962219315</v>
+      </c>
+      <c r="F27" s="34">
+        <f>IF(D27="","",100*(1-D27))</f>
+        <v/>
+      </c>
+      <c r="G27" s="34">
+        <f>IF(E27="","",IF(E27&lt;=0,20,IF(E27&lt;5%,20+400*E27,IF(E27&lt;10%,40+400*(E27-5%),IF(E27&lt;15%,60+400*(E27-10%),IF(E27&lt;25%,80+200*(E27-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H27" s="34">
+        <f>IF(OR(F27="",G27=""),"",70%*F27+30%*G27)</f>
+        <v/>
+      </c>
+      <c r="I27">
+        <f>IF(H27="","",IF(H27&gt;=70,"BUY",IF(H27&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -4746,7 +4779,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-10-26</t>
+          <t>Retrieved 2026-10-27</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">

--- a/docs/downloads/indices/nifty200-quality-30.xlsx
+++ b/docs/downloads/indices/nifty200-quality-30.xlsx
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>18824.35</v>
+        <v>18770.3</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>24.9</v>
+        <v>24.71</v>
       </c>
     </row>
     <row r="6">
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>755.9979919678715</v>
+        <v>759.623634156212</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.03359622193153333</v>
+        <v>0.03848321222679707</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.04016064257028112</v>
+        <v>0.04046944556859571</v>
       </c>
     </row>
     <row r="8">
@@ -677,7 +677,7 @@
         </is>
       </c>
       <c r="E8" s="28" t="n">
-        <v>33.43848877261333</v>
+        <v>35.39328489071883</v>
       </c>
     </row>
     <row r="9">
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>77.41960633327653</v>
+        <v>78.00604516870818</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -736,13 +736,13 @@
         </is>
       </c>
       <c r="B13" s="29" t="n">
-        <v>26.61958100143867</v>
+        <v>26.69033730321553</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>20124.34978411374</v>
+        <v>20274.61101912369</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>0.06905947796942447</v>
+        <v>0.08014315269994055</v>
       </c>
     </row>
     <row r="14">
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="B14" s="29" t="n">
-        <v>29.67976118725586</v>
+        <v>29.76126985429566</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>22437.8398596514</v>
+        <v>22607.36396382378</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>0.1919582806126852</v>
+        <v>0.2044220904207064</v>
       </c>
     </row>
     <row r="16">
@@ -3823,7 +3823,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I27"/>
+  <dimension ref="A1:I28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -4739,6 +4739,39 @@
       </c>
       <c r="I27">
         <f>IF(H27="","",IF(H27&gt;=70,"BUY",IF(H27&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="31" t="n">
+        <v>46323</v>
+      </c>
+      <c r="B28" s="24" t="n">
+        <v>18770.3</v>
+      </c>
+      <c r="C28" s="25" t="n">
+        <v>24.71</v>
+      </c>
+      <c r="D28" s="26" t="n">
+        <v>0.0373134328358</v>
+      </c>
+      <c r="E28" s="26" t="n">
+        <v>0.0384832122268</v>
+      </c>
+      <c r="F28" s="34">
+        <f>IF(D28="","",100*(1-D28))</f>
+        <v/>
+      </c>
+      <c r="G28" s="34">
+        <f>IF(E28="","",IF(E28&lt;=0,20,IF(E28&lt;5%,20+400*E28,IF(E28&lt;10%,40+400*(E28-5%),IF(E28&lt;15%,60+400*(E28-10%),IF(E28&lt;25%,80+200*(E28-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H28" s="34">
+        <f>IF(OR(F28="",G28=""),"",70%*F28+30%*G28)</f>
+        <v/>
+      </c>
+      <c r="I28">
+        <f>IF(H28="","",IF(H28&gt;=70,"BUY",IF(H28&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -4779,7 +4812,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-10-27</t>
+          <t>Retrieved 2026-10-28</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">

--- a/docs/downloads/indices/nifty200-quality-30.xlsx
+++ b/docs/downloads/indices/nifty200-quality-30.xlsx
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>18770.3</v>
+        <v>18930.75</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>24.71</v>
+        <v>24.92</v>
       </c>
     </row>
     <row r="6">
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>759.623634156212</v>
+        <v>759.6609149277688</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.03848321222679707</v>
+        <v>0.03858803895287433</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.04046944556859571</v>
+        <v>0.04012841091492777</v>
       </c>
     </row>
     <row r="8">
@@ -677,7 +677,7 @@
         </is>
       </c>
       <c r="E8" s="28" t="n">
-        <v>35.39328489071883</v>
+        <v>35.43521558114973</v>
       </c>
     </row>
     <row r="9">
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>78.00604516870818</v>
+        <v>78.01862437583746</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -736,13 +736,13 @@
         </is>
       </c>
       <c r="B13" s="29" t="n">
-        <v>26.69033730321553</v>
+        <v>26.69069311507433</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>20274.61101912369</v>
+        <v>20275.87635185366</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>0.08014315269994055</v>
+        <v>0.07105510092593592</v>
       </c>
     </row>
     <row r="14">
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="B14" s="29" t="n">
-        <v>29.76126985429566</v>
+        <v>29.76411634916605</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>22607.36396382378</v>
+        <v>22610.63585782404</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>0.2044220904207064</v>
+        <v>0.1943866913790548</v>
       </c>
     </row>
     <row r="16">
@@ -3823,7 +3823,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I28"/>
+  <dimension ref="A1:I29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -4772,6 +4772,39 @@
       </c>
       <c r="I28">
         <f>IF(H28="","",IF(H28&gt;=70,"BUY",IF(H28&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="31" t="n">
+        <v>46324</v>
+      </c>
+      <c r="B29" s="24" t="n">
+        <v>18930.75</v>
+      </c>
+      <c r="C29" s="25" t="n">
+        <v>24.92</v>
+      </c>
+      <c r="D29" s="26" t="n">
+        <v>0.0373134328358</v>
+      </c>
+      <c r="E29" s="26" t="n">
+        <v>0.0385880389529</v>
+      </c>
+      <c r="F29" s="34">
+        <f>IF(D29="","",100*(1-D29))</f>
+        <v/>
+      </c>
+      <c r="G29" s="34">
+        <f>IF(E29="","",IF(E29&lt;=0,20,IF(E29&lt;5%,20+400*E29,IF(E29&lt;10%,40+400*(E29-5%),IF(E29&lt;15%,60+400*(E29-10%),IF(E29&lt;25%,80+200*(E29-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H29" s="34">
+        <f>IF(OR(F29="",G29=""),"",70%*F29+30%*G29)</f>
+        <v/>
+      </c>
+      <c r="I29">
+        <f>IF(H29="","",IF(H29&gt;=70,"BUY",IF(H29&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -4812,7 +4845,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-10-28</t>
+          <t>Retrieved 2026-10-29</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">

--- a/docs/downloads/indices/nifty200-quality-30.xlsx
+++ b/docs/downloads/indices/nifty200-quality-30.xlsx
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46324</v>
+        <v>46325</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>18930.75</v>
+        <v>18937.8</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>24.92</v>
+        <v>24.87</v>
       </c>
     </row>
     <row r="6">
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>759.6609149277688</v>
+        <v>761.4716525934861</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.03858803895287433</v>
+        <v>0.04104284292970073</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.04012841091492777</v>
+        <v>0.04020908725371934</v>
       </c>
     </row>
     <row r="8">
@@ -677,7 +677,7 @@
         </is>
       </c>
       <c r="E8" s="28" t="n">
-        <v>35.43521558114973</v>
+        <v>36.41713717188029</v>
       </c>
     </row>
     <row r="9">
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>78.01862437583746</v>
+        <v>78.31320085305663</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -736,13 +736,13 @@
         </is>
       </c>
       <c r="B13" s="29" t="n">
-        <v>26.69069311507433</v>
+        <v>26.69902542114424</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>20275.87635185366</v>
+        <v>20330.5510100742</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>0.07105510092593592</v>
+        <v>0.07354344274805946</v>
       </c>
     </row>
     <row r="14">
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="B14" s="29" t="n">
-        <v>29.76411634916605</v>
+        <v>29.83077479772536</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>22610.63585782404</v>
+        <v>22715.28938336804</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>0.1943866913790548</v>
+        <v>0.1994682266877907</v>
       </c>
     </row>
     <row r="16">
@@ -3823,7 +3823,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I29"/>
+  <dimension ref="A1:I30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -4805,6 +4805,39 @@
       </c>
       <c r="I29">
         <f>IF(H29="","",IF(H29&gt;=70,"BUY",IF(H29&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="31" t="n">
+        <v>46325</v>
+      </c>
+      <c r="B30" s="24" t="n">
+        <v>18937.8</v>
+      </c>
+      <c r="C30" s="25" t="n">
+        <v>24.87</v>
+      </c>
+      <c r="D30" s="26" t="n">
+        <v>0.0373134328358</v>
+      </c>
+      <c r="E30" s="26" t="n">
+        <v>0.0410428429297</v>
+      </c>
+      <c r="F30" s="34">
+        <f>IF(D30="","",100*(1-D30))</f>
+        <v/>
+      </c>
+      <c r="G30" s="34">
+        <f>IF(E30="","",IF(E30&lt;=0,20,IF(E30&lt;5%,20+400*E30,IF(E30&lt;10%,40+400*(E30-5%),IF(E30&lt;15%,60+400*(E30-10%),IF(E30&lt;25%,80+200*(E30-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H30" s="34">
+        <f>IF(OR(F30="",G30=""),"",70%*F30+30%*G30)</f>
+        <v/>
+      </c>
+      <c r="I30">
+        <f>IF(H30="","",IF(H30&gt;=70,"BUY",IF(H30&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -4845,7 +4878,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-10-29</t>
+          <t>Retrieved 2026-10-30</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
